--- a/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{072A289B-6041-451D-BEAF-1CFCFFDCB9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F3B1894-699C-4A48-B126-7D196A3AC48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1371,18 +1371,354 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_030</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 30</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_005</t>
   </si>
   <si>
@@ -1413,28 +1749,46 @@
     <t>connecting solar to buses in cluster 53</t>
   </si>
   <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
   </si>
   <si>
     <t>distr_solelc_spv_006</t>
@@ -1491,360 +1845,6 @@
     <t>connecting solar to buses in cluster 41</t>
   </si>
   <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1854,88 +1854,190 @@
     <t>e_gen1</t>
   </si>
   <si>
+    <t>e_gen2,e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem2</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen0</t>
+  </si>
+  <si>
+    <t>e_gen0</t>
+  </si>
+  <si>
+    <t>e_dem0</t>
+  </si>
+  <si>
+    <t>e_dem1</t>
+  </si>
+  <si>
+    <t>e_dem1,e_gen2</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen2</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem4</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem0</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem2</t>
+  </si>
+  <si>
+    <t>e_dem4</t>
+  </si>
+  <si>
+    <t>e_dem3,e_dem4</t>
+  </si>
+  <si>
+    <t>e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen4</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem0,e_dem2</t>
+  </si>
+  <si>
     <t>e_gen1,e_dem3</t>
   </si>
   <si>
-    <t>e_gen4</t>
+    <t>e_dem4,e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen3</t>
   </si>
   <si>
     <t>e_dem3</t>
   </si>
   <si>
+    <t>e_dem3,e_dem0,e_gen3</t>
+  </si>
+  <si>
+    <t>e_dem3,e_gen2,e_dem4</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem1</t>
+  </si>
+  <si>
     <t>e_dem0,e_gen4</t>
   </si>
   <si>
-    <t>e_dem4,e_gen3</t>
-  </si>
-  <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen0</t>
+    <t>e_dem3,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem0</t>
   </si>
   <si>
     <t>e_gen1,e_dem3,e_dem0</t>
   </si>
   <si>
-    <t>e_dem4</t>
-  </si>
-  <si>
-    <t>e_gen3</t>
-  </si>
-  <si>
-    <t>e_dem2</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem3,e_dem4</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen0</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem2</t>
-  </si>
-  <si>
-    <t>e_dem3,e_dem0,e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem4</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen2,e_dem4</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen4,e_dem0</t>
-  </si>
-  <si>
-    <t>e_dem4,e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen2</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem0,e_dem2</t>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
   </si>
   <si>
     <t>distr_wonelc_won_057</t>
@@ -1980,6 +2082,30 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_wonelc_won_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_053</t>
   </si>
   <si>
@@ -2004,6 +2130,150 @@
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_065</t>
   </si>
   <si>
@@ -2034,28 +2304,16 @@
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_wonelc_won_050</t>
@@ -2082,262 +2340,61 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_dem1,e_gen2,e_dem4</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>e_dem0,e_dem3</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
   </si>
   <si>
     <t>elc_won_057</t>
@@ -2364,6 +2421,18 @@
     <t>elc_won_010</t>
   </si>
   <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
     <t>elc_won_053</t>
   </si>
   <si>
@@ -2379,6 +2448,90 @@
     <t>elc_won_011</t>
   </si>
   <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem3,e_dem1</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem4,e_dem1</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_dem0,e_dem3,e_gen3</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen2</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
     <t>elc_won_065</t>
   </si>
   <si>
@@ -2394,16 +2547,10 @@
     <t>elc_won_009</t>
   </si>
   <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
   </si>
   <si>
     <t>elc_won_050</t>
@@ -2418,153 +2565,6 @@
     <t>elc_won_016</t>
   </si>
   <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>elc_won_066</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen2,e_dem4</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>e_dem0,e_dem3</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>elc_won_067</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem3,e_dem1</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem4,e_dem1</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_dem0,e_dem3,e_gen3</t>
-  </si>
-  <si>
-    <t>elc_won_044</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen2</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_006</t>
   </si>
   <si>
@@ -2583,6 +2583,18 @@
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_010</t>
   </si>
   <si>
@@ -2595,6 +2607,78 @@
     <t>connecting wind offshore to buses in cluster 22</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_007</t>
   </si>
   <si>
@@ -2613,72 +2697,6 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_011</t>
   </si>
   <si>
@@ -2691,24 +2709,6 @@
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
@@ -2718,12 +2718,57 @@
     <t>elc_wof_014</t>
   </si>
   <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
     <t>elc_wof_010</t>
   </si>
   <si>
     <t>elc_wof_022</t>
   </si>
   <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_dem3,e_gen2</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
     <t>elc_wof_007</t>
   </si>
   <si>
@@ -2733,55 +2778,10 @@
     <t>elc_wof_023</t>
   </si>
   <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen2</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
     <t>elc_wof_011</t>
   </si>
   <si>
     <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -8106,7 +8106,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A706CA-46DB-4183-B3FA-D5923589792A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB753E1-BBE6-48B4-B6AC-D1327C335CC8}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8344,16 +8344,16 @@
         <v>414</v>
       </c>
       <c r="Y11" t="s">
-        <v>363</v>
+        <v>335</v>
       </c>
       <c r="Z11" t="s">
         <v>574</v>
       </c>
       <c r="AA11">
-        <v>0.98055369884714538</v>
+        <v>0.98443531955055918</v>
       </c>
       <c r="AB11">
-        <v>356.51552113566873</v>
+        <v>285.35247490641569</v>
       </c>
       <c r="AD11" t="s">
         <v>413</v>
@@ -8383,13 +8383,13 @@
         <v>737</v>
       </c>
       <c r="AN11" t="s">
-        <v>738</v>
+        <v>574</v>
       </c>
       <c r="AO11">
-        <v>0.98045336302656594</v>
+        <v>0.98039873263051136</v>
       </c>
       <c r="AP11">
-        <v>358.3550111796236</v>
+        <v>359.35656844062476</v>
       </c>
       <c r="AR11" t="s">
         <v>413</v>
@@ -8490,16 +8490,16 @@
         <v>418</v>
       </c>
       <c r="Y12" t="s">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="Z12" t="s">
         <v>575</v>
       </c>
       <c r="AA12">
-        <v>0.99284163372730061</v>
+        <v>0.97398849158227818</v>
       </c>
       <c r="AB12">
-        <v>131.23671499948927</v>
+        <v>476.87765432490079</v>
       </c>
       <c r="AD12" t="s">
         <v>413</v>
@@ -8526,16 +8526,16 @@
         <v>605</v>
       </c>
       <c r="AM12" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AN12" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="AO12">
-        <v>0.98832832974245843</v>
+        <v>0.98326547324039271</v>
       </c>
       <c r="AP12">
-        <v>213.98062138826123</v>
+        <v>306.79965725946761</v>
       </c>
       <c r="AR12" t="s">
         <v>413</v>
@@ -8636,16 +8636,16 @@
         <v>420</v>
       </c>
       <c r="Y13" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="Z13" t="s">
         <v>576</v>
       </c>
       <c r="AA13">
-        <v>0.980949293282396</v>
+        <v>0.98814122429339546</v>
       </c>
       <c r="AB13">
-        <v>349.26295648940771</v>
+        <v>217.4108879544159</v>
       </c>
       <c r="AD13" t="s">
         <v>413</v>
@@ -8672,16 +8672,16 @@
         <v>607</v>
       </c>
       <c r="AM13" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AN13" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="AO13">
-        <v>0.98934334912020028</v>
+        <v>0.98997462954848647</v>
       </c>
       <c r="AP13">
-        <v>195.37193279632865</v>
+        <v>183.79845827774895</v>
       </c>
       <c r="AR13" t="s">
         <v>413</v>
@@ -8782,16 +8782,16 @@
         <v>422</v>
       </c>
       <c r="Y14" t="s">
-        <v>342</v>
+        <v>373</v>
       </c>
       <c r="Z14" t="s">
         <v>577</v>
       </c>
       <c r="AA14">
-        <v>0.98440429555001041</v>
+        <v>0.97065607524213282</v>
       </c>
       <c r="AB14">
-        <v>285.92124824980857</v>
+        <v>537.97195389423189</v>
       </c>
       <c r="AD14" t="s">
         <v>413</v>
@@ -8818,16 +8818,16 @@
         <v>609</v>
       </c>
       <c r="AM14" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AN14" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="AO14">
-        <v>0.99072024613784004</v>
+        <v>0.98425147469462704</v>
       </c>
       <c r="AP14">
-        <v>170.12882080626682</v>
+        <v>288.72296393183791</v>
       </c>
       <c r="AR14" t="s">
         <v>413</v>
@@ -8857,13 +8857,13 @@
         <v>863</v>
       </c>
       <c r="BB14" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="BC14">
-        <v>0.96827543539739536</v>
+        <v>0.97204337209146163</v>
       </c>
       <c r="BD14">
-        <v>581.61701771441915</v>
+        <v>512.53817832320431</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8928,16 +8928,16 @@
         <v>424</v>
       </c>
       <c r="Y15" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="Z15" t="s">
         <v>578</v>
       </c>
       <c r="AA15">
-        <v>0.97996308088186879</v>
+        <v>0.97916314637278834</v>
       </c>
       <c r="AB15">
-        <v>367.343517165739</v>
+        <v>382.00898316554651</v>
       </c>
       <c r="AD15" t="s">
         <v>413</v>
@@ -8964,16 +8964,16 @@
         <v>611</v>
       </c>
       <c r="AM15" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AN15" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO15">
-        <v>0.97416703287609641</v>
+        <v>0.97434541537281683</v>
       </c>
       <c r="AP15">
-        <v>473.6043972715658</v>
+        <v>470.33405149835795</v>
       </c>
       <c r="AR15" t="s">
         <v>413</v>
@@ -9003,13 +9003,13 @@
         <v>864</v>
       </c>
       <c r="BB15" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="BC15">
-        <v>0.96595696185315882</v>
+        <v>0.97090678081281612</v>
       </c>
       <c r="BD15">
-        <v>624.12236602542168</v>
+        <v>533.37568509837058</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9074,16 +9074,16 @@
         <v>426</v>
       </c>
       <c r="Y16" t="s">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="Z16" t="s">
         <v>579</v>
       </c>
       <c r="AA16">
-        <v>0.97636760270586087</v>
+        <v>0.99243389564470808</v>
       </c>
       <c r="AB16">
-        <v>433.26061705921813</v>
+        <v>138.71191318035258</v>
       </c>
       <c r="AD16" t="s">
         <v>413</v>
@@ -9110,16 +9110,16 @@
         <v>613</v>
       </c>
       <c r="AM16" t="s">
+        <v>742</v>
+      </c>
+      <c r="AN16" t="s">
         <v>743</v>
       </c>
-      <c r="AN16" t="s">
-        <v>593</v>
-      </c>
       <c r="AO16">
-        <v>0.97182188871578934</v>
+        <v>0.98430775783289481</v>
       </c>
       <c r="AP16">
-        <v>516.59870687719467</v>
+        <v>287.69110639692803</v>
       </c>
       <c r="AR16" t="s">
         <v>413</v>
@@ -9149,13 +9149,13 @@
         <v>865</v>
       </c>
       <c r="BB16" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="BC16">
-        <v>0.96884606421228714</v>
+        <v>0.96827543539739536</v>
       </c>
       <c r="BD16">
-        <v>571.15548944140187</v>
+        <v>581.61701771441915</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9220,16 +9220,16 @@
         <v>428</v>
       </c>
       <c r="Y17" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="Z17" t="s">
         <v>580</v>
       </c>
       <c r="AA17">
-        <v>0.99165078812878382</v>
+        <v>0.98258925616289594</v>
       </c>
       <c r="AB17">
-        <v>153.06888430562992</v>
+        <v>319.19697034690739</v>
       </c>
       <c r="AD17" t="s">
         <v>413</v>
@@ -9259,13 +9259,13 @@
         <v>744</v>
       </c>
       <c r="AN17" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AO17">
-        <v>0.97902953573897011</v>
+        <v>0.97444364094885727</v>
       </c>
       <c r="AP17">
-        <v>384.45851145221434</v>
+        <v>468.53324927094968</v>
       </c>
       <c r="AR17" t="s">
         <v>413</v>
@@ -9295,13 +9295,13 @@
         <v>866</v>
       </c>
       <c r="BB17" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="BC17">
-        <v>0.97158773589553182</v>
+        <v>0.96595696185315882</v>
       </c>
       <c r="BD17">
-        <v>520.89150858191567</v>
+        <v>624.12236602542168</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9366,16 +9366,16 @@
         <v>430</v>
       </c>
       <c r="Y18" t="s">
-        <v>353</v>
+        <v>401</v>
       </c>
       <c r="Z18" t="s">
         <v>581</v>
       </c>
       <c r="AA18">
-        <v>0.97646479583958734</v>
+        <v>0.98625535317143753</v>
       </c>
       <c r="AB18">
-        <v>431.47874294089837</v>
+        <v>251.98519185697839</v>
       </c>
       <c r="AD18" t="s">
         <v>413</v>
@@ -9405,13 +9405,13 @@
         <v>745</v>
       </c>
       <c r="AN18" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AO18">
-        <v>0.98879946679477992</v>
+        <v>0.98574603285635165</v>
       </c>
       <c r="AP18">
-        <v>205.34310876236799</v>
+        <v>261.32273096688704</v>
       </c>
       <c r="AR18" t="s">
         <v>413</v>
@@ -9441,13 +9441,13 @@
         <v>867</v>
       </c>
       <c r="BB18" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="BC18">
-        <v>0.96837970323216338</v>
+        <v>0.96139268083002405</v>
       </c>
       <c r="BD18">
-        <v>579.70544074367149</v>
+        <v>707.80085144956001</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9512,16 +9512,16 @@
         <v>432</v>
       </c>
       <c r="Y19" t="s">
-        <v>372</v>
+        <v>405</v>
       </c>
       <c r="Z19" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AA19">
-        <v>0.96562135615554268</v>
+        <v>0.98719346865782154</v>
       </c>
       <c r="AB19">
-        <v>630.27513714838358</v>
+        <v>234.78640793993935</v>
       </c>
       <c r="AD19" t="s">
         <v>413</v>
@@ -9551,13 +9551,13 @@
         <v>746</v>
       </c>
       <c r="AN19" t="s">
-        <v>574</v>
+        <v>747</v>
       </c>
       <c r="AO19">
-        <v>0.98121294780398804</v>
+        <v>0.97968688829580564</v>
       </c>
       <c r="AP19">
-        <v>344.42929026021937</v>
+        <v>372.40704791023012</v>
       </c>
       <c r="AR19" t="s">
         <v>413</v>
@@ -9587,13 +9587,13 @@
         <v>868</v>
       </c>
       <c r="BB19" t="s">
-        <v>584</v>
+        <v>869</v>
       </c>
       <c r="BC19">
-        <v>0.98341789520181955</v>
+        <v>0.96285001328169728</v>
       </c>
       <c r="BD19">
-        <v>304.0052546333078</v>
+        <v>681.08308983555014</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9658,16 +9658,16 @@
         <v>434</v>
       </c>
       <c r="Y20" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="Z20" t="s">
         <v>582</v>
       </c>
       <c r="AA20">
-        <v>0.98843111817052332</v>
+        <v>0.97184397355215157</v>
       </c>
       <c r="AB20">
-        <v>212.09616687373853</v>
+        <v>516.19381821055424</v>
       </c>
       <c r="AD20" t="s">
         <v>413</v>
@@ -9694,16 +9694,16 @@
         <v>621</v>
       </c>
       <c r="AM20" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AN20" t="s">
-        <v>748</v>
+        <v>580</v>
       </c>
       <c r="AO20">
-        <v>0.97759288697657265</v>
+        <v>0.98420825457429406</v>
       </c>
       <c r="AP20">
-        <v>410.79707209616811</v>
+        <v>289.51533280460853</v>
       </c>
       <c r="AR20" t="s">
         <v>413</v>
@@ -9730,16 +9730,16 @@
         <v>830</v>
       </c>
       <c r="BA20" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="BB20" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="BC20">
-        <v>0.97048325247055856</v>
+        <v>0.98427567578715769</v>
       </c>
       <c r="BD20">
-        <v>541.14037137309333</v>
+        <v>288.27927723544332</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9804,16 +9804,16 @@
         <v>436</v>
       </c>
       <c r="Y21" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="Z21" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AA21">
-        <v>0.97878284543380634</v>
+        <v>0.97870278293688284</v>
       </c>
       <c r="AB21">
-        <v>388.98116704688283</v>
+        <v>390.44897949048118</v>
       </c>
       <c r="AD21" t="s">
         <v>413</v>
@@ -9843,13 +9843,13 @@
         <v>749</v>
       </c>
       <c r="AN21" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="AO21">
-        <v>0.97393752600115946</v>
+        <v>0.98302364254854535</v>
       </c>
       <c r="AP21">
-        <v>477.81202331207646</v>
+        <v>311.23321994333526</v>
       </c>
       <c r="AR21" t="s">
         <v>413</v>
@@ -9876,16 +9876,16 @@
         <v>832</v>
       </c>
       <c r="BA21" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="BB21" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="BC21">
-        <v>0.96692898910976954</v>
+        <v>0.96271559874449242</v>
       </c>
       <c r="BD21">
-        <v>606.30186632089146</v>
+        <v>683.54735635097268</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9950,16 +9950,16 @@
         <v>438</v>
       </c>
       <c r="Y22" t="s">
-        <v>340</v>
+        <v>395</v>
       </c>
       <c r="Z22" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="AA22">
-        <v>0.9898744603534384</v>
+        <v>0.98376398069352888</v>
       </c>
       <c r="AB22">
-        <v>185.63489352029583</v>
+        <v>297.66035395197099</v>
       </c>
       <c r="AD22" t="s">
         <v>413</v>
@@ -9989,13 +9989,13 @@
         <v>750</v>
       </c>
       <c r="AN22" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="AO22">
-        <v>0.97612238282801922</v>
+        <v>0.98689046040235784</v>
       </c>
       <c r="AP22">
-        <v>437.75631481964848</v>
+        <v>240.34155929010652</v>
       </c>
       <c r="AR22" t="s">
         <v>413</v>
@@ -10022,16 +10022,16 @@
         <v>834</v>
       </c>
       <c r="BA22" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="BB22" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="BC22">
-        <v>0.97481390334887996</v>
+        <v>0.97945251828158475</v>
       </c>
       <c r="BD22">
-        <v>461.74510527053314</v>
+        <v>376.70383150428029</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10096,16 +10096,16 @@
         <v>440</v>
       </c>
       <c r="Y23" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="Z23" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AA23">
-        <v>0.98205187669897798</v>
+        <v>0.98456002227805428</v>
       </c>
       <c r="AB23">
-        <v>329.04892718540373</v>
+        <v>283.06625823567157</v>
       </c>
       <c r="AD23" t="s">
         <v>413</v>
@@ -10135,13 +10135,13 @@
         <v>751</v>
       </c>
       <c r="AN23" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="AO23">
-        <v>0.98933138074259364</v>
+        <v>0.97821870369907904</v>
       </c>
       <c r="AP23">
-        <v>195.59135305245039</v>
+        <v>399.32376551688469</v>
       </c>
       <c r="AR23" t="s">
         <v>413</v>
@@ -10168,16 +10168,16 @@
         <v>836</v>
       </c>
       <c r="BA23" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="BB23" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="BC23">
-        <v>0.96271559874449242</v>
+        <v>0.97048325247055856</v>
       </c>
       <c r="BD23">
-        <v>683.54735635097268</v>
+        <v>541.14037137309333</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10242,16 +10242,16 @@
         <v>442</v>
       </c>
       <c r="Y24" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="Z24" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AA24">
-        <v>0.99142494197358011</v>
+        <v>0.98915672308345548</v>
       </c>
       <c r="AB24">
-        <v>157.20939715103142</v>
+        <v>198.79341013664933</v>
       </c>
       <c r="AD24" t="s">
         <v>413</v>
@@ -10281,13 +10281,13 @@
         <v>752</v>
       </c>
       <c r="AN24" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="AO24">
-        <v>0.98703324072992327</v>
+        <v>0.98830156477913722</v>
       </c>
       <c r="AP24">
-        <v>237.72391995140771</v>
+        <v>214.47131238248457</v>
       </c>
       <c r="AR24" t="s">
         <v>413</v>
@@ -10314,16 +10314,16 @@
         <v>838</v>
       </c>
       <c r="BA24" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="BB24" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="BC24">
-        <v>0.97945251828158475</v>
+        <v>0.96692898910976954</v>
       </c>
       <c r="BD24">
-        <v>376.70383150428029</v>
+        <v>606.30186632089146</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10388,16 +10388,16 @@
         <v>444</v>
       </c>
       <c r="Y25" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="Z25" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AA25">
-        <v>0.9807975141504387</v>
+        <v>0.98436057808473831</v>
       </c>
       <c r="AB25">
-        <v>352.04557390862351</v>
+        <v>286.72273511313136</v>
       </c>
       <c r="AD25" t="s">
         <v>413</v>
@@ -10430,10 +10430,10 @@
         <v>586</v>
       </c>
       <c r="AO25">
-        <v>0.98653333840245183</v>
+        <v>0.99112984822979389</v>
       </c>
       <c r="AP25">
-        <v>246.88879595504923</v>
+        <v>162.61944912044567</v>
       </c>
       <c r="AR25" t="s">
         <v>413</v>
@@ -10460,16 +10460,16 @@
         <v>840</v>
       </c>
       <c r="BA25" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="BB25" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="BC25">
-        <v>0.96683718298551269</v>
+        <v>0.97481390334887996</v>
       </c>
       <c r="BD25">
-        <v>607.98497859893303</v>
+        <v>461.74510527053314</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10534,16 +10534,16 @@
         <v>446</v>
       </c>
       <c r="Y26" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="Z26" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AA26">
-        <v>0.98596629583708084</v>
+        <v>0.99132783885824616</v>
       </c>
       <c r="AB26">
-        <v>257.28457632018387</v>
+        <v>158.989620932154</v>
       </c>
       <c r="AD26" t="s">
         <v>413</v>
@@ -10573,13 +10573,13 @@
         <v>754</v>
       </c>
       <c r="AN26" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="AO26">
-        <v>0.96800325464323944</v>
+        <v>0.99054353037519915</v>
       </c>
       <c r="AP26">
-        <v>586.60699820727632</v>
+        <v>173.36860978801644</v>
       </c>
       <c r="AR26" t="s">
         <v>413</v>
@@ -10606,16 +10606,16 @@
         <v>842</v>
       </c>
       <c r="BA26" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="BB26" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="BC26">
-        <v>0.96781631663497858</v>
+        <v>0.96683718298551269</v>
       </c>
       <c r="BD26">
-        <v>590.03419502539236</v>
+        <v>607.98497859893303</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10680,16 +10680,16 @@
         <v>448</v>
       </c>
       <c r="Y27" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="Z27" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="AA27">
-        <v>0.99365868734102913</v>
+        <v>0.98031356085023202</v>
       </c>
       <c r="AB27">
-        <v>116.25739874780012</v>
+        <v>360.91805107908004</v>
       </c>
       <c r="AD27" t="s">
         <v>413</v>
@@ -10719,13 +10719,13 @@
         <v>755</v>
       </c>
       <c r="AN27" t="s">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="AO27">
-        <v>0.99009266720704037</v>
+        <v>0.9768934332867476</v>
       </c>
       <c r="AP27">
-        <v>181.63443453759336</v>
+        <v>423.6203897429599</v>
       </c>
       <c r="AR27" t="s">
         <v>413</v>
@@ -10752,16 +10752,16 @@
         <v>844</v>
       </c>
       <c r="BA27" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="BB27" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="BC27">
-        <v>0.96139268083002405</v>
+        <v>0.96781631663497858</v>
       </c>
       <c r="BD27">
-        <v>707.80085144956001</v>
+        <v>590.03419502539236</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10826,16 +10826,16 @@
         <v>450</v>
       </c>
       <c r="Y28" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="Z28" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="AA28">
-        <v>0.98564262027093064</v>
+        <v>0.97974172455321451</v>
       </c>
       <c r="AB28">
-        <v>263.21862836627207</v>
+        <v>371.40171652440046</v>
       </c>
       <c r="AD28" t="s">
         <v>413</v>
@@ -10865,13 +10865,13 @@
         <v>756</v>
       </c>
       <c r="AN28" t="s">
-        <v>600</v>
+        <v>757</v>
       </c>
       <c r="AO28">
-        <v>0.98371568181207825</v>
+        <v>0.98045336302656594</v>
       </c>
       <c r="AP28">
-        <v>298.5458334452332</v>
+        <v>358.3550111796236</v>
       </c>
       <c r="AR28" t="s">
         <v>413</v>
@@ -10898,16 +10898,16 @@
         <v>846</v>
       </c>
       <c r="BA28" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="BB28" t="s">
-        <v>878</v>
+        <v>587</v>
       </c>
       <c r="BC28">
-        <v>0.96285001328169728</v>
+        <v>0.98341789520181955</v>
       </c>
       <c r="BD28">
-        <v>681.08308983555014</v>
+        <v>304.0052546333078</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10972,16 +10972,16 @@
         <v>452</v>
       </c>
       <c r="Y29" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z29" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="AA29">
-        <v>0.99296984942213296</v>
+        <v>0.98815787487536866</v>
       </c>
       <c r="AB29">
-        <v>128.88609392756314</v>
+        <v>217.10562728490754</v>
       </c>
       <c r="AD29" t="s">
         <v>413</v>
@@ -11008,16 +11008,16 @@
         <v>639</v>
       </c>
       <c r="AM29" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AN29" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="AO29">
-        <v>0.98435286039872183</v>
+        <v>0.98832832974245843</v>
       </c>
       <c r="AP29">
-        <v>286.8642260234331</v>
+        <v>213.98062138826123</v>
       </c>
       <c r="AR29" t="s">
         <v>413</v>
@@ -11118,16 +11118,16 @@
         <v>454</v>
       </c>
       <c r="Y30" t="s">
-        <v>411</v>
+        <v>348</v>
       </c>
       <c r="Z30" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AA30">
-        <v>0.99062084979042209</v>
+        <v>0.98338655524515672</v>
       </c>
       <c r="AB30">
-        <v>171.95108717559444</v>
+        <v>304.57982050546099</v>
       </c>
       <c r="AD30" t="s">
         <v>413</v>
@@ -11154,16 +11154,16 @@
         <v>641</v>
       </c>
       <c r="AM30" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AN30" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="AO30">
-        <v>0.97655782887090981</v>
+        <v>0.98934334912020028</v>
       </c>
       <c r="AP30">
-        <v>429.77313736665354</v>
+        <v>195.37193279632865</v>
       </c>
       <c r="AR30" t="s">
         <v>413</v>
@@ -11196,10 +11196,10 @@
         <v>574</v>
       </c>
       <c r="BC30">
-        <v>0.97443086368153087</v>
+        <v>0.96884606421228714</v>
       </c>
       <c r="BD30">
-        <v>468.76749917193416</v>
+        <v>571.15548944140187</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11264,16 +11264,16 @@
         <v>456</v>
       </c>
       <c r="Y31" t="s">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="Z31" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AA31">
-        <v>0.98254903847705999</v>
+        <v>0.97813651992719985</v>
       </c>
       <c r="AB31">
-        <v>319.93429458723335</v>
+        <v>400.83046800133633</v>
       </c>
       <c r="AD31" t="s">
         <v>413</v>
@@ -11300,16 +11300,16 @@
         <v>643</v>
       </c>
       <c r="AM31" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AN31" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="AO31">
-        <v>0.98583529483105414</v>
+        <v>0.99072024613784004</v>
       </c>
       <c r="AP31">
-        <v>259.6862614306732</v>
+        <v>170.12882080626682</v>
       </c>
       <c r="AR31" t="s">
         <v>413</v>
@@ -11339,13 +11339,13 @@
         <v>881</v>
       </c>
       <c r="BB31" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="BC31">
-        <v>0.97367031900560153</v>
+        <v>0.97158773589553182</v>
       </c>
       <c r="BD31">
-        <v>482.71081823063838</v>
+        <v>520.89150858191567</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11410,16 +11410,16 @@
         <v>458</v>
       </c>
       <c r="Y32" t="s">
-        <v>341</v>
+        <v>411</v>
       </c>
       <c r="Z32" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="AA32">
-        <v>0.97646711233585171</v>
+        <v>0.99062084979042209</v>
       </c>
       <c r="AB32">
-        <v>431.43627384271826</v>
+        <v>171.95108717559444</v>
       </c>
       <c r="AD32" t="s">
         <v>413</v>
@@ -11446,16 +11446,16 @@
         <v>645</v>
       </c>
       <c r="AM32" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AN32" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="AO32">
-        <v>0.97176508181545596</v>
+        <v>0.97416703287609641</v>
       </c>
       <c r="AP32">
-        <v>517.64016671664035</v>
+        <v>473.6043972715658</v>
       </c>
       <c r="AR32" t="s">
         <v>413</v>
@@ -11485,13 +11485,13 @@
         <v>882</v>
       </c>
       <c r="BB32" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="BC32">
-        <v>0.98427567578715769</v>
+        <v>0.96837970323216338</v>
       </c>
       <c r="BD32">
-        <v>288.27927723544332</v>
+        <v>579.70544074367149</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11556,16 +11556,16 @@
         <v>460</v>
       </c>
       <c r="Y33" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="Z33" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AA33">
-        <v>0.9863634971037446</v>
+        <v>0.98254903847705999</v>
       </c>
       <c r="AB33">
-        <v>250.00255309801472</v>
+        <v>319.93429458723335</v>
       </c>
       <c r="AD33" t="s">
         <v>413</v>
@@ -11592,16 +11592,16 @@
         <v>647</v>
       </c>
       <c r="AM33" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AN33" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="AO33">
-        <v>0.99168257517392877</v>
+        <v>0.97182188871578934</v>
       </c>
       <c r="AP33">
-        <v>152.48612181130682</v>
+        <v>516.59870687719467</v>
       </c>
       <c r="AR33" t="s">
         <v>413</v>
@@ -11631,13 +11631,13 @@
         <v>883</v>
       </c>
       <c r="BB33" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="BC33">
-        <v>0.97204337209146163</v>
+        <v>0.97443086368153087</v>
       </c>
       <c r="BD33">
-        <v>512.53817832320431</v>
+        <v>468.76749917193416</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11702,16 +11702,16 @@
         <v>462</v>
       </c>
       <c r="Y34" t="s">
-        <v>384</v>
+        <v>341</v>
       </c>
       <c r="Z34" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="AA34">
-        <v>0.98024768078410096</v>
+        <v>0.97646711233585171</v>
       </c>
       <c r="AB34">
-        <v>362.12585229148283</v>
+        <v>431.43627384271826</v>
       </c>
       <c r="AD34" t="s">
         <v>413</v>
@@ -11738,16 +11738,16 @@
         <v>649</v>
       </c>
       <c r="AM34" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AN34" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="AO34">
-        <v>0.97961567568507724</v>
+        <v>0.97902953573897011</v>
       </c>
       <c r="AP34">
-        <v>373.71261244025072</v>
+        <v>384.45851145221434</v>
       </c>
       <c r="AR34" t="s">
         <v>413</v>
@@ -11777,13 +11777,13 @@
         <v>884</v>
       </c>
       <c r="BB34" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="BC34">
-        <v>0.97090678081281612</v>
+        <v>0.97367031900560153</v>
       </c>
       <c r="BD34">
-        <v>533.37568509837058</v>
+        <v>482.71081823063838</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11848,16 +11848,16 @@
         <v>464</v>
       </c>
       <c r="Y35" t="s">
-        <v>335</v>
+        <v>397</v>
       </c>
       <c r="Z35" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="AA35">
-        <v>0.98443531955055918</v>
+        <v>0.9863634971037446</v>
       </c>
       <c r="AB35">
-        <v>285.35247490641569</v>
+        <v>250.00255309801472</v>
       </c>
       <c r="AD35" t="s">
         <v>413</v>
@@ -11884,16 +11884,16 @@
         <v>651</v>
       </c>
       <c r="AM35" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AN35" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="AO35">
-        <v>0.98039873263051136</v>
+        <v>0.97567317785568242</v>
       </c>
       <c r="AP35">
-        <v>359.35656844062476</v>
+        <v>445.99173931248959</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11958,16 +11958,16 @@
         <v>466</v>
       </c>
       <c r="Y36" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="Z36" t="s">
         <v>589</v>
       </c>
       <c r="AA36">
-        <v>0.97398849158227818</v>
+        <v>0.98024768078410096</v>
       </c>
       <c r="AB36">
-        <v>476.87765432490079</v>
+        <v>362.12585229148283</v>
       </c>
       <c r="AD36" t="s">
         <v>413</v>
@@ -11994,16 +11994,16 @@
         <v>653</v>
       </c>
       <c r="AM36" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AN36" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AO36">
-        <v>0.98326547324039271</v>
+        <v>0.99568797339637038</v>
       </c>
       <c r="AP36">
-        <v>306.79965725946761</v>
+        <v>79.053821066542412</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12068,16 +12068,16 @@
         <v>468</v>
       </c>
       <c r="Y37" t="s">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="Z37" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="AA37">
-        <v>0.98814122429339546</v>
+        <v>0.99395293926735107</v>
       </c>
       <c r="AB37">
-        <v>217.4108879544159</v>
+        <v>110.86278009856306</v>
       </c>
       <c r="AD37" t="s">
         <v>413</v>
@@ -12104,16 +12104,16 @@
         <v>655</v>
       </c>
       <c r="AM37" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AN37" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AO37">
-        <v>0.98997462954848647</v>
+        <v>0.9918951652662058</v>
       </c>
       <c r="AP37">
-        <v>183.79845827774895</v>
+        <v>148.58863678622743</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12178,16 +12178,16 @@
         <v>470</v>
       </c>
       <c r="Y38" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="Z38" t="s">
         <v>590</v>
       </c>
       <c r="AA38">
-        <v>0.97065607524213282</v>
+        <v>0.98304303411255212</v>
       </c>
       <c r="AB38">
-        <v>537.97195389423189</v>
+        <v>310.87770793654443</v>
       </c>
       <c r="AD38" t="s">
         <v>413</v>
@@ -12214,16 +12214,16 @@
         <v>657</v>
       </c>
       <c r="AM38" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AN38" t="s">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="AO38">
-        <v>0.98425147469462704</v>
+        <v>0.98531999116946412</v>
       </c>
       <c r="AP38">
-        <v>288.72296393183791</v>
+        <v>269.13349522649082</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12288,16 +12288,16 @@
         <v>472</v>
       </c>
       <c r="Y39" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="Z39" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="AA39">
-        <v>0.97916314637278834</v>
+        <v>0.9902907805210438</v>
       </c>
       <c r="AB39">
-        <v>382.00898316554651</v>
+        <v>178.00235711419791</v>
       </c>
       <c r="AD39" t="s">
         <v>413</v>
@@ -12324,16 +12324,16 @@
         <v>659</v>
       </c>
       <c r="AM39" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AN39" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="AO39">
-        <v>0.97434541537281683</v>
+        <v>0.98879946679477992</v>
       </c>
       <c r="AP39">
-        <v>470.33405149835795</v>
+        <v>205.34310876236799</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12398,16 +12398,16 @@
         <v>474</v>
       </c>
       <c r="Y40" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="Z40" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="AA40">
-        <v>0.97970789283404214</v>
+        <v>0.99409930001823366</v>
       </c>
       <c r="AB40">
-        <v>372.02196470922701</v>
+        <v>108.17949966571678</v>
       </c>
       <c r="AD40" t="s">
         <v>413</v>
@@ -12434,16 +12434,16 @@
         <v>661</v>
       </c>
       <c r="AM40" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AN40" t="s">
-        <v>769</v>
+        <v>574</v>
       </c>
       <c r="AO40">
-        <v>0.98430775783289481</v>
+        <v>0.98121294780398804</v>
       </c>
       <c r="AP40">
-        <v>287.69110639692803</v>
+        <v>344.42929026021937</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12508,16 +12508,16 @@
         <v>476</v>
       </c>
       <c r="Y41" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="Z41" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="AA41">
-        <v>0.98270299973748321</v>
+        <v>0.99045315399849054</v>
       </c>
       <c r="AB41">
-        <v>317.11167147947373</v>
+        <v>175.02551002767362</v>
       </c>
       <c r="AD41" t="s">
         <v>413</v>
@@ -12547,13 +12547,13 @@
         <v>770</v>
       </c>
       <c r="AN41" t="s">
-        <v>579</v>
+        <v>771</v>
       </c>
       <c r="AO41">
-        <v>0.97444364094885727</v>
+        <v>0.97759288697657265</v>
       </c>
       <c r="AP41">
-        <v>468.53324927094968</v>
+        <v>410.79707209616811</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12618,16 +12618,16 @@
         <v>478</v>
       </c>
       <c r="Y42" t="s">
-        <v>383</v>
+        <v>334</v>
       </c>
       <c r="Z42" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="AA42">
-        <v>0.97598085885692565</v>
+        <v>0.99382288375189876</v>
       </c>
       <c r="AB42">
-        <v>440.3509209563627</v>
+        <v>113.24713121519014</v>
       </c>
       <c r="AD42" t="s">
         <v>413</v>
@@ -12654,16 +12654,16 @@
         <v>665</v>
       </c>
       <c r="AM42" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AN42" t="s">
         <v>586</v>
       </c>
       <c r="AO42">
-        <v>0.98574603285635165</v>
+        <v>0.97393752600115946</v>
       </c>
       <c r="AP42">
-        <v>261.32273096688704</v>
+        <v>477.81202331207646</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12728,16 +12728,16 @@
         <v>480</v>
       </c>
       <c r="Y43" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="Z43" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AA43">
-        <v>0.98338655524515672</v>
+        <v>0.97000043567738925</v>
       </c>
       <c r="AB43">
-        <v>304.57982050546099</v>
+        <v>549.99201258119717</v>
       </c>
       <c r="AD43" t="s">
         <v>413</v>
@@ -12764,16 +12764,16 @@
         <v>667</v>
       </c>
       <c r="AM43" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AN43" t="s">
-        <v>773</v>
+        <v>599</v>
       </c>
       <c r="AO43">
-        <v>0.97968688829580564</v>
+        <v>0.98893828971746323</v>
       </c>
       <c r="AP43">
-        <v>372.40704791023012</v>
+        <v>202.7980218465068</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12838,16 +12838,16 @@
         <v>482</v>
       </c>
       <c r="Y44" t="s">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="Z44" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AA44">
-        <v>0.97813651992719985</v>
+        <v>0.98823937652699512</v>
       </c>
       <c r="AB44">
-        <v>400.83046800133633</v>
+        <v>215.61143033842296</v>
       </c>
       <c r="AD44" t="s">
         <v>413</v>
@@ -12877,13 +12877,13 @@
         <v>774</v>
       </c>
       <c r="AN44" t="s">
-        <v>580</v>
+        <v>775</v>
       </c>
       <c r="AO44">
-        <v>0.98420825457429406</v>
+        <v>0.97223070787085453</v>
       </c>
       <c r="AP44">
-        <v>289.51533280460853</v>
+        <v>509.10368903433471</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12948,16 +12948,16 @@
         <v>484</v>
       </c>
       <c r="Y45" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="Z45" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="AA45">
-        <v>0.98042255120792365</v>
+        <v>0.97307234437114887</v>
       </c>
       <c r="AB45">
-        <v>358.91989452139876</v>
+        <v>493.6736865289368</v>
       </c>
       <c r="AD45" t="s">
         <v>413</v>
@@ -12984,16 +12984,16 @@
         <v>671</v>
       </c>
       <c r="AM45" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AN45" t="s">
-        <v>593</v>
+        <v>777</v>
       </c>
       <c r="AO45">
-        <v>0.98302364254854535</v>
+        <v>0.99323428174300499</v>
       </c>
       <c r="AP45">
-        <v>311.23321994333526</v>
+        <v>124.03816804490805</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13058,16 +13058,16 @@
         <v>486</v>
       </c>
       <c r="Y46" t="s">
-        <v>343</v>
+        <v>398</v>
       </c>
       <c r="Z46" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
       <c r="AA46">
-        <v>0.98981198518654634</v>
+        <v>0.97831141720185744</v>
       </c>
       <c r="AB46">
-        <v>186.78027157998449</v>
+        <v>397.62401796594617</v>
       </c>
       <c r="AD46" t="s">
         <v>413</v>
@@ -13094,16 +13094,16 @@
         <v>673</v>
       </c>
       <c r="AM46" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="AN46" t="s">
-        <v>600</v>
+        <v>779</v>
       </c>
       <c r="AO46">
-        <v>0.99054353037519915</v>
+        <v>0.97340237375196048</v>
       </c>
       <c r="AP46">
-        <v>173.36860978801644</v>
+        <v>487.62314788072359</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13168,16 +13168,16 @@
         <v>488</v>
       </c>
       <c r="Y47" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z47" t="s">
         <v>594</v>
       </c>
       <c r="AA47">
-        <v>0.97580984429062223</v>
+        <v>0.9753018595470957</v>
       </c>
       <c r="AB47">
-        <v>443.48618800525958</v>
+        <v>452.79924163657859</v>
       </c>
       <c r="AD47" t="s">
         <v>413</v>
@@ -13204,16 +13204,16 @@
         <v>675</v>
       </c>
       <c r="AM47" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="AN47" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="AO47">
-        <v>0.9768934332867476</v>
+        <v>0.98709698070191276</v>
       </c>
       <c r="AP47">
-        <v>423.6203897429599</v>
+        <v>236.55535379826514</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13278,16 +13278,16 @@
         <v>490</v>
       </c>
       <c r="Y48" t="s">
-        <v>403</v>
+        <v>368</v>
       </c>
       <c r="Z48" t="s">
-        <v>595</v>
+        <v>576</v>
       </c>
       <c r="AA48">
-        <v>0.98738988106093839</v>
+        <v>0.98694170150784422</v>
       </c>
       <c r="AB48">
-        <v>231.18551388279656</v>
+        <v>239.40213902285669</v>
       </c>
       <c r="AD48" t="s">
         <v>413</v>
@@ -13314,16 +13314,16 @@
         <v>677</v>
       </c>
       <c r="AM48" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="AN48" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="AO48">
-        <v>0.97567317785568242</v>
+        <v>0.97913435966240669</v>
       </c>
       <c r="AP48">
-        <v>445.99173931248959</v>
+        <v>382.53673952254371</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13388,16 +13388,16 @@
         <v>492</v>
       </c>
       <c r="Y49" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="Z49" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="AA49">
-        <v>0.97723778280633045</v>
+        <v>0.98336988732579877</v>
       </c>
       <c r="AB49">
-        <v>417.30731521727455</v>
+        <v>304.88539902702166</v>
       </c>
       <c r="AD49" t="s">
         <v>413</v>
@@ -13424,16 +13424,16 @@
         <v>679</v>
       </c>
       <c r="AM49" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="AN49" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="AO49">
-        <v>0.99568797339637038</v>
+        <v>0.98238877493134946</v>
       </c>
       <c r="AP49">
-        <v>79.053821066542412</v>
+        <v>322.87245959192745</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13498,16 +13498,16 @@
         <v>494</v>
       </c>
       <c r="Y50" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="Z50" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="AA50">
-        <v>0.99035601519017957</v>
+        <v>0.98042255120792365</v>
       </c>
       <c r="AB50">
-        <v>176.80638818004016</v>
+        <v>358.91989452139876</v>
       </c>
       <c r="AD50" t="s">
         <v>413</v>
@@ -13534,16 +13534,16 @@
         <v>681</v>
       </c>
       <c r="AM50" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="AN50" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="AO50">
-        <v>0.9918951652662058</v>
+        <v>0.98644744628709446</v>
       </c>
       <c r="AP50">
-        <v>148.58863678622743</v>
+        <v>248.46348473660174</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13608,16 +13608,16 @@
         <v>496</v>
       </c>
       <c r="Y51" t="s">
-        <v>393</v>
+        <v>343</v>
       </c>
       <c r="Z51" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AA51">
-        <v>0.97545857121381951</v>
+        <v>0.98981198518654634</v>
       </c>
       <c r="AB51">
-        <v>449.92619441330908</v>
+        <v>186.78027157998449</v>
       </c>
       <c r="AD51" t="s">
         <v>413</v>
@@ -13644,16 +13644,16 @@
         <v>683</v>
       </c>
       <c r="AM51" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="AN51" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="AO51">
-        <v>0.98531999116946412</v>
+        <v>0.98967580974453273</v>
       </c>
       <c r="AP51">
-        <v>269.13349522649082</v>
+        <v>189.27682135023403</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13718,16 +13718,16 @@
         <v>498</v>
       </c>
       <c r="Y52" t="s">
-        <v>409</v>
+        <v>351</v>
       </c>
       <c r="Z52" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AA52">
-        <v>0.98212250728249206</v>
+        <v>0.97580984429062223</v>
       </c>
       <c r="AB52">
-        <v>327.75403315431197</v>
+        <v>443.48618800525958</v>
       </c>
       <c r="AD52" t="s">
         <v>413</v>
@@ -13754,16 +13754,16 @@
         <v>685</v>
       </c>
       <c r="AM52" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="AN52" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO52">
-        <v>0.98689046040235784</v>
+        <v>0.98562083412131529</v>
       </c>
       <c r="AP52">
-        <v>240.34155929010652</v>
+        <v>263.61804110921923</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13828,16 +13828,16 @@
         <v>500</v>
       </c>
       <c r="Y53" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="Z53" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="AA53">
-        <v>0.99456410459052502</v>
+        <v>0.98738988106093839</v>
       </c>
       <c r="AB53">
-        <v>99.658082507040461</v>
+        <v>231.18551388279656</v>
       </c>
       <c r="AD53" t="s">
         <v>413</v>
@@ -13864,16 +13864,16 @@
         <v>687</v>
       </c>
       <c r="AM53" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="AN53" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="AO53">
-        <v>0.97821870369907904</v>
+        <v>0.9802768549486589</v>
       </c>
       <c r="AP53">
-        <v>399.32376551688469</v>
+        <v>361.5909926079201</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -13938,16 +13938,16 @@
         <v>502</v>
       </c>
       <c r="Y54" t="s">
-        <v>344</v>
+        <v>381</v>
       </c>
       <c r="Z54" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AA54">
-        <v>0.97891429500574301</v>
+        <v>0.97723778280633045</v>
       </c>
       <c r="AB54">
-        <v>386.57125822804534</v>
+        <v>417.30731521727455</v>
       </c>
       <c r="AD54" t="s">
         <v>413</v>
@@ -13974,16 +13974,16 @@
         <v>689</v>
       </c>
       <c r="AM54" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="AN54" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="AO54">
-        <v>0.98830156477913722</v>
+        <v>0.97414990055259076</v>
       </c>
       <c r="AP54">
-        <v>214.47131238248457</v>
+        <v>473.91848986916989</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -14048,16 +14048,16 @@
         <v>504</v>
       </c>
       <c r="Y55" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="Z55" t="s">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="AA55">
-        <v>0.99086247853214549</v>
+        <v>0.99035601519017957</v>
       </c>
       <c r="AB55">
-        <v>167.52122691066626</v>
+        <v>176.80638818004016</v>
       </c>
       <c r="AD55" t="s">
         <v>413</v>
@@ -14084,16 +14084,16 @@
         <v>691</v>
       </c>
       <c r="AM55" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="AN55" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AO55">
-        <v>0.99112984822979389</v>
+        <v>0.98705643087911032</v>
       </c>
       <c r="AP55">
-        <v>162.61944912044567</v>
+        <v>237.29876721631038</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14158,16 +14158,16 @@
         <v>506</v>
       </c>
       <c r="Y56" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="Z56" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="AA56">
-        <v>0.9839124944774571</v>
+        <v>0.97545857121381951</v>
       </c>
       <c r="AB56">
-        <v>294.93760124661941</v>
+        <v>449.92619441330908</v>
       </c>
       <c r="AD56" t="s">
         <v>413</v>
@@ -14194,16 +14194,16 @@
         <v>693</v>
       </c>
       <c r="AM56" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="AN56" t="s">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="AO56">
-        <v>0.9802768549486589</v>
+        <v>0.98989284585574766</v>
       </c>
       <c r="AP56">
-        <v>361.5909926079201</v>
+        <v>185.29782597795898</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14268,16 +14268,16 @@
         <v>508</v>
       </c>
       <c r="Y57" t="s">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="Z57" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="AA57">
-        <v>0.97678875799905829</v>
+        <v>0.98212250728249206</v>
       </c>
       <c r="AB57">
-        <v>425.5394366839318</v>
+        <v>327.75403315431197</v>
       </c>
       <c r="AD57" t="s">
         <v>413</v>
@@ -14304,16 +14304,16 @@
         <v>695</v>
       </c>
       <c r="AM57" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="AN57" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="AO57">
-        <v>0.97414990055259076</v>
+        <v>0.99009266720704037</v>
       </c>
       <c r="AP57">
-        <v>473.91848986916989</v>
+        <v>181.63443453759336</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14378,16 +14378,16 @@
         <v>510</v>
       </c>
       <c r="Y58" t="s">
-        <v>410</v>
+        <v>350</v>
       </c>
       <c r="Z58" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="AA58">
-        <v>0.99395293926735107</v>
+        <v>0.99456410459052502</v>
       </c>
       <c r="AB58">
-        <v>110.86278009856306</v>
+        <v>99.658082507040461</v>
       </c>
       <c r="AD58" t="s">
         <v>413</v>
@@ -14414,16 +14414,16 @@
         <v>697</v>
       </c>
       <c r="AM58" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="AN58" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="AO58">
-        <v>0.98705643087911032</v>
+        <v>0.98371568181207825</v>
       </c>
       <c r="AP58">
-        <v>237.29876721631038</v>
+        <v>298.5458334452332</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14488,16 +14488,16 @@
         <v>512</v>
       </c>
       <c r="Y59" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="Z59" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="AA59">
-        <v>0.98304303411255212</v>
+        <v>0.97891429500574301</v>
       </c>
       <c r="AB59">
-        <v>310.87770793654443</v>
+        <v>386.57125822804534</v>
       </c>
       <c r="AD59" t="s">
         <v>413</v>
@@ -14524,16 +14524,16 @@
         <v>699</v>
       </c>
       <c r="AM59" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="AN59" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO59">
-        <v>0.98989284585574766</v>
+        <v>0.98435286039872183</v>
       </c>
       <c r="AP59">
-        <v>185.29782597795898</v>
+        <v>286.8642260234331</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14598,16 +14598,16 @@
         <v>514</v>
       </c>
       <c r="Y60" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Z60" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA60">
-        <v>0.9902907805210438</v>
+        <v>0.99086247853214549</v>
       </c>
       <c r="AB60">
-        <v>178.00235711419791</v>
+        <v>167.52122691066626</v>
       </c>
       <c r="AD60" t="s">
         <v>413</v>
@@ -14634,16 +14634,16 @@
         <v>701</v>
       </c>
       <c r="AM60" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="AN60" t="s">
-        <v>577</v>
+        <v>600</v>
       </c>
       <c r="AO60">
-        <v>0.98238877493134946</v>
+        <v>0.97655782887090981</v>
       </c>
       <c r="AP60">
-        <v>322.87245959192745</v>
+        <v>429.77313736665354</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14708,16 +14708,16 @@
         <v>516</v>
       </c>
       <c r="Y61" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="Z61" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="AA61">
-        <v>0.97272179131491798</v>
+        <v>0.9839124944774571</v>
       </c>
       <c r="AB61">
-        <v>500.10049255983796</v>
+        <v>294.93760124661941</v>
       </c>
       <c r="AD61" t="s">
         <v>413</v>
@@ -14744,16 +14744,16 @@
         <v>703</v>
       </c>
       <c r="AM61" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="AN61" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="AO61">
-        <v>0.98644744628709446</v>
+        <v>0.99417752457368125</v>
       </c>
       <c r="AP61">
-        <v>248.46348473660174</v>
+        <v>106.74538281584397</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14818,16 +14818,16 @@
         <v>518</v>
       </c>
       <c r="Y62" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="Z62" t="s">
-        <v>598</v>
+        <v>577</v>
       </c>
       <c r="AA62">
-        <v>0.98444284858889564</v>
+        <v>0.97678875799905829</v>
       </c>
       <c r="AB62">
-        <v>285.21444253691413</v>
+        <v>425.5394366839318</v>
       </c>
       <c r="AD62" t="s">
         <v>413</v>
@@ -14854,16 +14854,16 @@
         <v>705</v>
       </c>
       <c r="AM62" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="AN62" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AO62">
-        <v>0.98967580974453273</v>
+        <v>0.98213512486164511</v>
       </c>
       <c r="AP62">
-        <v>189.27682135023403</v>
+        <v>327.5227108698395</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14928,16 +14928,16 @@
         <v>520</v>
       </c>
       <c r="Y63" t="s">
-        <v>360</v>
+        <v>406</v>
       </c>
       <c r="Z63" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="AA63">
-        <v>0.98269942042940017</v>
+        <v>0.99165078812878382</v>
       </c>
       <c r="AB63">
-        <v>317.17729212766454</v>
+        <v>153.06888430562992</v>
       </c>
       <c r="AD63" t="s">
         <v>413</v>
@@ -14964,16 +14964,16 @@
         <v>707</v>
       </c>
       <c r="AM63" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="AN63" t="s">
-        <v>585</v>
+        <v>797</v>
       </c>
       <c r="AO63">
-        <v>0.98562083412131529</v>
+        <v>0.98305809009413248</v>
       </c>
       <c r="AP63">
-        <v>263.61804110921923</v>
+        <v>310.60168160757155</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -15038,16 +15038,16 @@
         <v>522</v>
       </c>
       <c r="Y64" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="Z64" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA64">
-        <v>0.98213943337265219</v>
+        <v>0.97646479583958734</v>
       </c>
       <c r="AB64">
-        <v>327.44372150137696</v>
+        <v>431.47874294089837</v>
       </c>
       <c r="AD64" t="s">
         <v>413</v>
@@ -15074,16 +15074,16 @@
         <v>709</v>
       </c>
       <c r="AM64" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="AN64" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="AO64">
-        <v>0.98003745158806088</v>
+        <v>0.99584474408886259</v>
       </c>
       <c r="AP64">
-        <v>365.98005421888422</v>
+        <v>76.179691704186226</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -15148,16 +15148,16 @@
         <v>524</v>
       </c>
       <c r="Y65" t="s">
-        <v>337</v>
+        <v>372</v>
       </c>
       <c r="Z65" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AA65">
-        <v>0.98823937652699512</v>
+        <v>0.96562135615554268</v>
       </c>
       <c r="AB65">
-        <v>215.61143033842296</v>
+        <v>630.27513714838358</v>
       </c>
       <c r="AD65" t="s">
         <v>413</v>
@@ -15184,16 +15184,16 @@
         <v>711</v>
       </c>
       <c r="AM65" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="AN65" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="AO65">
-        <v>0.98867603245018398</v>
+        <v>0.9771067451947747</v>
       </c>
       <c r="AP65">
-        <v>207.60607174662678</v>
+        <v>419.70967142912968</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15258,16 +15258,16 @@
         <v>526</v>
       </c>
       <c r="Y66" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="Z66" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="AA66">
-        <v>0.97307234437114887</v>
+        <v>0.98843111817052332</v>
       </c>
       <c r="AB66">
-        <v>493.6736865289368</v>
+        <v>212.09616687373853</v>
       </c>
       <c r="AD66" t="s">
         <v>413</v>
@@ -15294,16 +15294,16 @@
         <v>713</v>
       </c>
       <c r="AM66" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="AN66" t="s">
-        <v>797</v>
+        <v>600</v>
       </c>
       <c r="AO66">
-        <v>0.97223070787085453</v>
+        <v>0.97431371456908866</v>
       </c>
       <c r="AP66">
-        <v>509.10368903433471</v>
+        <v>470.91523290004181</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15368,16 +15368,16 @@
         <v>528</v>
       </c>
       <c r="Y67" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="Z67" t="s">
-        <v>599</v>
+        <v>574</v>
       </c>
       <c r="AA67">
-        <v>0.97831141720185744</v>
+        <v>0.98055369884714538</v>
       </c>
       <c r="AB67">
-        <v>397.62401796594617</v>
+        <v>356.51552113566873</v>
       </c>
       <c r="AD67" t="s">
         <v>413</v>
@@ -15404,16 +15404,16 @@
         <v>715</v>
       </c>
       <c r="AM67" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="AN67" t="s">
-        <v>799</v>
+        <v>579</v>
       </c>
       <c r="AO67">
-        <v>0.99323428174300499</v>
+        <v>0.97612238282801922</v>
       </c>
       <c r="AP67">
-        <v>124.03816804490805</v>
+        <v>437.75631481964848</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15478,16 +15478,16 @@
         <v>530</v>
       </c>
       <c r="Y68" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="Z68" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="AA68">
-        <v>0.9753018595470957</v>
+        <v>0.99284163372730061</v>
       </c>
       <c r="AB68">
-        <v>452.79924163657859</v>
+        <v>131.23671499948927</v>
       </c>
       <c r="AD68" t="s">
         <v>413</v>
@@ -15514,16 +15514,16 @@
         <v>717</v>
       </c>
       <c r="AM68" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AN68" t="s">
-        <v>801</v>
+        <v>580</v>
       </c>
       <c r="AO68">
-        <v>0.97340237375196048</v>
+        <v>0.98933138074259364</v>
       </c>
       <c r="AP68">
-        <v>487.62314788072359</v>
+        <v>195.59135305245039</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -15588,16 +15588,16 @@
         <v>532</v>
       </c>
       <c r="Y69" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="Z69" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AA69">
-        <v>0.98694170150784422</v>
+        <v>0.980949293282396</v>
       </c>
       <c r="AB69">
-        <v>239.40213902285669</v>
+        <v>349.26295648940771</v>
       </c>
       <c r="AD69" t="s">
         <v>413</v>
@@ -15624,16 +15624,16 @@
         <v>719</v>
       </c>
       <c r="AM69" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AN69" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="AO69">
-        <v>0.98709698070191276</v>
+        <v>0.98703324072992327</v>
       </c>
       <c r="AP69">
-        <v>236.55535379826514</v>
+        <v>237.72391995140771</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -15698,16 +15698,16 @@
         <v>534</v>
       </c>
       <c r="Y70" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="Z70" t="s">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="AA70">
-        <v>0.98336988732579877</v>
+        <v>0.98440429555001041</v>
       </c>
       <c r="AB70">
-        <v>304.88539902702166</v>
+        <v>285.92124824980857</v>
       </c>
       <c r="AD70" t="s">
         <v>413</v>
@@ -15734,16 +15734,16 @@
         <v>721</v>
       </c>
       <c r="AM70" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AN70" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="AO70">
-        <v>0.97913435966240669</v>
+        <v>0.98653333840245183</v>
       </c>
       <c r="AP70">
-        <v>382.53673952254371</v>
+        <v>246.88879595504923</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -15808,16 +15808,16 @@
         <v>536</v>
       </c>
       <c r="Y71" t="s">
-        <v>402</v>
+        <v>357</v>
       </c>
       <c r="Z71" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="AA71">
-        <v>0.99409930001823366</v>
+        <v>0.97996308088186879</v>
       </c>
       <c r="AB71">
-        <v>108.17949966571678</v>
+        <v>367.343517165739</v>
       </c>
       <c r="AD71" t="s">
         <v>413</v>
@@ -15844,16 +15844,16 @@
         <v>723</v>
       </c>
       <c r="AM71" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AN71" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AO71">
-        <v>0.99417752457368125</v>
+        <v>0.96800325464323944</v>
       </c>
       <c r="AP71">
-        <v>106.74538281584397</v>
+        <v>586.60699820727632</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -15918,16 +15918,16 @@
         <v>538</v>
       </c>
       <c r="Y72" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="Z72" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AA72">
-        <v>0.99045315399849054</v>
+        <v>0.97636760270586087</v>
       </c>
       <c r="AB72">
-        <v>175.02551002767362</v>
+        <v>433.26061705921813</v>
       </c>
       <c r="AD72" t="s">
         <v>413</v>
@@ -15954,16 +15954,16 @@
         <v>725</v>
       </c>
       <c r="AM72" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AN72" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AO72">
-        <v>0.98213512486164511</v>
+        <v>0.98003745158806088</v>
       </c>
       <c r="AP72">
-        <v>327.5227108698395</v>
+        <v>365.98005421888422</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16028,16 +16028,16 @@
         <v>540</v>
       </c>
       <c r="Y73" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="Z73" t="s">
-        <v>600</v>
+        <v>574</v>
       </c>
       <c r="AA73">
-        <v>0.99243389564470808</v>
+        <v>0.97272179131491798</v>
       </c>
       <c r="AB73">
-        <v>138.71191318035258</v>
+        <v>500.10049255983796</v>
       </c>
       <c r="AD73" t="s">
         <v>413</v>
@@ -16064,16 +16064,16 @@
         <v>727</v>
       </c>
       <c r="AM73" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AN73" t="s">
-        <v>807</v>
+        <v>580</v>
       </c>
       <c r="AO73">
-        <v>0.98305809009413248</v>
+        <v>0.98867603245018398</v>
       </c>
       <c r="AP73">
-        <v>310.60168160757155</v>
+        <v>207.60607174662678</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -16138,16 +16138,16 @@
         <v>542</v>
       </c>
       <c r="Y74" t="s">
-        <v>404</v>
+        <v>346</v>
       </c>
       <c r="Z74" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="AA74">
-        <v>0.98258925616289594</v>
+        <v>0.98444284858889564</v>
       </c>
       <c r="AB74">
-        <v>319.19697034690739</v>
+        <v>285.21444253691413</v>
       </c>
       <c r="AD74" t="s">
         <v>413</v>
@@ -16177,13 +16177,13 @@
         <v>808</v>
       </c>
       <c r="AN74" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="AO74">
-        <v>0.99584474408886259</v>
+        <v>0.98583529483105414</v>
       </c>
       <c r="AP74">
-        <v>76.179691704186226</v>
+        <v>259.6862614306732</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -16248,16 +16248,16 @@
         <v>544</v>
       </c>
       <c r="Y75" t="s">
-        <v>401</v>
+        <v>360</v>
       </c>
       <c r="Z75" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AA75">
-        <v>0.98625535317143753</v>
+        <v>0.98269942042940017</v>
       </c>
       <c r="AB75">
-        <v>251.98519185697839</v>
+        <v>317.17729212766454</v>
       </c>
       <c r="AD75" t="s">
         <v>413</v>
@@ -16287,13 +16287,13 @@
         <v>809</v>
       </c>
       <c r="AN75" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="AO75">
-        <v>0.9771067451947747</v>
+        <v>0.97176508181545596</v>
       </c>
       <c r="AP75">
-        <v>419.70967142912968</v>
+        <v>517.64016671664035</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -16358,16 +16358,16 @@
         <v>546</v>
       </c>
       <c r="Y76" t="s">
-        <v>405</v>
+        <v>361</v>
       </c>
       <c r="Z76" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="AA76">
-        <v>0.98719346865782154</v>
+        <v>0.98213943337265219</v>
       </c>
       <c r="AB76">
-        <v>234.78640793993935</v>
+        <v>327.44372150137696</v>
       </c>
       <c r="AD76" t="s">
         <v>413</v>
@@ -16397,13 +16397,13 @@
         <v>810</v>
       </c>
       <c r="AN76" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="AO76">
-        <v>0.97431371456908866</v>
+        <v>0.99168257517392877</v>
       </c>
       <c r="AP76">
-        <v>470.91523290004181</v>
+        <v>152.48612181130682</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -16468,16 +16468,16 @@
         <v>548</v>
       </c>
       <c r="Y77" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="Z77" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="AA77">
-        <v>0.97184397355215157</v>
+        <v>0.97970789283404214</v>
       </c>
       <c r="AB77">
-        <v>516.19381821055424</v>
+        <v>372.02196470922701</v>
       </c>
       <c r="AD77" t="s">
         <v>413</v>
@@ -16507,13 +16507,13 @@
         <v>811</v>
       </c>
       <c r="AN77" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="AO77">
-        <v>0.98893828971746323</v>
+        <v>0.97961567568507724</v>
       </c>
       <c r="AP77">
-        <v>202.7980218465068</v>
+        <v>373.71261244025072</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -16578,16 +16578,16 @@
         <v>550</v>
       </c>
       <c r="Y78" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="Z78" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="AA78">
-        <v>0.97870278293688284</v>
+        <v>0.98270299973748321</v>
       </c>
       <c r="AB78">
-        <v>390.44897949048118</v>
+        <v>317.11167147947373</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -16652,16 +16652,16 @@
         <v>552</v>
       </c>
       <c r="Y79" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="Z79" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="AA79">
-        <v>0.98376398069352888</v>
+        <v>0.97598085885692565</v>
       </c>
       <c r="AB79">
-        <v>297.66035395197099</v>
+        <v>440.3509209563627</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -16726,16 +16726,16 @@
         <v>554</v>
       </c>
       <c r="Y80" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="Z80" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="AA80">
-        <v>0.98456002227805428</v>
+        <v>0.97878284543380634</v>
       </c>
       <c r="AB80">
-        <v>283.06625823567157</v>
+        <v>388.98116704688283</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -16800,16 +16800,16 @@
         <v>556</v>
       </c>
       <c r="Y81" t="s">
-        <v>407</v>
+        <v>340</v>
       </c>
       <c r="Z81" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="AA81">
-        <v>0.98915672308345548</v>
+        <v>0.9898744603534384</v>
       </c>
       <c r="AB81">
-        <v>198.79341013664933</v>
+        <v>185.63489352029583</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -16874,16 +16874,16 @@
         <v>558</v>
       </c>
       <c r="Y82" t="s">
-        <v>408</v>
+        <v>336</v>
       </c>
       <c r="Z82" t="s">
-        <v>580</v>
+        <v>602</v>
       </c>
       <c r="AA82">
-        <v>0.98436057808473831</v>
+        <v>0.98205187669897798</v>
       </c>
       <c r="AB82">
-        <v>286.72273511313136</v>
+        <v>329.04892718540373</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -16948,16 +16948,16 @@
         <v>560</v>
       </c>
       <c r="Y83" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Z83" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="AA83">
-        <v>0.99132783885824616</v>
+        <v>0.99142494197358011</v>
       </c>
       <c r="AB83">
-        <v>158.989620932154</v>
+        <v>157.20939715103142</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -17022,16 +17022,16 @@
         <v>562</v>
       </c>
       <c r="Y84" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="Z84" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AA84">
-        <v>0.98031356085023202</v>
+        <v>0.9807975141504387</v>
       </c>
       <c r="AB84">
-        <v>360.91805107908004</v>
+        <v>352.04557390862351</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -17096,16 +17096,16 @@
         <v>564</v>
       </c>
       <c r="Y85" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="Z85" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AA85">
-        <v>0.97974172455321451</v>
+        <v>0.98596629583708084</v>
       </c>
       <c r="AB85">
-        <v>371.40171652440046</v>
+        <v>257.28457632018387</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -17170,16 +17170,16 @@
         <v>566</v>
       </c>
       <c r="Y86" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="Z86" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="AA86">
-        <v>0.98815787487536866</v>
+        <v>0.99365868734102913</v>
       </c>
       <c r="AB86">
-        <v>217.10562728490754</v>
+        <v>116.25739874780012</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -17244,16 +17244,16 @@
         <v>568</v>
       </c>
       <c r="Y87" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="Z87" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AA87">
-        <v>0.99382288375189876</v>
+        <v>0.98564262027093064</v>
       </c>
       <c r="AB87">
-        <v>113.24713121519014</v>
+        <v>263.21862836627207</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -17318,16 +17318,16 @@
         <v>570</v>
       </c>
       <c r="Y88" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="Z88" t="s">
-        <v>602</v>
+        <v>578</v>
       </c>
       <c r="AA88">
-        <v>0.97000043567738925</v>
+        <v>0.99296984942213296</v>
       </c>
       <c r="AB88">
-        <v>549.99201258119717</v>
+        <v>128.88609392756314</v>
       </c>
     </row>
   </sheetData>
@@ -17336,7 +17336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE766A14-EE46-454D-9C9F-5B57C0125935}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{294103D0-7DDA-417C-AECA-0EF0C0D7FA92}">
   <dimension ref="B9:Z77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17448,7 +17448,7 @@
         <v>885</v>
       </c>
       <c r="K11" t="s">
-        <v>767</v>
+        <v>741</v>
       </c>
       <c r="L11">
         <v>29.7146465744454</v>
@@ -17481,7 +17481,7 @@
         <v>1019</v>
       </c>
       <c r="X11" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="Y11">
         <v>0.33825</v>
@@ -17516,7 +17516,7 @@
         <v>887</v>
       </c>
       <c r="K12" t="s">
-        <v>743</v>
+        <v>762</v>
       </c>
       <c r="L12">
         <v>13.367096811591049</v>
@@ -17549,7 +17549,7 @@
         <v>1021</v>
       </c>
       <c r="X12" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="Y12">
         <v>10.88325</v>
@@ -17584,7 +17584,7 @@
         <v>889</v>
       </c>
       <c r="K13" t="s">
-        <v>742</v>
+        <v>761</v>
       </c>
       <c r="L13">
         <v>24.156328337033791</v>
@@ -17617,7 +17617,7 @@
         <v>1023</v>
       </c>
       <c r="X13" t="s">
-        <v>884</v>
+        <v>864</v>
       </c>
       <c r="Y13">
         <v>26.983499999999999</v>
@@ -17652,7 +17652,7 @@
         <v>891</v>
       </c>
       <c r="K14" t="s">
-        <v>811</v>
+        <v>773</v>
       </c>
       <c r="L14">
         <v>16.006796560234815</v>
@@ -17685,7 +17685,7 @@
         <v>1025</v>
       </c>
       <c r="X14" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="Y14">
         <v>42.507750000000001</v>
@@ -17720,7 +17720,7 @@
         <v>893</v>
       </c>
       <c r="K15" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
       <c r="L15">
         <v>17.682358378036344</v>
@@ -17753,7 +17753,7 @@
         <v>1027</v>
       </c>
       <c r="X15" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="Y15">
         <v>24.900749999999999</v>
@@ -17788,7 +17788,7 @@
         <v>895</v>
       </c>
       <c r="K16" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="L16">
         <v>29.492382648463739</v>
@@ -17856,7 +17856,7 @@
         <v>897</v>
       </c>
       <c r="K17" t="s">
-        <v>756</v>
+        <v>791</v>
       </c>
       <c r="L17">
         <v>8.6778699255653748</v>
@@ -17889,7 +17889,7 @@
         <v>1031</v>
       </c>
       <c r="X17" t="s">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="Y17">
         <v>29.838000000000001</v>
@@ -17924,7 +17924,7 @@
         <v>899</v>
       </c>
       <c r="K18" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="L18">
         <v>12.772248157772113</v>
@@ -17957,7 +17957,7 @@
         <v>1033</v>
       </c>
       <c r="X18" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="Y18">
         <v>58.689</v>
@@ -17992,7 +17992,7 @@
         <v>901</v>
       </c>
       <c r="K19" t="s">
-        <v>754</v>
+        <v>805</v>
       </c>
       <c r="L19">
         <v>11.876635800692616</v>
@@ -18025,7 +18025,7 @@
         <v>1035</v>
       </c>
       <c r="X19" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="Y19">
         <v>48.432000000000002</v>
@@ -18060,7 +18060,7 @@
         <v>903</v>
       </c>
       <c r="K20" t="s">
-        <v>744</v>
+        <v>763</v>
       </c>
       <c r="L20">
         <v>27.15579263061009</v>
@@ -18093,7 +18093,7 @@
         <v>1037</v>
       </c>
       <c r="X20" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="Y20">
         <v>47.794499999999999</v>
@@ -18128,7 +18128,7 @@
         <v>905</v>
       </c>
       <c r="K21" t="s">
-        <v>749</v>
+        <v>772</v>
       </c>
       <c r="L21">
         <v>27.043339674957092</v>
@@ -18161,7 +18161,7 @@
         <v>1039</v>
       </c>
       <c r="X21" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="Y21">
         <v>7.1767500000000002</v>
@@ -18196,7 +18196,7 @@
         <v>907</v>
       </c>
       <c r="K22" t="s">
-        <v>753</v>
+        <v>804</v>
       </c>
       <c r="L22">
         <v>12.170927347824723</v>
@@ -18229,7 +18229,7 @@
         <v>1041</v>
       </c>
       <c r="X22" t="s">
-        <v>883</v>
+        <v>863</v>
       </c>
       <c r="Y22">
         <v>8.1052499999999998</v>
@@ -18297,7 +18297,7 @@
         <v>1043</v>
       </c>
       <c r="X23" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="Y23">
         <v>9.3810000000000002</v>
@@ -18332,7 +18332,7 @@
         <v>911</v>
       </c>
       <c r="K24" t="s">
-        <v>780</v>
+        <v>766</v>
       </c>
       <c r="L24">
         <v>23.305350986470582</v>
@@ -18400,7 +18400,7 @@
         <v>913</v>
       </c>
       <c r="K25" t="s">
-        <v>781</v>
+        <v>767</v>
       </c>
       <c r="L25">
         <v>19.293897715957783</v>
@@ -18433,7 +18433,7 @@
         <v>1047</v>
       </c>
       <c r="X25" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
       <c r="Y25">
         <v>6.1372499999999999</v>
@@ -18468,7 +18468,7 @@
         <v>915</v>
       </c>
       <c r="K26" t="s">
-        <v>762</v>
+        <v>811</v>
       </c>
       <c r="L26">
         <v>15.217638427037592</v>
@@ -18536,7 +18536,7 @@
         <v>917</v>
       </c>
       <c r="K27" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="L27">
         <v>3.1385663053565613</v>
@@ -18569,7 +18569,7 @@
         <v>1051</v>
       </c>
       <c r="X27" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="Y27">
         <v>10.491</v>
@@ -18604,7 +18604,7 @@
         <v>919</v>
       </c>
       <c r="K28" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="L28">
         <v>4.0628682283884237</v>
@@ -18672,7 +18672,7 @@
         <v>921</v>
       </c>
       <c r="K29" t="s">
-        <v>771</v>
+        <v>745</v>
       </c>
       <c r="L29">
         <v>18.31221960055294</v>
@@ -18705,7 +18705,7 @@
         <v>1055</v>
       </c>
       <c r="X29" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="Y29">
         <v>10.968</v>
@@ -18740,7 +18740,7 @@
         <v>923</v>
       </c>
       <c r="K30" t="s">
-        <v>752</v>
+        <v>803</v>
       </c>
       <c r="L30">
         <v>27.91719839668141</v>
@@ -18773,7 +18773,7 @@
         <v>1057</v>
       </c>
       <c r="X30" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="Y30">
         <v>10.79175</v>
@@ -18808,7 +18808,7 @@
         <v>925</v>
       </c>
       <c r="K31" t="s">
-        <v>775</v>
+        <v>749</v>
       </c>
       <c r="L31">
         <v>20.659184774772967</v>
@@ -18841,7 +18841,7 @@
         <v>1059</v>
       </c>
       <c r="X31" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="Y31">
         <v>20.114249999999998</v>
@@ -18876,7 +18876,7 @@
         <v>927</v>
       </c>
       <c r="K32" t="s">
-        <v>784</v>
+        <v>752</v>
       </c>
       <c r="L32">
         <v>1.6724491767694549</v>
@@ -18909,7 +18909,7 @@
         <v>1061</v>
       </c>
       <c r="X32" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="Y32">
         <v>44.373750000000001</v>
@@ -18944,7 +18944,7 @@
         <v>929</v>
       </c>
       <c r="K33" t="s">
-        <v>785</v>
+        <v>753</v>
       </c>
       <c r="L33">
         <v>13.9157416320151</v>
@@ -18977,7 +18977,7 @@
         <v>1063</v>
       </c>
       <c r="X33" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="Y33">
         <v>18.57525</v>
@@ -19012,7 +19012,7 @@
         <v>931</v>
       </c>
       <c r="K34" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="L34">
         <v>19.755004592887676</v>
@@ -19045,7 +19045,7 @@
         <v>1065</v>
       </c>
       <c r="X34" t="s">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="Y34">
         <v>18.241499999999998</v>
@@ -19080,7 +19080,7 @@
         <v>933</v>
       </c>
       <c r="K35" t="s">
-        <v>774</v>
+        <v>748</v>
       </c>
       <c r="L35">
         <v>14.794879040591612</v>
@@ -19115,7 +19115,7 @@
         <v>935</v>
       </c>
       <c r="K36" t="s">
-        <v>783</v>
+        <v>751</v>
       </c>
       <c r="L36">
         <v>6.2274748795149915</v>
@@ -19150,7 +19150,7 @@
         <v>937</v>
       </c>
       <c r="K37" t="s">
-        <v>768</v>
+        <v>742</v>
       </c>
       <c r="L37">
         <v>20.047482861417784</v>
@@ -19185,7 +19185,7 @@
         <v>939</v>
       </c>
       <c r="K38" t="s">
-        <v>761</v>
+        <v>810</v>
       </c>
       <c r="L38">
         <v>39.487686646898077</v>
@@ -19220,7 +19220,7 @@
         <v>941</v>
       </c>
       <c r="K39" t="s">
-        <v>741</v>
+        <v>760</v>
       </c>
       <c r="L39">
         <v>25.823486809088088</v>
@@ -19255,7 +19255,7 @@
         <v>943</v>
       </c>
       <c r="K40" t="s">
-        <v>740</v>
+        <v>759</v>
       </c>
       <c r="L40">
         <v>66.70158467196768</v>
@@ -19290,7 +19290,7 @@
         <v>945</v>
       </c>
       <c r="K41" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="L41">
         <v>48.268110562179842</v>
@@ -19325,7 +19325,7 @@
         <v>947</v>
       </c>
       <c r="K42" t="s">
-        <v>798</v>
+        <v>776</v>
       </c>
       <c r="L42">
         <v>90.630298494129065</v>
@@ -19360,7 +19360,7 @@
         <v>949</v>
       </c>
       <c r="K43" t="s">
-        <v>796</v>
+        <v>774</v>
       </c>
       <c r="L43">
         <v>33.627820830597955</v>
@@ -19395,7 +19395,7 @@
         <v>951</v>
       </c>
       <c r="K44" t="s">
-        <v>751</v>
+        <v>802</v>
       </c>
       <c r="L44">
         <v>30.412670648726838</v>
@@ -19430,7 +19430,7 @@
         <v>953</v>
       </c>
       <c r="K45" t="s">
-        <v>755</v>
+        <v>790</v>
       </c>
       <c r="L45">
         <v>47.878917655816522</v>
@@ -19465,7 +19465,7 @@
         <v>955</v>
       </c>
       <c r="K46" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="L46">
         <v>69.366510391046873</v>
@@ -19500,7 +19500,7 @@
         <v>957</v>
       </c>
       <c r="K47" t="s">
-        <v>758</v>
+        <v>793</v>
       </c>
       <c r="L47">
         <v>19.428837136062757</v>
@@ -19570,7 +19570,7 @@
         <v>961</v>
       </c>
       <c r="K49" t="s">
-        <v>747</v>
+        <v>770</v>
       </c>
       <c r="L49">
         <v>13.019602602156084</v>
@@ -19605,7 +19605,7 @@
         <v>963</v>
       </c>
       <c r="K50" t="s">
-        <v>803</v>
+        <v>781</v>
       </c>
       <c r="L50">
         <v>25.094411791551167</v>
@@ -19640,7 +19640,7 @@
         <v>965</v>
       </c>
       <c r="K51" t="s">
-        <v>777</v>
+        <v>755</v>
       </c>
       <c r="L51">
         <v>10.512568509966947</v>
@@ -19675,7 +19675,7 @@
         <v>967</v>
       </c>
       <c r="K52" t="s">
-        <v>757</v>
+        <v>792</v>
       </c>
       <c r="L52">
         <v>19.484319735030326</v>
@@ -19710,7 +19710,7 @@
         <v>969</v>
       </c>
       <c r="K53" t="s">
-        <v>770</v>
+        <v>744</v>
       </c>
       <c r="L53">
         <v>10.300130106481824</v>
@@ -19745,7 +19745,7 @@
         <v>971</v>
       </c>
       <c r="K54" t="s">
-        <v>802</v>
+        <v>780</v>
       </c>
       <c r="L54">
         <v>38.113797875314695</v>
@@ -19780,7 +19780,7 @@
         <v>973</v>
       </c>
       <c r="K55" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="L55">
         <v>48.324816212675138</v>
@@ -19850,7 +19850,7 @@
         <v>977</v>
       </c>
       <c r="K57" t="s">
-        <v>782</v>
+        <v>750</v>
       </c>
       <c r="L57">
         <v>65.706815294563484</v>
@@ -19885,7 +19885,7 @@
         <v>979</v>
       </c>
       <c r="K58" t="s">
-        <v>763</v>
+        <v>737</v>
       </c>
       <c r="L58">
         <v>55.231206871897385</v>
@@ -19920,7 +19920,7 @@
         <v>981</v>
       </c>
       <c r="K59" t="s">
-        <v>764</v>
+        <v>738</v>
       </c>
       <c r="L59">
         <v>19.970554339652629</v>
@@ -19955,7 +19955,7 @@
         <v>983</v>
       </c>
       <c r="K60" t="s">
-        <v>759</v>
+        <v>808</v>
       </c>
       <c r="L60">
         <v>72.559102068013246</v>
@@ -19990,7 +19990,7 @@
         <v>985</v>
       </c>
       <c r="K61" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="L61">
         <v>44.220292794619994</v>
@@ -20025,7 +20025,7 @@
         <v>987</v>
       </c>
       <c r="K62" t="s">
-        <v>746</v>
+        <v>769</v>
       </c>
       <c r="L62">
         <v>39.277945374969107</v>
@@ -20060,7 +20060,7 @@
         <v>989</v>
       </c>
       <c r="K63" t="s">
-        <v>745</v>
+        <v>768</v>
       </c>
       <c r="L63">
         <v>59.341737840109467</v>
@@ -20095,7 +20095,7 @@
         <v>991</v>
       </c>
       <c r="K64" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="L64">
         <v>29.191927665826828</v>
@@ -20130,7 +20130,7 @@
         <v>993</v>
       </c>
       <c r="K65" t="s">
-        <v>765</v>
+        <v>739</v>
       </c>
       <c r="L65">
         <v>39.617260419426948</v>
@@ -20165,7 +20165,7 @@
         <v>995</v>
       </c>
       <c r="K66" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="L66">
         <v>47.296862636729713</v>
@@ -20200,7 +20200,7 @@
         <v>997</v>
       </c>
       <c r="K67" t="s">
-        <v>737</v>
+        <v>756</v>
       </c>
       <c r="L67">
         <v>23.350121881103082</v>
@@ -20235,7 +20235,7 @@
         <v>999</v>
       </c>
       <c r="K68" t="s">
-        <v>772</v>
+        <v>746</v>
       </c>
       <c r="L68">
         <v>15.401477961960474</v>
@@ -20305,7 +20305,7 @@
         <v>1003</v>
       </c>
       <c r="K70" t="s">
-        <v>800</v>
+        <v>778</v>
       </c>
       <c r="L70">
         <v>23.89105636564183</v>
@@ -20340,7 +20340,7 @@
         <v>1005</v>
       </c>
       <c r="K71" t="s">
-        <v>739</v>
+        <v>758</v>
       </c>
       <c r="L71">
         <v>18.959710131684457</v>
@@ -20375,7 +20375,7 @@
         <v>1007</v>
       </c>
       <c r="K72" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="L72">
         <v>6.6550975614073966</v>
@@ -20410,7 +20410,7 @@
         <v>1009</v>
       </c>
       <c r="K73" t="s">
-        <v>776</v>
+        <v>754</v>
       </c>
       <c r="L73">
         <v>13.961943802326671</v>
@@ -20445,7 +20445,7 @@
         <v>1011</v>
       </c>
       <c r="K74" t="s">
-        <v>760</v>
+        <v>809</v>
       </c>
       <c r="L74">
         <v>53.946776653453853</v>
@@ -20480,7 +20480,7 @@
         <v>1013</v>
       </c>
       <c r="K75" t="s">
-        <v>750</v>
+        <v>801</v>
       </c>
       <c r="L75">
         <v>21.246092446368579</v>
@@ -20515,7 +20515,7 @@
         <v>1015</v>
       </c>
       <c r="K76" t="s">
-        <v>766</v>
+        <v>740</v>
       </c>
       <c r="L76">
         <v>19.51059121972445</v>
@@ -20550,7 +20550,7 @@
         <v>1017</v>
       </c>
       <c r="K77" t="s">
-        <v>778</v>
+        <v>764</v>
       </c>
       <c r="L77">
         <v>30.378621105864486</v>
@@ -20565,7 +20565,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{962B8832-5D69-4298-8256-89F636239651}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A840AB1-3774-4AF5-BCF6-4F30E38C3738}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F3B1894-699C-4A48-B126-7D196A3AC48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CBB9906-CB17-495E-8C05-0A6EEE587B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1371,18 +1371,414 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_061</t>
   </si>
   <si>
@@ -1407,246 +1803,6 @@
     <t>connecting solar to buses in cluster 36</t>
   </si>
   <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_060</t>
   </si>
   <si>
@@ -1689,253 +1845,301 @@
     <t>connecting solar to buses in cluster 44</t>
   </si>
   <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_dem1,e_gen2</t>
+  </si>
+  <si>
+    <t>e_gen4</t>
+  </si>
+  <si>
+    <t>e_gen3</t>
+  </si>
+  <si>
+    <t>e_dem4</t>
+  </si>
+  <si>
+    <t>e_dem3,e_dem4</t>
+  </si>
+  <si>
+    <t>e_dem3</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem3,e_dem0</t>
+  </si>
+  <si>
+    <t>e_dem2</t>
+  </si>
+  <si>
+    <t>e_gen0</t>
+  </si>
+  <si>
     <t>e_gen1</t>
   </si>
   <si>
+    <t>e_dem3,e_dem0,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem4</t>
+  </si>
+  <si>
+    <t>e_dem3,e_gen3</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem0</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem2</t>
+  </si>
+  <si>
+    <t>e_dem0</t>
+  </si>
+  <si>
+    <t>e_dem1</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem0,e_dem2</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem4,e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen2</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen0</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem0</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen4</t>
+  </si>
+  <si>
     <t>e_gen2,e_dem3</t>
   </si>
   <si>
-    <t>e_dem2</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen0</t>
-  </si>
-  <si>
-    <t>e_gen0</t>
-  </si>
-  <si>
-    <t>e_dem0</t>
-  </si>
-  <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen2</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem4</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem2</t>
-  </si>
-  <si>
-    <t>e_dem4</t>
-  </si>
-  <si>
-    <t>e_dem3,e_dem4</t>
-  </si>
-  <si>
-    <t>e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen4</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem4,e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen3</t>
-  </si>
-  <si>
-    <t>e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem3,e_dem0,e_gen3</t>
-  </si>
-  <si>
     <t>e_dem3,e_gen2,e_dem4</t>
   </si>
   <si>
     <t>e_gen2,e_dem1</t>
   </si>
   <si>
-    <t>e_dem0,e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen4,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem3,e_dem0</t>
+    <t>distr_wonelc_won_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
   </si>
   <si>
     <t>distr_wonelc_won_048</t>
@@ -2004,6 +2208,18 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_047</t>
   </si>
   <si>
@@ -2028,58 +2244,28 @@
     <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_wonelc_won_067</t>
@@ -2106,114 +2292,6 @@
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_035</t>
   </si>
   <si>
@@ -2238,84 +2316,6 @@
     <t>connecting wind onshore to buses in cluster 37</t>
   </si>
   <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_050</t>
   </si>
   <si>
@@ -2340,6 +2340,123 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem0,e_dem3</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem3,e_dem1</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem4,e_dem1</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_dem0,e_dem3,e_gen3</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>elc_won_065</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen2</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
     <t>elc_won_048</t>
   </si>
   <si>
@@ -2379,6 +2496,12 @@
     <t>elc_won_021</t>
   </si>
   <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
     <t>elc_won_047</t>
   </si>
   <si>
@@ -2391,34 +2514,19 @@
     <t>elc_won_023</t>
   </si>
   <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem0,e_dem3</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem4</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
   </si>
   <si>
     <t>elc_won_067</t>
@@ -2433,72 +2541,6 @@
     <t>elc_won_015</t>
   </si>
   <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem4</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem3,e_dem1</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem4,e_dem1</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_dem0,e_dem3,e_gen3</t>
-  </si>
-  <si>
-    <t>elc_won_044</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
     <t>elc_won_035</t>
   </si>
   <si>
@@ -2511,48 +2553,6 @@
     <t>elc_won_037</t>
   </si>
   <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen2</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>elc_won_065</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
     <t>elc_won_050</t>
   </si>
   <si>
@@ -2565,6 +2565,132 @@
     <t>elc_won_016</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_006</t>
   </si>
   <si>
@@ -2583,130 +2709,70 @@
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_dem3,e_gen2</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
   </si>
   <si>
     <t>elc_wof_006</t>
@@ -2716,72 +2782,6 @@
   </si>
   <si>
     <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen2</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -8106,7 +8106,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB753E1-BBE6-48B4-B6AC-D1327C335CC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFF78516-ED72-45F7-B4FE-9B12C31A5B5A}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8344,16 +8344,16 @@
         <v>414</v>
       </c>
       <c r="Y11" t="s">
-        <v>335</v>
+        <v>410</v>
       </c>
       <c r="Z11" t="s">
         <v>574</v>
       </c>
       <c r="AA11">
-        <v>0.98443531955055918</v>
+        <v>0.99395293926735107</v>
       </c>
       <c r="AB11">
-        <v>285.35247490641569</v>
+        <v>110.86278009856306</v>
       </c>
       <c r="AD11" t="s">
         <v>413</v>
@@ -8383,13 +8383,13 @@
         <v>737</v>
       </c>
       <c r="AN11" t="s">
-        <v>574</v>
+        <v>738</v>
       </c>
       <c r="AO11">
-        <v>0.98039873263051136</v>
+        <v>0.98045336302656594</v>
       </c>
       <c r="AP11">
-        <v>359.35656844062476</v>
+        <v>358.3550111796236</v>
       </c>
       <c r="AR11" t="s">
         <v>413</v>
@@ -8419,13 +8419,13 @@
         <v>860</v>
       </c>
       <c r="BB11" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="BC11">
-        <v>0.96501685329080267</v>
+        <v>0.97204337209146163</v>
       </c>
       <c r="BD11">
-        <v>641.35768966861792</v>
+        <v>512.53817832320431</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8490,16 +8490,16 @@
         <v>418</v>
       </c>
       <c r="Y12" t="s">
-        <v>394</v>
+        <v>356</v>
       </c>
       <c r="Z12" t="s">
         <v>575</v>
       </c>
       <c r="AA12">
-        <v>0.97398849158227818</v>
+        <v>0.98304303411255212</v>
       </c>
       <c r="AB12">
-        <v>476.87765432490079</v>
+        <v>310.87770793654443</v>
       </c>
       <c r="AD12" t="s">
         <v>413</v>
@@ -8526,16 +8526,16 @@
         <v>605</v>
       </c>
       <c r="AM12" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AN12" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="AO12">
-        <v>0.98326547324039271</v>
+        <v>0.98832832974245843</v>
       </c>
       <c r="AP12">
-        <v>306.79965725946761</v>
+        <v>213.98062138826123</v>
       </c>
       <c r="AR12" t="s">
         <v>413</v>
@@ -8565,13 +8565,13 @@
         <v>861</v>
       </c>
       <c r="BB12" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="BC12">
-        <v>0.97197172623840289</v>
+        <v>0.97090678081281612</v>
       </c>
       <c r="BD12">
-        <v>513.8516856292805</v>
+        <v>533.37568509837058</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8636,16 +8636,16 @@
         <v>420</v>
       </c>
       <c r="Y13" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="Z13" t="s">
         <v>576</v>
       </c>
       <c r="AA13">
-        <v>0.98814122429339546</v>
+        <v>0.9902907805210438</v>
       </c>
       <c r="AB13">
-        <v>217.4108879544159</v>
+        <v>178.00235711419791</v>
       </c>
       <c r="AD13" t="s">
         <v>413</v>
@@ -8672,16 +8672,16 @@
         <v>607</v>
       </c>
       <c r="AM13" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AN13" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="AO13">
-        <v>0.98997462954848647</v>
+        <v>0.98934334912020028</v>
       </c>
       <c r="AP13">
-        <v>183.79845827774895</v>
+        <v>195.37193279632865</v>
       </c>
       <c r="AR13" t="s">
         <v>413</v>
@@ -8711,13 +8711,13 @@
         <v>862</v>
       </c>
       <c r="BB13" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="BC13">
-        <v>0.98010852330645815</v>
+        <v>0.96271559874449242</v>
       </c>
       <c r="BD13">
-        <v>364.67707271493384</v>
+        <v>683.54735635097268</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8782,16 +8782,16 @@
         <v>422</v>
       </c>
       <c r="Y14" t="s">
-        <v>373</v>
+        <v>411</v>
       </c>
       <c r="Z14" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="AA14">
-        <v>0.97065607524213282</v>
+        <v>0.99062084979042209</v>
       </c>
       <c r="AB14">
-        <v>537.97195389423189</v>
+        <v>171.95108717559444</v>
       </c>
       <c r="AD14" t="s">
         <v>413</v>
@@ -8818,16 +8818,16 @@
         <v>609</v>
       </c>
       <c r="AM14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AN14" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="AO14">
-        <v>0.98425147469462704</v>
+        <v>0.99072024613784004</v>
       </c>
       <c r="AP14">
-        <v>288.72296393183791</v>
+        <v>170.12882080626682</v>
       </c>
       <c r="AR14" t="s">
         <v>413</v>
@@ -8857,13 +8857,13 @@
         <v>863</v>
       </c>
       <c r="BB14" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="BC14">
-        <v>0.97204337209146163</v>
+        <v>0.97945251828158475</v>
       </c>
       <c r="BD14">
-        <v>512.53817832320431</v>
+        <v>376.70383150428029</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8928,16 +8928,16 @@
         <v>424</v>
       </c>
       <c r="Y15" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="Z15" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AA15">
-        <v>0.97916314637278834</v>
+        <v>0.98254903847705999</v>
       </c>
       <c r="AB15">
-        <v>382.00898316554651</v>
+        <v>319.93429458723335</v>
       </c>
       <c r="AD15" t="s">
         <v>413</v>
@@ -8964,16 +8964,16 @@
         <v>611</v>
       </c>
       <c r="AM15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AN15" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="AO15">
-        <v>0.97434541537281683</v>
+        <v>0.97416703287609641</v>
       </c>
       <c r="AP15">
-        <v>470.33405149835795</v>
+        <v>473.6043972715658</v>
       </c>
       <c r="AR15" t="s">
         <v>413</v>
@@ -9006,10 +9006,10 @@
         <v>583</v>
       </c>
       <c r="BC15">
-        <v>0.97090678081281612</v>
+        <v>0.96884606421228714</v>
       </c>
       <c r="BD15">
-        <v>533.37568509837058</v>
+        <v>571.15548944140187</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9074,16 +9074,16 @@
         <v>426</v>
       </c>
       <c r="Y16" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="Z16" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AA16">
-        <v>0.99243389564470808</v>
+        <v>0.97646711233585171</v>
       </c>
       <c r="AB16">
-        <v>138.71191318035258</v>
+        <v>431.43627384271826</v>
       </c>
       <c r="AD16" t="s">
         <v>413</v>
@@ -9110,16 +9110,16 @@
         <v>613</v>
       </c>
       <c r="AM16" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AN16" t="s">
-        <v>743</v>
+        <v>589</v>
       </c>
       <c r="AO16">
-        <v>0.98430775783289481</v>
+        <v>0.97182188871578934</v>
       </c>
       <c r="AP16">
-        <v>287.69110639692803</v>
+        <v>516.59870687719467</v>
       </c>
       <c r="AR16" t="s">
         <v>413</v>
@@ -9149,13 +9149,13 @@
         <v>865</v>
       </c>
       <c r="BB16" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="BC16">
-        <v>0.96827543539739536</v>
+        <v>0.97158773589553182</v>
       </c>
       <c r="BD16">
-        <v>581.61701771441915</v>
+        <v>520.89150858191567</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9220,16 +9220,16 @@
         <v>428</v>
       </c>
       <c r="Y17" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="Z17" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="AA17">
-        <v>0.98258925616289594</v>
+        <v>0.9863634971037446</v>
       </c>
       <c r="AB17">
-        <v>319.19697034690739</v>
+        <v>250.00255309801472</v>
       </c>
       <c r="AD17" t="s">
         <v>413</v>
@@ -9259,13 +9259,13 @@
         <v>744</v>
       </c>
       <c r="AN17" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AO17">
-        <v>0.97444364094885727</v>
+        <v>0.97902953573897011</v>
       </c>
       <c r="AP17">
-        <v>468.53324927094968</v>
+        <v>384.45851145221434</v>
       </c>
       <c r="AR17" t="s">
         <v>413</v>
@@ -9295,13 +9295,13 @@
         <v>866</v>
       </c>
       <c r="BB17" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="BC17">
-        <v>0.96595696185315882</v>
+        <v>0.96837970323216338</v>
       </c>
       <c r="BD17">
-        <v>624.12236602542168</v>
+        <v>579.70544074367149</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9366,16 +9366,16 @@
         <v>430</v>
       </c>
       <c r="Y18" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="Z18" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="AA18">
-        <v>0.98625535317143753</v>
+        <v>0.98024768078410096</v>
       </c>
       <c r="AB18">
-        <v>251.98519185697839</v>
+        <v>362.12585229148283</v>
       </c>
       <c r="AD18" t="s">
         <v>413</v>
@@ -9405,13 +9405,13 @@
         <v>745</v>
       </c>
       <c r="AN18" t="s">
-        <v>576</v>
+        <v>746</v>
       </c>
       <c r="AO18">
-        <v>0.98574603285635165</v>
+        <v>0.97223070787085453</v>
       </c>
       <c r="AP18">
-        <v>261.32273096688704</v>
+        <v>509.10368903433471</v>
       </c>
       <c r="AR18" t="s">
         <v>413</v>
@@ -9441,13 +9441,13 @@
         <v>867</v>
       </c>
       <c r="BB18" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="BC18">
-        <v>0.96139268083002405</v>
+        <v>0.98427567578715769</v>
       </c>
       <c r="BD18">
-        <v>707.80085144956001</v>
+        <v>288.27927723544332</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9512,16 +9512,16 @@
         <v>432</v>
       </c>
       <c r="Y19" t="s">
-        <v>405</v>
+        <v>339</v>
       </c>
       <c r="Z19" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AA19">
-        <v>0.98719346865782154</v>
+        <v>0.97878284543380634</v>
       </c>
       <c r="AB19">
-        <v>234.78640793993935</v>
+        <v>388.98116704688283</v>
       </c>
       <c r="AD19" t="s">
         <v>413</v>
@@ -9548,16 +9548,16 @@
         <v>619</v>
       </c>
       <c r="AM19" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AN19" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AO19">
-        <v>0.97968688829580564</v>
+        <v>0.99323428174300499</v>
       </c>
       <c r="AP19">
-        <v>372.40704791023012</v>
+        <v>124.03816804490805</v>
       </c>
       <c r="AR19" t="s">
         <v>413</v>
@@ -9587,13 +9587,13 @@
         <v>868</v>
       </c>
       <c r="BB19" t="s">
-        <v>869</v>
+        <v>596</v>
       </c>
       <c r="BC19">
-        <v>0.96285001328169728</v>
+        <v>0.96683718298551269</v>
       </c>
       <c r="BD19">
-        <v>681.08308983555014</v>
+        <v>607.98497859893303</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9658,16 +9658,16 @@
         <v>434</v>
       </c>
       <c r="Y20" t="s">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="Z20" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="AA20">
-        <v>0.97184397355215157</v>
+        <v>0.9898744603534384</v>
       </c>
       <c r="AB20">
-        <v>516.19381821055424</v>
+        <v>185.63489352029583</v>
       </c>
       <c r="AD20" t="s">
         <v>413</v>
@@ -9694,16 +9694,16 @@
         <v>621</v>
       </c>
       <c r="AM20" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AN20" t="s">
-        <v>580</v>
+        <v>750</v>
       </c>
       <c r="AO20">
-        <v>0.98420825457429406</v>
+        <v>0.97340237375196048</v>
       </c>
       <c r="AP20">
-        <v>289.51533280460853</v>
+        <v>487.62314788072359</v>
       </c>
       <c r="AR20" t="s">
         <v>413</v>
@@ -9730,16 +9730,16 @@
         <v>830</v>
       </c>
       <c r="BA20" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="BB20" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="BC20">
-        <v>0.98427567578715769</v>
+        <v>0.96781631663497858</v>
       </c>
       <c r="BD20">
-        <v>288.27927723544332</v>
+        <v>590.03419502539236</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9804,16 +9804,16 @@
         <v>436</v>
       </c>
       <c r="Y21" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="Z21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA21">
-        <v>0.97870278293688284</v>
+        <v>0.98205187669897798</v>
       </c>
       <c r="AB21">
-        <v>390.44897949048118</v>
+        <v>329.04892718540373</v>
       </c>
       <c r="AD21" t="s">
         <v>413</v>
@@ -9840,16 +9840,16 @@
         <v>623</v>
       </c>
       <c r="AM21" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="AN21" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="AO21">
-        <v>0.98302364254854535</v>
+        <v>0.98709698070191276</v>
       </c>
       <c r="AP21">
-        <v>311.23321994333526</v>
+        <v>236.55535379826514</v>
       </c>
       <c r="AR21" t="s">
         <v>413</v>
@@ -9876,16 +9876,16 @@
         <v>832</v>
       </c>
       <c r="BA21" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="BB21" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="BC21">
-        <v>0.96271559874449242</v>
+        <v>0.9781715029140422</v>
       </c>
       <c r="BD21">
-        <v>683.54735635097268</v>
+        <v>400.18911324255913</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9950,16 +9950,16 @@
         <v>438</v>
       </c>
       <c r="Y22" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Z22" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="AA22">
-        <v>0.98376398069352888</v>
+        <v>0.99142494197358011</v>
       </c>
       <c r="AB22">
-        <v>297.66035395197099</v>
+        <v>157.20939715103142</v>
       </c>
       <c r="AD22" t="s">
         <v>413</v>
@@ -9986,16 +9986,16 @@
         <v>625</v>
       </c>
       <c r="AM22" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="AN22" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="AO22">
-        <v>0.98689046040235784</v>
+        <v>0.97913435966240669</v>
       </c>
       <c r="AP22">
-        <v>240.34155929010652</v>
+        <v>382.53673952254371</v>
       </c>
       <c r="AR22" t="s">
         <v>413</v>
@@ -10022,16 +10022,16 @@
         <v>834</v>
       </c>
       <c r="BA22" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="BB22" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="BC22">
-        <v>0.97945251828158475</v>
+        <v>0.96139268083002405</v>
       </c>
       <c r="BD22">
-        <v>376.70383150428029</v>
+        <v>707.80085144956001</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10096,16 +10096,16 @@
         <v>440</v>
       </c>
       <c r="Y23" t="s">
-        <v>354</v>
+        <v>399</v>
       </c>
       <c r="Z23" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AA23">
-        <v>0.98456002227805428</v>
+        <v>0.9807975141504387</v>
       </c>
       <c r="AB23">
-        <v>283.06625823567157</v>
+        <v>352.04557390862351</v>
       </c>
       <c r="AD23" t="s">
         <v>413</v>
@@ -10132,16 +10132,16 @@
         <v>627</v>
       </c>
       <c r="AM23" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="AN23" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="AO23">
-        <v>0.97821870369907904</v>
+        <v>0.9802768549486589</v>
       </c>
       <c r="AP23">
-        <v>399.32376551688469</v>
+        <v>361.5909926079201</v>
       </c>
       <c r="AR23" t="s">
         <v>413</v>
@@ -10168,16 +10168,16 @@
         <v>836</v>
       </c>
       <c r="BA23" t="s">
+        <v>872</v>
+      </c>
+      <c r="BB23" t="s">
         <v>873</v>
       </c>
-      <c r="BB23" t="s">
-        <v>574</v>
-      </c>
       <c r="BC23">
-        <v>0.97048325247055856</v>
+        <v>0.96285001328169728</v>
       </c>
       <c r="BD23">
-        <v>541.14037137309333</v>
+        <v>681.08308983555014</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10242,16 +10242,16 @@
         <v>442</v>
       </c>
       <c r="Y24" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="Z24" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AA24">
-        <v>0.98915672308345548</v>
+        <v>0.98596629583708084</v>
       </c>
       <c r="AB24">
-        <v>198.79341013664933</v>
+        <v>257.28457632018387</v>
       </c>
       <c r="AD24" t="s">
         <v>413</v>
@@ -10278,16 +10278,16 @@
         <v>629</v>
       </c>
       <c r="AM24" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="AN24" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="AO24">
-        <v>0.98830156477913722</v>
+        <v>0.97414990055259076</v>
       </c>
       <c r="AP24">
-        <v>214.47131238248457</v>
+        <v>473.91848986916989</v>
       </c>
       <c r="AR24" t="s">
         <v>413</v>
@@ -10317,13 +10317,13 @@
         <v>874</v>
       </c>
       <c r="BB24" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="BC24">
-        <v>0.96692898910976954</v>
+        <v>0.97443086368153087</v>
       </c>
       <c r="BD24">
-        <v>606.30186632089146</v>
+        <v>468.76749917193416</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10388,16 +10388,16 @@
         <v>444</v>
       </c>
       <c r="Y25" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="Z25" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AA25">
-        <v>0.98436057808473831</v>
+        <v>0.99365868734102913</v>
       </c>
       <c r="AB25">
-        <v>286.72273511313136</v>
+        <v>116.25739874780012</v>
       </c>
       <c r="AD25" t="s">
         <v>413</v>
@@ -10424,16 +10424,16 @@
         <v>631</v>
       </c>
       <c r="AM25" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AN25" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="AO25">
-        <v>0.99112984822979389</v>
+        <v>0.98705643087911032</v>
       </c>
       <c r="AP25">
-        <v>162.61944912044567</v>
+        <v>237.29876721631038</v>
       </c>
       <c r="AR25" t="s">
         <v>413</v>
@@ -10463,13 +10463,13 @@
         <v>875</v>
       </c>
       <c r="BB25" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="BC25">
-        <v>0.97481390334887996</v>
+        <v>0.97367031900560153</v>
       </c>
       <c r="BD25">
-        <v>461.74510527053314</v>
+        <v>482.71081823063838</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10534,16 +10534,16 @@
         <v>446</v>
       </c>
       <c r="Y26" t="s">
-        <v>396</v>
+        <v>358</v>
       </c>
       <c r="Z26" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="AA26">
-        <v>0.99132783885824616</v>
+        <v>0.98564262027093064</v>
       </c>
       <c r="AB26">
-        <v>158.989620932154</v>
+        <v>263.21862836627207</v>
       </c>
       <c r="AD26" t="s">
         <v>413</v>
@@ -10570,16 +10570,16 @@
         <v>633</v>
       </c>
       <c r="AM26" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="AN26" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AO26">
-        <v>0.99054353037519915</v>
+        <v>0.98989284585574766</v>
       </c>
       <c r="AP26">
-        <v>173.36860978801644</v>
+        <v>185.29782597795898</v>
       </c>
       <c r="AR26" t="s">
         <v>413</v>
@@ -10612,10 +10612,10 @@
         <v>583</v>
       </c>
       <c r="BC26">
-        <v>0.96683718298551269</v>
+        <v>0.97048325247055856</v>
       </c>
       <c r="BD26">
-        <v>607.98497859893303</v>
+        <v>541.14037137309333</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10680,16 +10680,16 @@
         <v>448</v>
       </c>
       <c r="Y27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="Z27" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="AA27">
-        <v>0.98031356085023202</v>
+        <v>0.99296984942213296</v>
       </c>
       <c r="AB27">
-        <v>360.91805107908004</v>
+        <v>128.88609392756314</v>
       </c>
       <c r="AD27" t="s">
         <v>413</v>
@@ -10716,16 +10716,16 @@
         <v>635</v>
       </c>
       <c r="AM27" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AN27" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="AO27">
-        <v>0.9768934332867476</v>
+        <v>0.99054353037519915</v>
       </c>
       <c r="AP27">
-        <v>423.6203897429599</v>
+        <v>173.36860978801644</v>
       </c>
       <c r="AR27" t="s">
         <v>413</v>
@@ -10755,13 +10755,13 @@
         <v>877</v>
       </c>
       <c r="BB27" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="BC27">
-        <v>0.96781631663497858</v>
+        <v>0.96692898910976954</v>
       </c>
       <c r="BD27">
-        <v>590.03419502539236</v>
+        <v>606.30186632089146</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10826,16 +10826,16 @@
         <v>450</v>
       </c>
       <c r="Y28" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="Z28" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="AA28">
-        <v>0.97974172455321451</v>
+        <v>0.98042255120792365</v>
       </c>
       <c r="AB28">
-        <v>371.40171652440046</v>
+        <v>358.91989452139876</v>
       </c>
       <c r="AD28" t="s">
         <v>413</v>
@@ -10862,16 +10862,16 @@
         <v>637</v>
       </c>
       <c r="AM28" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AN28" t="s">
-        <v>757</v>
+        <v>587</v>
       </c>
       <c r="AO28">
-        <v>0.98045336302656594</v>
+        <v>0.9768934332867476</v>
       </c>
       <c r="AP28">
-        <v>358.3550111796236</v>
+        <v>423.6203897429599</v>
       </c>
       <c r="AR28" t="s">
         <v>413</v>
@@ -10901,13 +10901,13 @@
         <v>878</v>
       </c>
       <c r="BB28" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="BC28">
-        <v>0.98341789520181955</v>
+        <v>0.97481390334887996</v>
       </c>
       <c r="BD28">
-        <v>304.0052546333078</v>
+        <v>461.74510527053314</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10972,16 +10972,16 @@
         <v>452</v>
       </c>
       <c r="Y29" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="Z29" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AA29">
-        <v>0.98815787487536866</v>
+        <v>0.98981198518654634</v>
       </c>
       <c r="AB29">
-        <v>217.10562728490754</v>
+        <v>186.78027157998449</v>
       </c>
       <c r="AD29" t="s">
         <v>413</v>
@@ -11008,16 +11008,16 @@
         <v>639</v>
       </c>
       <c r="AM29" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AN29" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="AO29">
-        <v>0.98832832974245843</v>
+        <v>0.97612238282801922</v>
       </c>
       <c r="AP29">
-        <v>213.98062138826123</v>
+        <v>437.75631481964848</v>
       </c>
       <c r="AR29" t="s">
         <v>413</v>
@@ -11047,13 +11047,13 @@
         <v>879</v>
       </c>
       <c r="BB29" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="BC29">
-        <v>0.9781715029140422</v>
+        <v>0.98341789520181955</v>
       </c>
       <c r="BD29">
-        <v>400.18911324255913</v>
+        <v>304.0052546333078</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11118,16 +11118,16 @@
         <v>454</v>
       </c>
       <c r="Y30" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Z30" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AA30">
-        <v>0.98338655524515672</v>
+        <v>0.97580984429062223</v>
       </c>
       <c r="AB30">
-        <v>304.57982050546099</v>
+        <v>443.48618800525958</v>
       </c>
       <c r="AD30" t="s">
         <v>413</v>
@@ -11154,16 +11154,16 @@
         <v>641</v>
       </c>
       <c r="AM30" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AN30" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AO30">
-        <v>0.98934334912020028</v>
+        <v>0.98933138074259364</v>
       </c>
       <c r="AP30">
-        <v>195.37193279632865</v>
+        <v>195.59135305245039</v>
       </c>
       <c r="AR30" t="s">
         <v>413</v>
@@ -11193,13 +11193,13 @@
         <v>880</v>
       </c>
       <c r="BB30" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="BC30">
-        <v>0.96884606421228714</v>
+        <v>0.96827543539739536</v>
       </c>
       <c r="BD30">
-        <v>571.15548944140187</v>
+        <v>581.61701771441915</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11264,16 +11264,16 @@
         <v>456</v>
       </c>
       <c r="Y31" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="Z31" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AA31">
-        <v>0.97813651992719985</v>
+        <v>0.98738988106093839</v>
       </c>
       <c r="AB31">
-        <v>400.83046800133633</v>
+        <v>231.18551388279656</v>
       </c>
       <c r="AD31" t="s">
         <v>413</v>
@@ -11300,16 +11300,16 @@
         <v>643</v>
       </c>
       <c r="AM31" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AN31" t="s">
         <v>581</v>
       </c>
       <c r="AO31">
-        <v>0.99072024613784004</v>
+        <v>0.98703324072992327</v>
       </c>
       <c r="AP31">
-        <v>170.12882080626682</v>
+        <v>237.72391995140771</v>
       </c>
       <c r="AR31" t="s">
         <v>413</v>
@@ -11339,13 +11339,13 @@
         <v>881</v>
       </c>
       <c r="BB31" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="BC31">
-        <v>0.97158773589553182</v>
+        <v>0.96595696185315882</v>
       </c>
       <c r="BD31">
-        <v>520.89150858191567</v>
+        <v>624.12236602542168</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11410,16 +11410,16 @@
         <v>458</v>
       </c>
       <c r="Y32" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="Z32" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="AA32">
-        <v>0.99062084979042209</v>
+        <v>0.97723778280633045</v>
       </c>
       <c r="AB32">
-        <v>171.95108717559444</v>
+        <v>417.30731521727455</v>
       </c>
       <c r="AD32" t="s">
         <v>413</v>
@@ -11446,16 +11446,16 @@
         <v>645</v>
       </c>
       <c r="AM32" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AN32" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="AO32">
-        <v>0.97416703287609641</v>
+        <v>0.98653333840245183</v>
       </c>
       <c r="AP32">
-        <v>473.6043972715658</v>
+        <v>246.88879595504923</v>
       </c>
       <c r="AR32" t="s">
         <v>413</v>
@@ -11485,13 +11485,13 @@
         <v>882</v>
       </c>
       <c r="BB32" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="BC32">
-        <v>0.96837970323216338</v>
+        <v>0.96501685329080267</v>
       </c>
       <c r="BD32">
-        <v>579.70544074367149</v>
+        <v>641.35768966861792</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11556,16 +11556,16 @@
         <v>460</v>
       </c>
       <c r="Y33" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="Z33" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AA33">
-        <v>0.98254903847705999</v>
+        <v>0.99035601519017957</v>
       </c>
       <c r="AB33">
-        <v>319.93429458723335</v>
+        <v>176.80638818004016</v>
       </c>
       <c r="AD33" t="s">
         <v>413</v>
@@ -11592,16 +11592,16 @@
         <v>647</v>
       </c>
       <c r="AM33" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AN33" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="AO33">
-        <v>0.97182188871578934</v>
+        <v>0.96800325464323944</v>
       </c>
       <c r="AP33">
-        <v>516.59870687719467</v>
+        <v>586.60699820727632</v>
       </c>
       <c r="AR33" t="s">
         <v>413</v>
@@ -11631,13 +11631,13 @@
         <v>883</v>
       </c>
       <c r="BB33" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="BC33">
-        <v>0.97443086368153087</v>
+        <v>0.97197172623840289</v>
       </c>
       <c r="BD33">
-        <v>468.76749917193416</v>
+        <v>513.8516856292805</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11702,16 +11702,16 @@
         <v>462</v>
       </c>
       <c r="Y34" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="Z34" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AA34">
-        <v>0.97646711233585171</v>
+        <v>0.97970789283404214</v>
       </c>
       <c r="AB34">
-        <v>431.43627384271826</v>
+        <v>372.02196470922701</v>
       </c>
       <c r="AD34" t="s">
         <v>413</v>
@@ -11738,16 +11738,16 @@
         <v>649</v>
       </c>
       <c r="AM34" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AN34" t="s">
-        <v>576</v>
+        <v>599</v>
       </c>
       <c r="AO34">
-        <v>0.97902953573897011</v>
+        <v>0.98893828971746323</v>
       </c>
       <c r="AP34">
-        <v>384.45851145221434</v>
+        <v>202.7980218465068</v>
       </c>
       <c r="AR34" t="s">
         <v>413</v>
@@ -11777,13 +11777,13 @@
         <v>884</v>
       </c>
       <c r="BB34" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="BC34">
-        <v>0.97367031900560153</v>
+        <v>0.98010852330645815</v>
       </c>
       <c r="BD34">
-        <v>482.71081823063838</v>
+        <v>364.67707271493384</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11848,16 +11848,16 @@
         <v>464</v>
       </c>
       <c r="Y35" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="Z35" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="AA35">
-        <v>0.9863634971037446</v>
+        <v>0.98270299973748321</v>
       </c>
       <c r="AB35">
-        <v>250.00255309801472</v>
+        <v>317.11167147947373</v>
       </c>
       <c r="AD35" t="s">
         <v>413</v>
@@ -11884,16 +11884,16 @@
         <v>651</v>
       </c>
       <c r="AM35" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AN35" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="AO35">
-        <v>0.97567317785568242</v>
+        <v>0.98238877493134946</v>
       </c>
       <c r="AP35">
-        <v>445.99173931248959</v>
+        <v>322.87245959192745</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11958,16 +11958,16 @@
         <v>466</v>
       </c>
       <c r="Y36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Z36" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AA36">
-        <v>0.98024768078410096</v>
+        <v>0.97598085885692565</v>
       </c>
       <c r="AB36">
-        <v>362.12585229148283</v>
+        <v>440.3509209563627</v>
       </c>
       <c r="AD36" t="s">
         <v>413</v>
@@ -11994,16 +11994,16 @@
         <v>653</v>
       </c>
       <c r="AM36" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AN36" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="AO36">
-        <v>0.99568797339637038</v>
+        <v>0.98644744628709446</v>
       </c>
       <c r="AP36">
-        <v>79.053821066542412</v>
+        <v>248.46348473660174</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12068,16 +12068,16 @@
         <v>468</v>
       </c>
       <c r="Y37" t="s">
-        <v>410</v>
+        <v>348</v>
       </c>
       <c r="Z37" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="AA37">
-        <v>0.99395293926735107</v>
+        <v>0.98338655524515672</v>
       </c>
       <c r="AB37">
-        <v>110.86278009856306</v>
+        <v>304.57982050546099</v>
       </c>
       <c r="AD37" t="s">
         <v>413</v>
@@ -12104,16 +12104,16 @@
         <v>655</v>
       </c>
       <c r="AM37" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AN37" t="s">
         <v>576</v>
       </c>
       <c r="AO37">
-        <v>0.9918951652662058</v>
+        <v>0.98967580974453273</v>
       </c>
       <c r="AP37">
-        <v>148.58863678622743</v>
+        <v>189.27682135023403</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12178,16 +12178,16 @@
         <v>470</v>
       </c>
       <c r="Y38" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="Z38" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AA38">
-        <v>0.98304303411255212</v>
+        <v>0.97813651992719985</v>
       </c>
       <c r="AB38">
-        <v>310.87770793654443</v>
+        <v>400.83046800133633</v>
       </c>
       <c r="AD38" t="s">
         <v>413</v>
@@ -12214,16 +12214,16 @@
         <v>657</v>
       </c>
       <c r="AM38" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AN38" t="s">
         <v>576</v>
       </c>
       <c r="AO38">
-        <v>0.98531999116946412</v>
+        <v>0.98562083412131529</v>
       </c>
       <c r="AP38">
-        <v>269.13349522649082</v>
+        <v>263.61804110921923</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12288,16 +12288,16 @@
         <v>472</v>
       </c>
       <c r="Y39" t="s">
-        <v>388</v>
+        <v>355</v>
       </c>
       <c r="Z39" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA39">
-        <v>0.9902907805210438</v>
+        <v>0.99243389564470808</v>
       </c>
       <c r="AB39">
-        <v>178.00235711419791</v>
+        <v>138.71191318035258</v>
       </c>
       <c r="AD39" t="s">
         <v>413</v>
@@ -12324,16 +12324,16 @@
         <v>659</v>
       </c>
       <c r="AM39" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AN39" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="AO39">
-        <v>0.98879946679477992</v>
+        <v>0.99417752457368125</v>
       </c>
       <c r="AP39">
-        <v>205.34310876236799</v>
+        <v>106.74538281584397</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12398,16 +12398,16 @@
         <v>474</v>
       </c>
       <c r="Y40" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Z40" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="AA40">
-        <v>0.99409930001823366</v>
+        <v>0.98258925616289594</v>
       </c>
       <c r="AB40">
-        <v>108.17949966571678</v>
+        <v>319.19697034690739</v>
       </c>
       <c r="AD40" t="s">
         <v>413</v>
@@ -12434,16 +12434,16 @@
         <v>661</v>
       </c>
       <c r="AM40" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AN40" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="AO40">
-        <v>0.98121294780398804</v>
+        <v>0.98213512486164511</v>
       </c>
       <c r="AP40">
-        <v>344.42929026021937</v>
+        <v>327.5227108698395</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12508,16 +12508,16 @@
         <v>476</v>
       </c>
       <c r="Y41" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="Z41" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AA41">
-        <v>0.99045315399849054</v>
+        <v>0.98625535317143753</v>
       </c>
       <c r="AB41">
-        <v>175.02551002767362</v>
+        <v>251.98519185697839</v>
       </c>
       <c r="AD41" t="s">
         <v>413</v>
@@ -12544,16 +12544,16 @@
         <v>663</v>
       </c>
       <c r="AM41" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN41" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO41">
-        <v>0.97759288697657265</v>
+        <v>0.98305809009413248</v>
       </c>
       <c r="AP41">
-        <v>410.79707209616811</v>
+        <v>310.60168160757155</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12618,16 +12618,16 @@
         <v>478</v>
       </c>
       <c r="Y42" t="s">
-        <v>334</v>
+        <v>405</v>
       </c>
       <c r="Z42" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="AA42">
-        <v>0.99382288375189876</v>
+        <v>0.98719346865782154</v>
       </c>
       <c r="AB42">
-        <v>113.24713121519014</v>
+        <v>234.78640793993935</v>
       </c>
       <c r="AD42" t="s">
         <v>413</v>
@@ -12654,16 +12654,16 @@
         <v>665</v>
       </c>
       <c r="AM42" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AN42" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="AO42">
-        <v>0.97393752600115946</v>
+        <v>0.99584474408886259</v>
       </c>
       <c r="AP42">
-        <v>477.81202331207646</v>
+        <v>76.179691704186226</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12728,16 +12728,16 @@
         <v>480</v>
       </c>
       <c r="Y43" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="Z43" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="AA43">
-        <v>0.97000043567738925</v>
+        <v>0.97184397355215157</v>
       </c>
       <c r="AB43">
-        <v>549.99201258119717</v>
+        <v>516.19381821055424</v>
       </c>
       <c r="AD43" t="s">
         <v>413</v>
@@ -12764,16 +12764,16 @@
         <v>667</v>
       </c>
       <c r="AM43" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AN43" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="AO43">
-        <v>0.98893828971746323</v>
+        <v>0.9771067451947747</v>
       </c>
       <c r="AP43">
-        <v>202.7980218465068</v>
+        <v>419.70967142912968</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12838,16 +12838,16 @@
         <v>482</v>
       </c>
       <c r="Y44" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="Z44" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="AA44">
-        <v>0.98823937652699512</v>
+        <v>0.99382288375189876</v>
       </c>
       <c r="AB44">
-        <v>215.61143033842296</v>
+        <v>113.24713121519014</v>
       </c>
       <c r="AD44" t="s">
         <v>413</v>
@@ -12874,16 +12874,16 @@
         <v>669</v>
       </c>
       <c r="AM44" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AN44" t="s">
-        <v>775</v>
+        <v>586</v>
       </c>
       <c r="AO44">
-        <v>0.97223070787085453</v>
+        <v>0.97431371456908866</v>
       </c>
       <c r="AP44">
-        <v>509.10368903433471</v>
+        <v>470.91523290004181</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12948,16 +12948,16 @@
         <v>484</v>
       </c>
       <c r="Y45" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="Z45" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="AA45">
-        <v>0.97307234437114887</v>
+        <v>0.97000043567738925</v>
       </c>
       <c r="AB45">
-        <v>493.6736865289368</v>
+        <v>549.99201258119717</v>
       </c>
       <c r="AD45" t="s">
         <v>413</v>
@@ -12987,13 +12987,13 @@
         <v>776</v>
       </c>
       <c r="AN45" t="s">
-        <v>777</v>
+        <v>583</v>
       </c>
       <c r="AO45">
-        <v>0.99323428174300499</v>
+        <v>0.98039873263051136</v>
       </c>
       <c r="AP45">
-        <v>124.03816804490805</v>
+        <v>359.35656844062476</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13058,16 +13058,16 @@
         <v>486</v>
       </c>
       <c r="Y46" t="s">
-        <v>398</v>
+        <v>337</v>
       </c>
       <c r="Z46" t="s">
         <v>593</v>
       </c>
       <c r="AA46">
-        <v>0.97831141720185744</v>
+        <v>0.98823937652699512</v>
       </c>
       <c r="AB46">
-        <v>397.62401796594617</v>
+        <v>215.61143033842296</v>
       </c>
       <c r="AD46" t="s">
         <v>413</v>
@@ -13094,16 +13094,16 @@
         <v>673</v>
       </c>
       <c r="AM46" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="AN46" t="s">
-        <v>779</v>
+        <v>579</v>
       </c>
       <c r="AO46">
-        <v>0.97340237375196048</v>
+        <v>0.98326547324039271</v>
       </c>
       <c r="AP46">
-        <v>487.62314788072359</v>
+        <v>306.79965725946761</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13168,16 +13168,16 @@
         <v>488</v>
       </c>
       <c r="Y47" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="Z47" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="AA47">
-        <v>0.9753018595470957</v>
+        <v>0.97307234437114887</v>
       </c>
       <c r="AB47">
-        <v>452.79924163657859</v>
+        <v>493.6736865289368</v>
       </c>
       <c r="AD47" t="s">
         <v>413</v>
@@ -13204,16 +13204,16 @@
         <v>675</v>
       </c>
       <c r="AM47" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="AN47" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="AO47">
-        <v>0.98709698070191276</v>
+        <v>0.98997462954848647</v>
       </c>
       <c r="AP47">
-        <v>236.55535379826514</v>
+        <v>183.79845827774895</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13278,16 +13278,16 @@
         <v>490</v>
       </c>
       <c r="Y48" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="Z48" t="s">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="AA48">
-        <v>0.98694170150784422</v>
+        <v>0.97831141720185744</v>
       </c>
       <c r="AB48">
-        <v>239.40213902285669</v>
+        <v>397.62401796594617</v>
       </c>
       <c r="AD48" t="s">
         <v>413</v>
@@ -13314,16 +13314,16 @@
         <v>677</v>
       </c>
       <c r="AM48" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AN48" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO48">
-        <v>0.97913435966240669</v>
+        <v>0.98425147469462704</v>
       </c>
       <c r="AP48">
-        <v>382.53673952254371</v>
+        <v>288.72296393183791</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13388,16 +13388,16 @@
         <v>492</v>
       </c>
       <c r="Y49" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="Z49" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="AA49">
-        <v>0.98336988732579877</v>
+        <v>0.9753018595470957</v>
       </c>
       <c r="AB49">
-        <v>304.88539902702166</v>
+        <v>452.79924163657859</v>
       </c>
       <c r="AD49" t="s">
         <v>413</v>
@@ -13424,16 +13424,16 @@
         <v>679</v>
       </c>
       <c r="AM49" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="AN49" t="s">
         <v>595</v>
       </c>
       <c r="AO49">
-        <v>0.98238877493134946</v>
+        <v>0.97434541537281683</v>
       </c>
       <c r="AP49">
-        <v>322.87245959192745</v>
+        <v>470.33405149835795</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13498,16 +13498,16 @@
         <v>494</v>
       </c>
       <c r="Y50" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Z50" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="AA50">
-        <v>0.98042255120792365</v>
+        <v>0.98694170150784422</v>
       </c>
       <c r="AB50">
-        <v>358.91989452139876</v>
+        <v>239.40213902285669</v>
       </c>
       <c r="AD50" t="s">
         <v>413</v>
@@ -13534,16 +13534,16 @@
         <v>681</v>
       </c>
       <c r="AM50" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AN50" t="s">
-        <v>579</v>
+        <v>782</v>
       </c>
       <c r="AO50">
-        <v>0.98644744628709446</v>
+        <v>0.98430775783289481</v>
       </c>
       <c r="AP50">
-        <v>248.46348473660174</v>
+        <v>287.69110639692803</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13608,16 +13608,16 @@
         <v>496</v>
       </c>
       <c r="Y51" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="Z51" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="AA51">
-        <v>0.98981198518654634</v>
+        <v>0.98336988732579877</v>
       </c>
       <c r="AB51">
-        <v>186.78027157998449</v>
+        <v>304.88539902702166</v>
       </c>
       <c r="AD51" t="s">
         <v>413</v>
@@ -13644,16 +13644,16 @@
         <v>683</v>
       </c>
       <c r="AM51" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AN51" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AO51">
-        <v>0.98967580974453273</v>
+        <v>0.97444364094885727</v>
       </c>
       <c r="AP51">
-        <v>189.27682135023403</v>
+        <v>468.53324927094968</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13718,16 +13718,16 @@
         <v>498</v>
       </c>
       <c r="Y52" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="Z52" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="AA52">
-        <v>0.97580984429062223</v>
+        <v>0.97870278293688284</v>
       </c>
       <c r="AB52">
-        <v>443.48618800525958</v>
+        <v>390.44897949048118</v>
       </c>
       <c r="AD52" t="s">
         <v>413</v>
@@ -13754,16 +13754,16 @@
         <v>685</v>
       </c>
       <c r="AM52" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AN52" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="AO52">
-        <v>0.98562083412131529</v>
+        <v>0.98574603285635165</v>
       </c>
       <c r="AP52">
-        <v>263.61804110921923</v>
+        <v>261.32273096688704</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13828,16 +13828,16 @@
         <v>500</v>
       </c>
       <c r="Y53" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="Z53" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="AA53">
-        <v>0.98738988106093839</v>
+        <v>0.98376398069352888</v>
       </c>
       <c r="AB53">
-        <v>231.18551388279656</v>
+        <v>297.66035395197099</v>
       </c>
       <c r="AD53" t="s">
         <v>413</v>
@@ -13864,16 +13864,16 @@
         <v>687</v>
       </c>
       <c r="AM53" t="s">
+        <v>785</v>
+      </c>
+      <c r="AN53" t="s">
         <v>786</v>
       </c>
-      <c r="AN53" t="s">
-        <v>597</v>
-      </c>
       <c r="AO53">
-        <v>0.9802768549486589</v>
+        <v>0.97968688829580564</v>
       </c>
       <c r="AP53">
-        <v>361.5909926079201</v>
+        <v>372.40704791023012</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -13938,16 +13938,16 @@
         <v>502</v>
       </c>
       <c r="Y54" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="Z54" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA54">
-        <v>0.97723778280633045</v>
+        <v>0.98456002227805428</v>
       </c>
       <c r="AB54">
-        <v>417.30731521727455</v>
+        <v>283.06625823567157</v>
       </c>
       <c r="AD54" t="s">
         <v>413</v>
@@ -13977,13 +13977,13 @@
         <v>787</v>
       </c>
       <c r="AN54" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="AO54">
-        <v>0.97414990055259076</v>
+        <v>0.98420825457429406</v>
       </c>
       <c r="AP54">
-        <v>473.91848986916989</v>
+        <v>289.51533280460853</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -14048,16 +14048,16 @@
         <v>504</v>
       </c>
       <c r="Y55" t="s">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="Z55" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="AA55">
-        <v>0.99035601519017957</v>
+        <v>0.98915672308345548</v>
       </c>
       <c r="AB55">
-        <v>176.80638818004016</v>
+        <v>198.79341013664933</v>
       </c>
       <c r="AD55" t="s">
         <v>413</v>
@@ -14090,10 +14090,10 @@
         <v>589</v>
       </c>
       <c r="AO55">
-        <v>0.98705643087911032</v>
+        <v>0.98302364254854535</v>
       </c>
       <c r="AP55">
-        <v>237.29876721631038</v>
+        <v>311.23321994333526</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14158,16 +14158,16 @@
         <v>506</v>
       </c>
       <c r="Y56" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="Z56" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="AA56">
-        <v>0.97545857121381951</v>
+        <v>0.98436057808473831</v>
       </c>
       <c r="AB56">
-        <v>449.92619441330908</v>
+        <v>286.72273511313136</v>
       </c>
       <c r="AD56" t="s">
         <v>413</v>
@@ -14197,13 +14197,13 @@
         <v>789</v>
       </c>
       <c r="AN56" t="s">
-        <v>576</v>
+        <v>595</v>
       </c>
       <c r="AO56">
-        <v>0.98989284585574766</v>
+        <v>0.98003745158806088</v>
       </c>
       <c r="AP56">
-        <v>185.29782597795898</v>
+        <v>365.98005421888422</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14268,16 +14268,16 @@
         <v>508</v>
       </c>
       <c r="Y57" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="Z57" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="AA57">
-        <v>0.98212250728249206</v>
+        <v>0.99132783885824616</v>
       </c>
       <c r="AB57">
-        <v>327.75403315431197</v>
+        <v>158.989620932154</v>
       </c>
       <c r="AD57" t="s">
         <v>413</v>
@@ -14307,13 +14307,13 @@
         <v>790</v>
       </c>
       <c r="AN57" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="AO57">
-        <v>0.99009266720704037</v>
+        <v>0.98867603245018398</v>
       </c>
       <c r="AP57">
-        <v>181.63443453759336</v>
+        <v>207.60607174662678</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14378,16 +14378,16 @@
         <v>510</v>
       </c>
       <c r="Y58" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="Z58" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="AA58">
-        <v>0.99456410459052502</v>
+        <v>0.98031356085023202</v>
       </c>
       <c r="AB58">
-        <v>99.658082507040461</v>
+        <v>360.91805107908004</v>
       </c>
       <c r="AD58" t="s">
         <v>413</v>
@@ -14417,13 +14417,13 @@
         <v>791</v>
       </c>
       <c r="AN58" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AO58">
-        <v>0.98371568181207825</v>
+        <v>0.98689046040235784</v>
       </c>
       <c r="AP58">
-        <v>298.5458334452332</v>
+        <v>240.34155929010652</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14488,16 +14488,16 @@
         <v>512</v>
       </c>
       <c r="Y59" t="s">
-        <v>344</v>
+        <v>379</v>
       </c>
       <c r="Z59" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="AA59">
-        <v>0.97891429500574301</v>
+        <v>0.97974172455321451</v>
       </c>
       <c r="AB59">
-        <v>386.57125822804534</v>
+        <v>371.40171652440046</v>
       </c>
       <c r="AD59" t="s">
         <v>413</v>
@@ -14527,13 +14527,13 @@
         <v>792</v>
       </c>
       <c r="AN59" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="AO59">
-        <v>0.98435286039872183</v>
+        <v>0.97821870369907904</v>
       </c>
       <c r="AP59">
-        <v>286.8642260234331</v>
+        <v>399.32376551688469</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14598,16 +14598,16 @@
         <v>514</v>
       </c>
       <c r="Y60" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="Z60" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AA60">
-        <v>0.99086247853214549</v>
+        <v>0.98815787487536866</v>
       </c>
       <c r="AB60">
-        <v>167.52122691066626</v>
+        <v>217.10562728490754</v>
       </c>
       <c r="AD60" t="s">
         <v>413</v>
@@ -14637,13 +14637,13 @@
         <v>793</v>
       </c>
       <c r="AN60" t="s">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="AO60">
-        <v>0.97655782887090981</v>
+        <v>0.98830156477913722</v>
       </c>
       <c r="AP60">
-        <v>429.77313736665354</v>
+        <v>214.47131238248457</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14708,16 +14708,16 @@
         <v>516</v>
       </c>
       <c r="Y61" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="Z61" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="AA61">
-        <v>0.9839124944774571</v>
+        <v>0.97272179131491798</v>
       </c>
       <c r="AB61">
-        <v>294.93760124661941</v>
+        <v>500.10049255983796</v>
       </c>
       <c r="AD61" t="s">
         <v>413</v>
@@ -14747,13 +14747,13 @@
         <v>794</v>
       </c>
       <c r="AN61" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="AO61">
-        <v>0.99417752457368125</v>
+        <v>0.99112984822979389</v>
       </c>
       <c r="AP61">
-        <v>106.74538281584397</v>
+        <v>162.61944912044567</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14818,16 +14818,16 @@
         <v>518</v>
       </c>
       <c r="Y62" t="s">
-        <v>377</v>
+        <v>346</v>
       </c>
       <c r="Z62" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="AA62">
-        <v>0.97678875799905829</v>
+        <v>0.98444284858889564</v>
       </c>
       <c r="AB62">
-        <v>425.5394366839318</v>
+        <v>285.21444253691413</v>
       </c>
       <c r="AD62" t="s">
         <v>413</v>
@@ -14857,13 +14857,13 @@
         <v>795</v>
       </c>
       <c r="AN62" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AO62">
-        <v>0.98213512486164511</v>
+        <v>0.98879946679477992</v>
       </c>
       <c r="AP62">
-        <v>327.5227108698395</v>
+        <v>205.34310876236799</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14928,16 +14928,16 @@
         <v>520</v>
       </c>
       <c r="Y63" t="s">
-        <v>406</v>
+        <v>360</v>
       </c>
       <c r="Z63" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AA63">
-        <v>0.99165078812878382</v>
+        <v>0.98269942042940017</v>
       </c>
       <c r="AB63">
-        <v>153.06888430562992</v>
+        <v>317.17729212766454</v>
       </c>
       <c r="AD63" t="s">
         <v>413</v>
@@ -14967,13 +14967,13 @@
         <v>796</v>
       </c>
       <c r="AN63" t="s">
-        <v>797</v>
+        <v>583</v>
       </c>
       <c r="AO63">
-        <v>0.98305809009413248</v>
+        <v>0.98121294780398804</v>
       </c>
       <c r="AP63">
-        <v>310.60168160757155</v>
+        <v>344.42929026021937</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -15038,16 +15038,16 @@
         <v>522</v>
       </c>
       <c r="Y64" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="Z64" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="AA64">
-        <v>0.97646479583958734</v>
+        <v>0.98213943337265219</v>
       </c>
       <c r="AB64">
-        <v>431.47874294089837</v>
+        <v>327.44372150137696</v>
       </c>
       <c r="AD64" t="s">
         <v>413</v>
@@ -15074,16 +15074,16 @@
         <v>709</v>
       </c>
       <c r="AM64" t="s">
+        <v>797</v>
+      </c>
+      <c r="AN64" t="s">
         <v>798</v>
       </c>
-      <c r="AN64" t="s">
-        <v>601</v>
-      </c>
       <c r="AO64">
-        <v>0.99584474408886259</v>
+        <v>0.97759288697657265</v>
       </c>
       <c r="AP64">
-        <v>76.179691704186226</v>
+        <v>410.79707209616811</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -15148,16 +15148,16 @@
         <v>524</v>
       </c>
       <c r="Y65" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="Z65" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="AA65">
-        <v>0.96562135615554268</v>
+        <v>0.98055369884714538</v>
       </c>
       <c r="AB65">
-        <v>630.27513714838358</v>
+        <v>356.51552113566873</v>
       </c>
       <c r="AD65" t="s">
         <v>413</v>
@@ -15187,13 +15187,13 @@
         <v>799</v>
       </c>
       <c r="AN65" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO65">
-        <v>0.9771067451947747</v>
+        <v>0.97393752600115946</v>
       </c>
       <c r="AP65">
-        <v>419.70967142912968</v>
+        <v>477.81202331207646</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15258,16 +15258,16 @@
         <v>526</v>
       </c>
       <c r="Y66" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="Z66" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="AA66">
-        <v>0.98843111817052332</v>
+        <v>0.99284163372730061</v>
       </c>
       <c r="AB66">
-        <v>212.09616687373853</v>
+        <v>131.23671499948927</v>
       </c>
       <c r="AD66" t="s">
         <v>413</v>
@@ -15297,13 +15297,13 @@
         <v>800</v>
       </c>
       <c r="AN66" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="AO66">
-        <v>0.97431371456908866</v>
+        <v>0.97567317785568242</v>
       </c>
       <c r="AP66">
-        <v>470.91523290004181</v>
+        <v>445.99173931248959</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15368,16 +15368,16 @@
         <v>528</v>
       </c>
       <c r="Y67" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="Z67" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA67">
-        <v>0.98055369884714538</v>
+        <v>0.980949293282396</v>
       </c>
       <c r="AB67">
-        <v>356.51552113566873</v>
+        <v>349.26295648940771</v>
       </c>
       <c r="AD67" t="s">
         <v>413</v>
@@ -15407,13 +15407,13 @@
         <v>801</v>
       </c>
       <c r="AN67" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="AO67">
-        <v>0.97612238282801922</v>
+        <v>0.99568797339637038</v>
       </c>
       <c r="AP67">
-        <v>437.75631481964848</v>
+        <v>79.053821066542412</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15478,16 +15478,16 @@
         <v>530</v>
       </c>
       <c r="Y68" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Z68" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="AA68">
-        <v>0.99284163372730061</v>
+        <v>0.98440429555001041</v>
       </c>
       <c r="AB68">
-        <v>131.23671499948927</v>
+        <v>285.92124824980857</v>
       </c>
       <c r="AD68" t="s">
         <v>413</v>
@@ -15517,13 +15517,13 @@
         <v>802</v>
       </c>
       <c r="AN68" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO68">
-        <v>0.98933138074259364</v>
+        <v>0.9918951652662058</v>
       </c>
       <c r="AP68">
-        <v>195.59135305245039</v>
+        <v>148.58863678622743</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -15588,16 +15588,16 @@
         <v>532</v>
       </c>
       <c r="Y69" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="Z69" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="AA69">
-        <v>0.980949293282396</v>
+        <v>0.97996308088186879</v>
       </c>
       <c r="AB69">
-        <v>349.26295648940771</v>
+        <v>367.343517165739</v>
       </c>
       <c r="AD69" t="s">
         <v>413</v>
@@ -15627,13 +15627,13 @@
         <v>803</v>
       </c>
       <c r="AN69" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="AO69">
-        <v>0.98703324072992327</v>
+        <v>0.98531999116946412</v>
       </c>
       <c r="AP69">
-        <v>237.72391995140771</v>
+        <v>269.13349522649082</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -15698,16 +15698,16 @@
         <v>534</v>
       </c>
       <c r="Y70" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="Z70" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="AA70">
-        <v>0.98440429555001041</v>
+        <v>0.97636760270586087</v>
       </c>
       <c r="AB70">
-        <v>285.92124824980857</v>
+        <v>433.26061705921813</v>
       </c>
       <c r="AD70" t="s">
         <v>413</v>
@@ -15737,13 +15737,13 @@
         <v>804</v>
       </c>
       <c r="AN70" t="s">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="AO70">
-        <v>0.98653333840245183</v>
+        <v>0.99009266720704037</v>
       </c>
       <c r="AP70">
-        <v>246.88879595504923</v>
+        <v>181.63443453759336</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -15808,16 +15808,16 @@
         <v>536</v>
       </c>
       <c r="Y71" t="s">
-        <v>357</v>
+        <v>406</v>
       </c>
       <c r="Z71" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="AA71">
-        <v>0.97996308088186879</v>
+        <v>0.99165078812878382</v>
       </c>
       <c r="AB71">
-        <v>367.343517165739</v>
+        <v>153.06888430562992</v>
       </c>
       <c r="AD71" t="s">
         <v>413</v>
@@ -15847,13 +15847,13 @@
         <v>805</v>
       </c>
       <c r="AN71" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="AO71">
-        <v>0.96800325464323944</v>
+        <v>0.98371568181207825</v>
       </c>
       <c r="AP71">
-        <v>586.60699820727632</v>
+        <v>298.5458334452332</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -15918,16 +15918,16 @@
         <v>538</v>
       </c>
       <c r="Y72" t="s">
-        <v>386</v>
+        <v>353</v>
       </c>
       <c r="Z72" t="s">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="AA72">
-        <v>0.97636760270586087</v>
+        <v>0.97646479583958734</v>
       </c>
       <c r="AB72">
-        <v>433.26061705921813</v>
+        <v>431.47874294089837</v>
       </c>
       <c r="AD72" t="s">
         <v>413</v>
@@ -15957,13 +15957,13 @@
         <v>806</v>
       </c>
       <c r="AN72" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="AO72">
-        <v>0.98003745158806088</v>
+        <v>0.98435286039872183</v>
       </c>
       <c r="AP72">
-        <v>365.98005421888422</v>
+        <v>286.8642260234331</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16028,16 +16028,16 @@
         <v>540</v>
       </c>
       <c r="Y73" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="Z73" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="AA73">
-        <v>0.97272179131491798</v>
+        <v>0.96562135615554268</v>
       </c>
       <c r="AB73">
-        <v>500.10049255983796</v>
+        <v>630.27513714838358</v>
       </c>
       <c r="AD73" t="s">
         <v>413</v>
@@ -16067,13 +16067,13 @@
         <v>807</v>
       </c>
       <c r="AN73" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="AO73">
-        <v>0.98867603245018398</v>
+        <v>0.97655782887090981</v>
       </c>
       <c r="AP73">
-        <v>207.60607174662678</v>
+        <v>429.77313736665354</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -16138,16 +16138,16 @@
         <v>542</v>
       </c>
       <c r="Y74" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="Z74" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="AA74">
-        <v>0.98444284858889564</v>
+        <v>0.98843111817052332</v>
       </c>
       <c r="AB74">
-        <v>285.21444253691413</v>
+        <v>212.09616687373853</v>
       </c>
       <c r="AD74" t="s">
         <v>413</v>
@@ -16177,7 +16177,7 @@
         <v>808</v>
       </c>
       <c r="AN74" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO74">
         <v>0.98583529483105414</v>
@@ -16248,16 +16248,16 @@
         <v>544</v>
       </c>
       <c r="Y75" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="Z75" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="AA75">
-        <v>0.98269942042940017</v>
+        <v>0.99409930001823366</v>
       </c>
       <c r="AB75">
-        <v>317.17729212766454</v>
+        <v>108.17949966571678</v>
       </c>
       <c r="AD75" t="s">
         <v>413</v>
@@ -16287,7 +16287,7 @@
         <v>809</v>
       </c>
       <c r="AN75" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="AO75">
         <v>0.97176508181545596</v>
@@ -16358,16 +16358,16 @@
         <v>546</v>
       </c>
       <c r="Y76" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="Z76" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="AA76">
-        <v>0.98213943337265219</v>
+        <v>0.99045315399849054</v>
       </c>
       <c r="AB76">
-        <v>327.44372150137696</v>
+        <v>175.02551002767362</v>
       </c>
       <c r="AD76" t="s">
         <v>413</v>
@@ -16397,7 +16397,7 @@
         <v>810</v>
       </c>
       <c r="AN76" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO76">
         <v>0.99168257517392877</v>
@@ -16468,16 +16468,16 @@
         <v>548</v>
       </c>
       <c r="Y77" t="s">
-        <v>385</v>
+        <v>335</v>
       </c>
       <c r="Z77" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
       <c r="AA77">
-        <v>0.97970789283404214</v>
+        <v>0.98443531955055918</v>
       </c>
       <c r="AB77">
-        <v>372.02196470922701</v>
+        <v>285.35247490641569</v>
       </c>
       <c r="AD77" t="s">
         <v>413</v>
@@ -16507,7 +16507,7 @@
         <v>811</v>
       </c>
       <c r="AN77" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="AO77">
         <v>0.97961567568507724</v>
@@ -16578,16 +16578,16 @@
         <v>550</v>
       </c>
       <c r="Y78" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="Z78" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="AA78">
-        <v>0.98270299973748321</v>
+        <v>0.97398849158227818</v>
       </c>
       <c r="AB78">
-        <v>317.11167147947373</v>
+        <v>476.87765432490079</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -16652,16 +16652,16 @@
         <v>552</v>
       </c>
       <c r="Y79" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="Z79" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AA79">
-        <v>0.97598085885692565</v>
+        <v>0.98814122429339546</v>
       </c>
       <c r="AB79">
-        <v>440.3509209563627</v>
+        <v>217.4108879544159</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -16726,16 +16726,16 @@
         <v>554</v>
       </c>
       <c r="Y80" t="s">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="Z80" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AA80">
-        <v>0.97878284543380634</v>
+        <v>0.97065607524213282</v>
       </c>
       <c r="AB80">
-        <v>388.98116704688283</v>
+        <v>537.97195389423189</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -16800,16 +16800,16 @@
         <v>556</v>
       </c>
       <c r="Y81" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="Z81" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="AA81">
-        <v>0.9898744603534384</v>
+        <v>0.97916314637278834</v>
       </c>
       <c r="AB81">
-        <v>185.63489352029583</v>
+        <v>382.00898316554651</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -16874,16 +16874,16 @@
         <v>558</v>
       </c>
       <c r="Y82" t="s">
-        <v>336</v>
+        <v>393</v>
       </c>
       <c r="Z82" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AA82">
-        <v>0.98205187669897798</v>
+        <v>0.97545857121381951</v>
       </c>
       <c r="AB82">
-        <v>329.04892718540373</v>
+        <v>449.92619441330908</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -16948,16 +16948,16 @@
         <v>560</v>
       </c>
       <c r="Y83" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="Z83" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
       <c r="AA83">
-        <v>0.99142494197358011</v>
+        <v>0.98212250728249206</v>
       </c>
       <c r="AB83">
-        <v>157.20939715103142</v>
+        <v>327.75403315431197</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -17022,16 +17022,16 @@
         <v>562</v>
       </c>
       <c r="Y84" t="s">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="Z84" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="AA84">
-        <v>0.9807975141504387</v>
+        <v>0.99456410459052502</v>
       </c>
       <c r="AB84">
-        <v>352.04557390862351</v>
+        <v>99.658082507040461</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -17096,16 +17096,16 @@
         <v>564</v>
       </c>
       <c r="Y85" t="s">
-        <v>387</v>
+        <v>344</v>
       </c>
       <c r="Z85" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="AA85">
-        <v>0.98596629583708084</v>
+        <v>0.97891429500574301</v>
       </c>
       <c r="AB85">
-        <v>257.28457632018387</v>
+        <v>386.57125822804534</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -17170,16 +17170,16 @@
         <v>566</v>
       </c>
       <c r="Y86" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z86" t="s">
         <v>589</v>
       </c>
       <c r="AA86">
-        <v>0.99365868734102913</v>
+        <v>0.99086247853214549</v>
       </c>
       <c r="AB86">
-        <v>116.25739874780012</v>
+        <v>167.52122691066626</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -17244,16 +17244,16 @@
         <v>568</v>
       </c>
       <c r="Y87" t="s">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="Z87" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="AA87">
-        <v>0.98564262027093064</v>
+        <v>0.9839124944774571</v>
       </c>
       <c r="AB87">
-        <v>263.21862836627207</v>
+        <v>294.93760124661941</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -17318,16 +17318,16 @@
         <v>570</v>
       </c>
       <c r="Y88" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Z88" t="s">
-        <v>578</v>
+        <v>597</v>
       </c>
       <c r="AA88">
-        <v>0.99296984942213296</v>
+        <v>0.97678875799905829</v>
       </c>
       <c r="AB88">
-        <v>128.88609392756314</v>
+        <v>425.5394366839318</v>
       </c>
     </row>
   </sheetData>
@@ -17336,7 +17336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{294103D0-7DDA-417C-AECA-0EF0C0D7FA92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43274664-79B4-4115-BA76-BCCD51465C6E}">
   <dimension ref="B9:Z77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17448,7 +17448,7 @@
         <v>885</v>
       </c>
       <c r="K11" t="s">
-        <v>741</v>
+        <v>780</v>
       </c>
       <c r="L11">
         <v>29.7146465744454</v>
@@ -17481,7 +17481,7 @@
         <v>1019</v>
       </c>
       <c r="X11" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="Y11">
         <v>0.33825</v>
@@ -17516,7 +17516,7 @@
         <v>887</v>
       </c>
       <c r="K12" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="L12">
         <v>13.367096811591049</v>
@@ -17549,7 +17549,7 @@
         <v>1021</v>
       </c>
       <c r="X12" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="Y12">
         <v>10.88325</v>
@@ -17584,7 +17584,7 @@
         <v>889</v>
       </c>
       <c r="K13" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="L13">
         <v>24.156328337033791</v>
@@ -17617,7 +17617,7 @@
         <v>1023</v>
       </c>
       <c r="X13" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="Y13">
         <v>26.983499999999999</v>
@@ -17652,7 +17652,7 @@
         <v>891</v>
       </c>
       <c r="K14" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="L14">
         <v>16.006796560234815</v>
@@ -17685,7 +17685,7 @@
         <v>1025</v>
       </c>
       <c r="X14" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="Y14">
         <v>42.507750000000001</v>
@@ -17720,7 +17720,7 @@
         <v>893</v>
       </c>
       <c r="K15" t="s">
-        <v>798</v>
+        <v>773</v>
       </c>
       <c r="L15">
         <v>17.682358378036344</v>
@@ -17753,7 +17753,7 @@
         <v>1027</v>
       </c>
       <c r="X15" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="Y15">
         <v>24.900749999999999</v>
@@ -17788,7 +17788,7 @@
         <v>895</v>
       </c>
       <c r="K16" t="s">
-        <v>806</v>
+        <v>789</v>
       </c>
       <c r="L16">
         <v>29.492382648463739</v>
@@ -17821,7 +17821,7 @@
         <v>1029</v>
       </c>
       <c r="X16" t="s">
-        <v>860</v>
+        <v>882</v>
       </c>
       <c r="Y16">
         <v>18.545249999999999</v>
@@ -17856,7 +17856,7 @@
         <v>897</v>
       </c>
       <c r="K17" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
       <c r="L17">
         <v>8.6778699255653748</v>
@@ -17889,7 +17889,7 @@
         <v>1031</v>
       </c>
       <c r="X17" t="s">
-        <v>880</v>
+        <v>864</v>
       </c>
       <c r="Y17">
         <v>29.838000000000001</v>
@@ -17924,7 +17924,7 @@
         <v>899</v>
       </c>
       <c r="K18" t="s">
-        <v>765</v>
+        <v>801</v>
       </c>
       <c r="L18">
         <v>12.772248157772113</v>
@@ -17957,7 +17957,7 @@
         <v>1033</v>
       </c>
       <c r="X18" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="Y18">
         <v>58.689</v>
@@ -17992,7 +17992,7 @@
         <v>901</v>
       </c>
       <c r="K19" t="s">
-        <v>805</v>
+        <v>763</v>
       </c>
       <c r="L19">
         <v>11.876635800692616</v>
@@ -18025,7 +18025,7 @@
         <v>1035</v>
       </c>
       <c r="X19" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="Y19">
         <v>48.432000000000002</v>
@@ -18060,7 +18060,7 @@
         <v>903</v>
       </c>
       <c r="K20" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
       <c r="L20">
         <v>27.15579263061009</v>
@@ -18093,7 +18093,7 @@
         <v>1037</v>
       </c>
       <c r="X20" t="s">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="Y20">
         <v>47.794499999999999</v>
@@ -18128,7 +18128,7 @@
         <v>905</v>
       </c>
       <c r="K21" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="L21">
         <v>27.043339674957092</v>
@@ -18161,7 +18161,7 @@
         <v>1039</v>
       </c>
       <c r="X21" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="Y21">
         <v>7.1767500000000002</v>
@@ -18196,7 +18196,7 @@
         <v>907</v>
       </c>
       <c r="K22" t="s">
-        <v>804</v>
+        <v>762</v>
       </c>
       <c r="L22">
         <v>12.170927347824723</v>
@@ -18229,7 +18229,7 @@
         <v>1041</v>
       </c>
       <c r="X22" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="Y22">
         <v>8.1052499999999998</v>
@@ -18264,7 +18264,7 @@
         <v>909</v>
       </c>
       <c r="K23" t="s">
-        <v>789</v>
+        <v>756</v>
       </c>
       <c r="L23">
         <v>26.999240466622091</v>
@@ -18297,7 +18297,7 @@
         <v>1043</v>
       </c>
       <c r="X23" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="Y23">
         <v>9.3810000000000002</v>
@@ -18332,7 +18332,7 @@
         <v>911</v>
       </c>
       <c r="K24" t="s">
-        <v>766</v>
+        <v>802</v>
       </c>
       <c r="L24">
         <v>23.305350986470582</v>
@@ -18365,7 +18365,7 @@
         <v>1045</v>
       </c>
       <c r="X24" t="s">
-        <v>862</v>
+        <v>884</v>
       </c>
       <c r="Y24">
         <v>11.47575</v>
@@ -18400,7 +18400,7 @@
         <v>913</v>
       </c>
       <c r="K25" t="s">
-        <v>767</v>
+        <v>803</v>
       </c>
       <c r="L25">
         <v>19.293897715957783</v>
@@ -18433,7 +18433,7 @@
         <v>1047</v>
       </c>
       <c r="X25" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="Y25">
         <v>6.1372499999999999</v>
@@ -18501,7 +18501,7 @@
         <v>1049</v>
       </c>
       <c r="X26" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="Y26">
         <v>14.57325</v>
@@ -18536,7 +18536,7 @@
         <v>917</v>
       </c>
       <c r="K27" t="s">
-        <v>784</v>
+        <v>767</v>
       </c>
       <c r="L27">
         <v>3.1385663053565613</v>
@@ -18569,7 +18569,7 @@
         <v>1051</v>
       </c>
       <c r="X27" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="Y27">
         <v>10.491</v>
@@ -18604,7 +18604,7 @@
         <v>919</v>
       </c>
       <c r="K28" t="s">
-        <v>785</v>
+        <v>768</v>
       </c>
       <c r="L28">
         <v>4.0628682283884237</v>
@@ -18637,7 +18637,7 @@
         <v>1053</v>
       </c>
       <c r="X28" t="s">
-        <v>861</v>
+        <v>883</v>
       </c>
       <c r="Y28">
         <v>17.414249999999999</v>
@@ -18672,7 +18672,7 @@
         <v>921</v>
       </c>
       <c r="K29" t="s">
-        <v>745</v>
+        <v>784</v>
       </c>
       <c r="L29">
         <v>18.31221960055294</v>
@@ -18705,7 +18705,7 @@
         <v>1055</v>
       </c>
       <c r="X29" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="Y29">
         <v>10.968</v>
@@ -18740,7 +18740,7 @@
         <v>923</v>
       </c>
       <c r="K30" t="s">
-        <v>803</v>
+        <v>761</v>
       </c>
       <c r="L30">
         <v>27.91719839668141</v>
@@ -18773,7 +18773,7 @@
         <v>1057</v>
       </c>
       <c r="X30" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="Y30">
         <v>10.79175</v>
@@ -18808,7 +18808,7 @@
         <v>925</v>
       </c>
       <c r="K31" t="s">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="L31">
         <v>20.659184774772967</v>
@@ -18841,7 +18841,7 @@
         <v>1059</v>
       </c>
       <c r="X31" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="Y31">
         <v>20.114249999999998</v>
@@ -18876,7 +18876,7 @@
         <v>927</v>
       </c>
       <c r="K32" t="s">
-        <v>752</v>
+        <v>793</v>
       </c>
       <c r="L32">
         <v>1.6724491767694549</v>
@@ -18909,7 +18909,7 @@
         <v>1061</v>
       </c>
       <c r="X32" t="s">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="Y32">
         <v>44.373750000000001</v>
@@ -18944,7 +18944,7 @@
         <v>929</v>
       </c>
       <c r="K33" t="s">
-        <v>753</v>
+        <v>794</v>
       </c>
       <c r="L33">
         <v>13.9157416320151</v>
@@ -18977,7 +18977,7 @@
         <v>1063</v>
       </c>
       <c r="X33" t="s">
-        <v>882</v>
+        <v>866</v>
       </c>
       <c r="Y33">
         <v>18.57525</v>
@@ -19012,7 +19012,7 @@
         <v>931</v>
       </c>
       <c r="K34" t="s">
-        <v>807</v>
+        <v>790</v>
       </c>
       <c r="L34">
         <v>19.755004592887676</v>
@@ -19045,7 +19045,7 @@
         <v>1065</v>
       </c>
       <c r="X34" t="s">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="Y34">
         <v>18.241499999999998</v>
@@ -19080,7 +19080,7 @@
         <v>933</v>
       </c>
       <c r="K35" t="s">
-        <v>748</v>
+        <v>787</v>
       </c>
       <c r="L35">
         <v>14.794879040591612</v>
@@ -19115,7 +19115,7 @@
         <v>935</v>
       </c>
       <c r="K36" t="s">
-        <v>751</v>
+        <v>792</v>
       </c>
       <c r="L36">
         <v>6.2274748795149915</v>
@@ -19150,7 +19150,7 @@
         <v>937</v>
       </c>
       <c r="K37" t="s">
-        <v>742</v>
+        <v>781</v>
       </c>
       <c r="L37">
         <v>20.047482861417784</v>
@@ -19220,7 +19220,7 @@
         <v>941</v>
       </c>
       <c r="K39" t="s">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="L39">
         <v>25.823486809088088</v>
@@ -19255,7 +19255,7 @@
         <v>943</v>
       </c>
       <c r="K40" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="L40">
         <v>66.70158467196768</v>
@@ -19290,7 +19290,7 @@
         <v>945</v>
       </c>
       <c r="K41" t="s">
-        <v>796</v>
+        <v>771</v>
       </c>
       <c r="L41">
         <v>48.268110562179842</v>
@@ -19325,7 +19325,7 @@
         <v>947</v>
       </c>
       <c r="K42" t="s">
-        <v>776</v>
+        <v>747</v>
       </c>
       <c r="L42">
         <v>90.630298494129065</v>
@@ -19360,7 +19360,7 @@
         <v>949</v>
       </c>
       <c r="K43" t="s">
-        <v>774</v>
+        <v>745</v>
       </c>
       <c r="L43">
         <v>33.627820830597955</v>
@@ -19395,7 +19395,7 @@
         <v>951</v>
       </c>
       <c r="K44" t="s">
-        <v>802</v>
+        <v>760</v>
       </c>
       <c r="L44">
         <v>30.412670648726838</v>
@@ -19430,7 +19430,7 @@
         <v>953</v>
       </c>
       <c r="K45" t="s">
-        <v>790</v>
+        <v>804</v>
       </c>
       <c r="L45">
         <v>47.878917655816522</v>
@@ -19465,7 +19465,7 @@
         <v>955</v>
       </c>
       <c r="K46" t="s">
-        <v>795</v>
+        <v>770</v>
       </c>
       <c r="L46">
         <v>69.366510391046873</v>
@@ -19500,7 +19500,7 @@
         <v>957</v>
       </c>
       <c r="K47" t="s">
-        <v>793</v>
+        <v>807</v>
       </c>
       <c r="L47">
         <v>19.428837136062757</v>
@@ -19535,7 +19535,7 @@
         <v>959</v>
       </c>
       <c r="K48" t="s">
-        <v>788</v>
+        <v>755</v>
       </c>
       <c r="L48">
         <v>15.054857587707319</v>
@@ -19570,7 +19570,7 @@
         <v>961</v>
       </c>
       <c r="K49" t="s">
-        <v>770</v>
+        <v>797</v>
       </c>
       <c r="L49">
         <v>13.019602602156084</v>
@@ -19605,7 +19605,7 @@
         <v>963</v>
       </c>
       <c r="K50" t="s">
-        <v>781</v>
+        <v>752</v>
       </c>
       <c r="L50">
         <v>25.094411791551167</v>
@@ -19640,7 +19640,7 @@
         <v>965</v>
       </c>
       <c r="K51" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="L51">
         <v>10.512568509966947</v>
@@ -19675,7 +19675,7 @@
         <v>967</v>
       </c>
       <c r="K52" t="s">
-        <v>792</v>
+        <v>806</v>
       </c>
       <c r="L52">
         <v>19.484319735030326</v>
@@ -19710,7 +19710,7 @@
         <v>969</v>
       </c>
       <c r="K53" t="s">
-        <v>744</v>
+        <v>783</v>
       </c>
       <c r="L53">
         <v>10.300130106481824</v>
@@ -19745,7 +19745,7 @@
         <v>971</v>
       </c>
       <c r="K54" t="s">
-        <v>780</v>
+        <v>751</v>
       </c>
       <c r="L54">
         <v>38.113797875314695</v>
@@ -19780,7 +19780,7 @@
         <v>973</v>
       </c>
       <c r="K55" t="s">
-        <v>799</v>
+        <v>774</v>
       </c>
       <c r="L55">
         <v>48.324816212675138</v>
@@ -19815,7 +19815,7 @@
         <v>975</v>
       </c>
       <c r="K56" t="s">
-        <v>786</v>
+        <v>753</v>
       </c>
       <c r="L56">
         <v>69.883597189706848</v>
@@ -19850,7 +19850,7 @@
         <v>977</v>
       </c>
       <c r="K57" t="s">
-        <v>750</v>
+        <v>791</v>
       </c>
       <c r="L57">
         <v>65.706815294563484</v>
@@ -19885,7 +19885,7 @@
         <v>979</v>
       </c>
       <c r="K58" t="s">
-        <v>737</v>
+        <v>776</v>
       </c>
       <c r="L58">
         <v>55.231206871897385</v>
@@ -19920,7 +19920,7 @@
         <v>981</v>
       </c>
       <c r="K59" t="s">
-        <v>738</v>
+        <v>777</v>
       </c>
       <c r="L59">
         <v>19.970554339652629</v>
@@ -19990,7 +19990,7 @@
         <v>985</v>
       </c>
       <c r="K61" t="s">
-        <v>794</v>
+        <v>769</v>
       </c>
       <c r="L61">
         <v>44.220292794619994</v>
@@ -20025,7 +20025,7 @@
         <v>987</v>
       </c>
       <c r="K62" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
       <c r="L62">
         <v>39.277945374969107</v>
@@ -20060,7 +20060,7 @@
         <v>989</v>
       </c>
       <c r="K63" t="s">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="L63">
         <v>59.341737840109467</v>
@@ -20095,7 +20095,7 @@
         <v>991</v>
       </c>
       <c r="K64" t="s">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="L64">
         <v>29.191927665826828</v>
@@ -20130,7 +20130,7 @@
         <v>993</v>
       </c>
       <c r="K65" t="s">
-        <v>739</v>
+        <v>778</v>
       </c>
       <c r="L65">
         <v>39.617260419426948</v>
@@ -20165,7 +20165,7 @@
         <v>995</v>
       </c>
       <c r="K66" t="s">
-        <v>782</v>
+        <v>765</v>
       </c>
       <c r="L66">
         <v>47.296862636729713</v>
@@ -20200,7 +20200,7 @@
         <v>997</v>
       </c>
       <c r="K67" t="s">
-        <v>756</v>
+        <v>737</v>
       </c>
       <c r="L67">
         <v>23.350121881103082</v>
@@ -20235,7 +20235,7 @@
         <v>999</v>
       </c>
       <c r="K68" t="s">
-        <v>746</v>
+        <v>785</v>
       </c>
       <c r="L68">
         <v>15.401477961960474</v>
@@ -20270,7 +20270,7 @@
         <v>1001</v>
       </c>
       <c r="K69" t="s">
-        <v>787</v>
+        <v>754</v>
       </c>
       <c r="L69">
         <v>10.395885695189069</v>
@@ -20305,7 +20305,7 @@
         <v>1003</v>
       </c>
       <c r="K70" t="s">
-        <v>778</v>
+        <v>749</v>
       </c>
       <c r="L70">
         <v>23.89105636564183</v>
@@ -20340,7 +20340,7 @@
         <v>1005</v>
       </c>
       <c r="K71" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="L71">
         <v>18.959710131684457</v>
@@ -20375,7 +20375,7 @@
         <v>1007</v>
       </c>
       <c r="K72" t="s">
-        <v>783</v>
+        <v>766</v>
       </c>
       <c r="L72">
         <v>6.6550975614073966</v>
@@ -20410,7 +20410,7 @@
         <v>1009</v>
       </c>
       <c r="K73" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="L73">
         <v>13.961943802326671</v>
@@ -20480,7 +20480,7 @@
         <v>1013</v>
       </c>
       <c r="K75" t="s">
-        <v>801</v>
+        <v>759</v>
       </c>
       <c r="L75">
         <v>21.246092446368579</v>
@@ -20515,7 +20515,7 @@
         <v>1015</v>
       </c>
       <c r="K76" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="L76">
         <v>19.51059121972445</v>
@@ -20550,7 +20550,7 @@
         <v>1017</v>
       </c>
       <c r="K77" t="s">
-        <v>764</v>
+        <v>800</v>
       </c>
       <c r="L77">
         <v>30.378621105864486</v>
@@ -20565,7 +20565,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A840AB1-3774-4AF5-BCF6-4F30E38C3738}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E095C656-32EC-483F-A9C0-C875B69C0001}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CBB9906-CB17-495E-8C05-0A6EEE587B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B4E58F1-24A1-4171-A463-E57C638FF96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1371,18 +1371,30 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_077</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 77</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_023</t>
   </si>
   <si>
@@ -1395,6 +1407,210 @@
     <t>connecting solar to buses in cluster 55</t>
   </si>
   <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_078</t>
   </si>
   <si>
@@ -1425,6 +1641,90 @@
     <t>connecting solar to buses in cluster 51</t>
   </si>
   <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_006</t>
   </si>
   <si>
@@ -1479,6 +1779,36 @@
     <t>connecting solar to buses in cluster 41</t>
   </si>
   <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_031</t>
   </si>
   <si>
@@ -1515,342 +1845,18 @@
     <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_gen1,e_dem0</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem2</t>
+  </si>
+  <si>
     <t>e_dem1,e_gen2</t>
   </si>
   <si>
@@ -1860,84 +1866,78 @@
     <t>e_gen3</t>
   </si>
   <si>
+    <t>e_gen1</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem0,e_dem2</t>
+  </si>
+  <si>
+    <t>e_dem1</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen0</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem4,e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem2</t>
+  </si>
+  <si>
+    <t>e_dem3,e_gen2,e_dem4</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem1</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen4</t>
+  </si>
+  <si>
+    <t>e_dem3,e_gen3</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen0</t>
+  </si>
+  <si>
+    <t>e_dem3</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem0</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem3</t>
+  </si>
+  <si>
     <t>e_dem4</t>
   </si>
   <si>
     <t>e_dem3,e_dem4</t>
   </si>
   <si>
-    <t>e_dem3</t>
+    <t>e_dem0</t>
+  </si>
+  <si>
+    <t>e_gen2</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem4</t>
   </si>
   <si>
     <t>e_gen1,e_dem3,e_dem0</t>
   </si>
   <si>
-    <t>e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen0</t>
-  </si>
-  <si>
-    <t>e_gen1</t>
-  </si>
-  <si>
     <t>e_dem3,e_dem0,e_gen3</t>
   </si>
   <si>
-    <t>e_gen2,e_dem4</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen3</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem2</t>
-  </si>
-  <si>
-    <t>e_dem0</t>
-  </si>
-  <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem4,e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen0</t>
-  </si>
-  <si>
-    <t>e_gen4,e_dem0</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen4</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen2,e_dem4</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem1</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_057</t>
   </si>
   <si>
@@ -1980,6 +1980,336 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_033</t>
   </si>
   <si>
@@ -2010,336 +2340,6 @@
     <t>connecting wind onshore to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
     <t>elc_won_057</t>
   </si>
   <si>
@@ -2364,6 +2364,183 @@
     <t>elc_won_010</t>
   </si>
   <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen2</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>e_dem0,e_dem3</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_065</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem4</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_dem1,e_gen2,e_dem4</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
     <t>elc_won_033</t>
   </si>
   <si>
@@ -2388,181 +2565,58 @@
     <t>elc_won_040</t>
   </si>
   <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>elc_won_065</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen2</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>elc_won_066</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen2,e_dem4</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>e_dem0,e_dem3</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem4</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_067</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>elc_won_050</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wofelc_wof_012</t>
@@ -2577,16 +2631,64 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wofelc_wof_007</t>
@@ -2607,106 +2709,31 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
   </si>
   <si>
     <t>elc_wof_012</t>
@@ -2715,10 +2742,37 @@
     <t>elc_wof_003</t>
   </si>
   <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_dem3,e_gen2</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
   </si>
   <si>
     <t>elc_wof_007</t>
@@ -2728,60 +2782,6 @@
   </si>
   <si>
     <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen2</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -8106,7 +8106,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFF78516-ED72-45F7-B4FE-9B12C31A5B5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B1F613-F675-4806-8DEB-1BD6A9EE63DF}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8344,16 +8344,16 @@
         <v>414</v>
       </c>
       <c r="Y11" t="s">
-        <v>410</v>
+        <v>348</v>
       </c>
       <c r="Z11" t="s">
         <v>574</v>
       </c>
       <c r="AA11">
-        <v>0.99395293926735107</v>
+        <v>0.98338655524515672</v>
       </c>
       <c r="AB11">
-        <v>110.86278009856306</v>
+        <v>304.57982050546099</v>
       </c>
       <c r="AD11" t="s">
         <v>413</v>
@@ -8419,13 +8419,13 @@
         <v>860</v>
       </c>
       <c r="BB11" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="BC11">
-        <v>0.97204337209146163</v>
+        <v>0.97443086368153087</v>
       </c>
       <c r="BD11">
-        <v>512.53817832320431</v>
+        <v>468.76749917193416</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8490,16 +8490,16 @@
         <v>418</v>
       </c>
       <c r="Y12" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="Z12" t="s">
         <v>575</v>
       </c>
       <c r="AA12">
-        <v>0.98304303411255212</v>
+        <v>0.97813651992719985</v>
       </c>
       <c r="AB12">
-        <v>310.87770793654443</v>
+        <v>400.83046800133633</v>
       </c>
       <c r="AD12" t="s">
         <v>413</v>
@@ -8529,7 +8529,7 @@
         <v>739</v>
       </c>
       <c r="AN12" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="AO12">
         <v>0.98832832974245843</v>
@@ -8568,10 +8568,10 @@
         <v>596</v>
       </c>
       <c r="BC12">
-        <v>0.97090678081281612</v>
+        <v>0.97367031900560153</v>
       </c>
       <c r="BD12">
-        <v>533.37568509837058</v>
+        <v>482.71081823063838</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8636,16 +8636,16 @@
         <v>420</v>
       </c>
       <c r="Y13" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="Z13" t="s">
         <v>576</v>
       </c>
       <c r="AA13">
-        <v>0.9902907805210438</v>
+        <v>0.99395293926735107</v>
       </c>
       <c r="AB13">
-        <v>178.00235711419791</v>
+        <v>110.86278009856306</v>
       </c>
       <c r="AD13" t="s">
         <v>413</v>
@@ -8675,7 +8675,7 @@
         <v>740</v>
       </c>
       <c r="AN13" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="AO13">
         <v>0.98934334912020028</v>
@@ -8711,13 +8711,13 @@
         <v>862</v>
       </c>
       <c r="BB13" t="s">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="BC13">
-        <v>0.96271559874449242</v>
+        <v>0.96683718298551269</v>
       </c>
       <c r="BD13">
-        <v>683.54735635097268</v>
+        <v>607.98497859893303</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8782,16 +8782,16 @@
         <v>422</v>
       </c>
       <c r="Y14" t="s">
-        <v>411</v>
+        <v>356</v>
       </c>
       <c r="Z14" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AA14">
-        <v>0.99062084979042209</v>
+        <v>0.98304303411255212</v>
       </c>
       <c r="AB14">
-        <v>171.95108717559444</v>
+        <v>310.87770793654443</v>
       </c>
       <c r="AD14" t="s">
         <v>413</v>
@@ -8821,7 +8821,7 @@
         <v>741</v>
       </c>
       <c r="AN14" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AO14">
         <v>0.99072024613784004</v>
@@ -8857,13 +8857,13 @@
         <v>863</v>
       </c>
       <c r="BB14" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="BC14">
-        <v>0.97945251828158475</v>
+        <v>0.96781631663497858</v>
       </c>
       <c r="BD14">
-        <v>376.70383150428029</v>
+        <v>590.03419502539236</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8928,16 +8928,16 @@
         <v>424</v>
       </c>
       <c r="Y15" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="Z15" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AA15">
-        <v>0.98254903847705999</v>
+        <v>0.9902907805210438</v>
       </c>
       <c r="AB15">
-        <v>319.93429458723335</v>
+        <v>178.00235711419791</v>
       </c>
       <c r="AD15" t="s">
         <v>413</v>
@@ -8967,7 +8967,7 @@
         <v>742</v>
       </c>
       <c r="AN15" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="AO15">
         <v>0.97416703287609641</v>
@@ -9003,13 +9003,13 @@
         <v>864</v>
       </c>
       <c r="BB15" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="BC15">
-        <v>0.96884606421228714</v>
+        <v>0.96501685329080267</v>
       </c>
       <c r="BD15">
-        <v>571.15548944140187</v>
+        <v>641.35768966861792</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9074,16 +9074,16 @@
         <v>426</v>
       </c>
       <c r="Y16" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="Z16" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AA16">
-        <v>0.97646711233585171</v>
+        <v>0.99382288375189876</v>
       </c>
       <c r="AB16">
-        <v>431.43627384271826</v>
+        <v>113.24713121519014</v>
       </c>
       <c r="AD16" t="s">
         <v>413</v>
@@ -9113,7 +9113,7 @@
         <v>743</v>
       </c>
       <c r="AN16" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="AO16">
         <v>0.97182188871578934</v>
@@ -9149,13 +9149,13 @@
         <v>865</v>
       </c>
       <c r="BB16" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="BC16">
-        <v>0.97158773589553182</v>
+        <v>0.97197172623840289</v>
       </c>
       <c r="BD16">
-        <v>520.89150858191567</v>
+        <v>513.8516856292805</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9220,16 +9220,16 @@
         <v>428</v>
       </c>
       <c r="Y17" t="s">
-        <v>397</v>
+        <v>359</v>
       </c>
       <c r="Z17" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="AA17">
-        <v>0.9863634971037446</v>
+        <v>0.97000043567738925</v>
       </c>
       <c r="AB17">
-        <v>250.00255309801472</v>
+        <v>549.99201258119717</v>
       </c>
       <c r="AD17" t="s">
         <v>413</v>
@@ -9259,7 +9259,7 @@
         <v>744</v>
       </c>
       <c r="AN17" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="AO17">
         <v>0.97902953573897011</v>
@@ -9295,13 +9295,13 @@
         <v>866</v>
       </c>
       <c r="BB17" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="BC17">
-        <v>0.96837970323216338</v>
+        <v>0.98010852330645815</v>
       </c>
       <c r="BD17">
-        <v>579.70544074367149</v>
+        <v>364.67707271493384</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9366,16 +9366,16 @@
         <v>430</v>
       </c>
       <c r="Y18" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="Z18" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="AA18">
-        <v>0.98024768078410096</v>
+        <v>0.99165078812878382</v>
       </c>
       <c r="AB18">
-        <v>362.12585229148283</v>
+        <v>153.06888430562992</v>
       </c>
       <c r="AD18" t="s">
         <v>413</v>
@@ -9405,13 +9405,13 @@
         <v>745</v>
       </c>
       <c r="AN18" t="s">
-        <v>746</v>
+        <v>589</v>
       </c>
       <c r="AO18">
-        <v>0.97223070787085453</v>
+        <v>0.98893828971746323</v>
       </c>
       <c r="AP18">
-        <v>509.10368903433471</v>
+        <v>202.7980218465068</v>
       </c>
       <c r="AR18" t="s">
         <v>413</v>
@@ -9441,13 +9441,13 @@
         <v>867</v>
       </c>
       <c r="BB18" t="s">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="BC18">
-        <v>0.98427567578715769</v>
+        <v>0.96271559874449242</v>
       </c>
       <c r="BD18">
-        <v>288.27927723544332</v>
+        <v>683.54735635097268</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9512,16 +9512,16 @@
         <v>432</v>
       </c>
       <c r="Y19" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="Z19" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="AA19">
-        <v>0.97878284543380634</v>
+        <v>0.97646479583958734</v>
       </c>
       <c r="AB19">
-        <v>388.98116704688283</v>
+        <v>431.47874294089837</v>
       </c>
       <c r="AD19" t="s">
         <v>413</v>
@@ -9548,16 +9548,16 @@
         <v>619</v>
       </c>
       <c r="AM19" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AN19" t="s">
-        <v>748</v>
+        <v>584</v>
       </c>
       <c r="AO19">
-        <v>0.99323428174300499</v>
+        <v>0.99417752457368125</v>
       </c>
       <c r="AP19">
-        <v>124.03816804490805</v>
+        <v>106.74538281584397</v>
       </c>
       <c r="AR19" t="s">
         <v>413</v>
@@ -9587,13 +9587,13 @@
         <v>868</v>
       </c>
       <c r="BB19" t="s">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="BC19">
-        <v>0.96683718298551269</v>
+        <v>0.97945251828158475</v>
       </c>
       <c r="BD19">
-        <v>607.98497859893303</v>
+        <v>376.70383150428029</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9658,16 +9658,16 @@
         <v>434</v>
       </c>
       <c r="Y20" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="Z20" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AA20">
-        <v>0.9898744603534384</v>
+        <v>0.96562135615554268</v>
       </c>
       <c r="AB20">
-        <v>185.63489352029583</v>
+        <v>630.27513714838358</v>
       </c>
       <c r="AD20" t="s">
         <v>413</v>
@@ -9694,16 +9694,16 @@
         <v>621</v>
       </c>
       <c r="AM20" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="AN20" t="s">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="AO20">
-        <v>0.97340237375196048</v>
+        <v>0.98213512486164511</v>
       </c>
       <c r="AP20">
-        <v>487.62314788072359</v>
+        <v>327.5227108698395</v>
       </c>
       <c r="AR20" t="s">
         <v>413</v>
@@ -9733,13 +9733,13 @@
         <v>869</v>
       </c>
       <c r="BB20" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="BC20">
-        <v>0.96781631663497858</v>
+        <v>0.97204337209146163</v>
       </c>
       <c r="BD20">
-        <v>590.03419502539236</v>
+        <v>512.53817832320431</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9804,16 +9804,16 @@
         <v>436</v>
       </c>
       <c r="Y21" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="Z21" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AA21">
-        <v>0.98205187669897798</v>
+        <v>0.98843111817052332</v>
       </c>
       <c r="AB21">
-        <v>329.04892718540373</v>
+        <v>212.09616687373853</v>
       </c>
       <c r="AD21" t="s">
         <v>413</v>
@@ -9840,16 +9840,16 @@
         <v>623</v>
       </c>
       <c r="AM21" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="AN21" t="s">
-        <v>577</v>
+        <v>749</v>
       </c>
       <c r="AO21">
-        <v>0.98709698070191276</v>
+        <v>0.98305809009413248</v>
       </c>
       <c r="AP21">
-        <v>236.55535379826514</v>
+        <v>310.60168160757155</v>
       </c>
       <c r="AR21" t="s">
         <v>413</v>
@@ -9879,13 +9879,13 @@
         <v>870</v>
       </c>
       <c r="BB21" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="BC21">
-        <v>0.9781715029140422</v>
+        <v>0.97090678081281612</v>
       </c>
       <c r="BD21">
-        <v>400.18911324255913</v>
+        <v>533.37568509837058</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9950,16 +9950,16 @@
         <v>438</v>
       </c>
       <c r="Y22" t="s">
-        <v>400</v>
+        <v>337</v>
       </c>
       <c r="Z22" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="AA22">
-        <v>0.99142494197358011</v>
+        <v>0.98823937652699512</v>
       </c>
       <c r="AB22">
-        <v>157.20939715103142</v>
+        <v>215.61143033842296</v>
       </c>
       <c r="AD22" t="s">
         <v>413</v>
@@ -9986,16 +9986,16 @@
         <v>625</v>
       </c>
       <c r="AM22" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="AN22" t="s">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="AO22">
-        <v>0.97913435966240669</v>
+        <v>0.99584474408886259</v>
       </c>
       <c r="AP22">
-        <v>382.53673952254371</v>
+        <v>76.179691704186226</v>
       </c>
       <c r="AR22" t="s">
         <v>413</v>
@@ -10025,7 +10025,7 @@
         <v>871</v>
       </c>
       <c r="BB22" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="BC22">
         <v>0.96139268083002405</v>
@@ -10096,16 +10096,16 @@
         <v>440</v>
       </c>
       <c r="Y23" t="s">
-        <v>399</v>
+        <v>347</v>
       </c>
       <c r="Z23" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="AA23">
-        <v>0.9807975141504387</v>
+        <v>0.97307234437114887</v>
       </c>
       <c r="AB23">
-        <v>352.04557390862351</v>
+        <v>493.6736865289368</v>
       </c>
       <c r="AD23" t="s">
         <v>413</v>
@@ -10132,16 +10132,16 @@
         <v>627</v>
       </c>
       <c r="AM23" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AN23" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AO23">
-        <v>0.9802768549486589</v>
+        <v>0.9771067451947747</v>
       </c>
       <c r="AP23">
-        <v>361.5909926079201</v>
+        <v>419.70967142912968</v>
       </c>
       <c r="AR23" t="s">
         <v>413</v>
@@ -10242,16 +10242,16 @@
         <v>442</v>
       </c>
       <c r="Y24" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="Z24" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="AA24">
-        <v>0.98596629583708084</v>
+        <v>0.97831141720185744</v>
       </c>
       <c r="AB24">
-        <v>257.28457632018387</v>
+        <v>397.62401796594617</v>
       </c>
       <c r="AD24" t="s">
         <v>413</v>
@@ -10278,16 +10278,16 @@
         <v>629</v>
       </c>
       <c r="AM24" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AN24" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="AO24">
-        <v>0.97414990055259076</v>
+        <v>0.97431371456908866</v>
       </c>
       <c r="AP24">
-        <v>473.91848986916989</v>
+        <v>470.91523290004181</v>
       </c>
       <c r="AR24" t="s">
         <v>413</v>
@@ -10317,13 +10317,13 @@
         <v>874</v>
       </c>
       <c r="BB24" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="BC24">
-        <v>0.97443086368153087</v>
+        <v>0.98427567578715769</v>
       </c>
       <c r="BD24">
-        <v>468.76749917193416</v>
+        <v>288.27927723544332</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10388,16 +10388,16 @@
         <v>444</v>
       </c>
       <c r="Y25" t="s">
-        <v>390</v>
+        <v>352</v>
       </c>
       <c r="Z25" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="AA25">
-        <v>0.99365868734102913</v>
+        <v>0.9753018595470957</v>
       </c>
       <c r="AB25">
-        <v>116.25739874780012</v>
+        <v>452.79924163657859</v>
       </c>
       <c r="AD25" t="s">
         <v>413</v>
@@ -10424,16 +10424,16 @@
         <v>631</v>
       </c>
       <c r="AM25" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="AN25" t="s">
-        <v>576</v>
+        <v>754</v>
       </c>
       <c r="AO25">
-        <v>0.98705643087911032</v>
+        <v>0.97968688829580564</v>
       </c>
       <c r="AP25">
-        <v>237.29876721631038</v>
+        <v>372.40704791023012</v>
       </c>
       <c r="AR25" t="s">
         <v>413</v>
@@ -10463,13 +10463,13 @@
         <v>875</v>
       </c>
       <c r="BB25" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="BC25">
-        <v>0.97367031900560153</v>
+        <v>0.9781715029140422</v>
       </c>
       <c r="BD25">
-        <v>482.71081823063838</v>
+        <v>400.18911324255913</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10534,16 +10534,16 @@
         <v>446</v>
       </c>
       <c r="Y26" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="Z26" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="AA26">
-        <v>0.98564262027093064</v>
+        <v>0.98694170150784422</v>
       </c>
       <c r="AB26">
-        <v>263.21862836627207</v>
+        <v>239.40213902285669</v>
       </c>
       <c r="AD26" t="s">
         <v>413</v>
@@ -10570,16 +10570,16 @@
         <v>633</v>
       </c>
       <c r="AM26" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AN26" t="s">
         <v>581</v>
       </c>
       <c r="AO26">
-        <v>0.98989284585574766</v>
+        <v>0.98420825457429406</v>
       </c>
       <c r="AP26">
-        <v>185.29782597795898</v>
+        <v>289.51533280460853</v>
       </c>
       <c r="AR26" t="s">
         <v>413</v>
@@ -10609,13 +10609,13 @@
         <v>876</v>
       </c>
       <c r="BB26" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="BC26">
-        <v>0.97048325247055856</v>
+        <v>0.96827543539739536</v>
       </c>
       <c r="BD26">
-        <v>541.14037137309333</v>
+        <v>581.61701771441915</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10680,16 +10680,16 @@
         <v>448</v>
       </c>
       <c r="Y27" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="Z27" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA27">
-        <v>0.99296984942213296</v>
+        <v>0.98336988732579877</v>
       </c>
       <c r="AB27">
-        <v>128.88609392756314</v>
+        <v>304.88539902702166</v>
       </c>
       <c r="AD27" t="s">
         <v>413</v>
@@ -10716,16 +10716,16 @@
         <v>635</v>
       </c>
       <c r="AM27" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AN27" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="AO27">
-        <v>0.99054353037519915</v>
+        <v>0.98302364254854535</v>
       </c>
       <c r="AP27">
-        <v>173.36860978801644</v>
+        <v>311.23321994333526</v>
       </c>
       <c r="AR27" t="s">
         <v>413</v>
@@ -10755,13 +10755,13 @@
         <v>877</v>
       </c>
       <c r="BB27" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="BC27">
-        <v>0.96692898910976954</v>
+        <v>0.96595696185315882</v>
       </c>
       <c r="BD27">
-        <v>606.30186632089146</v>
+        <v>624.12236602542168</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10826,16 +10826,16 @@
         <v>450</v>
       </c>
       <c r="Y28" t="s">
-        <v>364</v>
+        <v>393</v>
       </c>
       <c r="Z28" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="AA28">
-        <v>0.98042255120792365</v>
+        <v>0.97545857121381951</v>
       </c>
       <c r="AB28">
-        <v>358.91989452139876</v>
+        <v>449.92619441330908</v>
       </c>
       <c r="AD28" t="s">
         <v>413</v>
@@ -10862,16 +10862,16 @@
         <v>637</v>
       </c>
       <c r="AM28" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AN28" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="AO28">
-        <v>0.9768934332867476</v>
+        <v>0.97612238282801922</v>
       </c>
       <c r="AP28">
-        <v>423.6203897429599</v>
+        <v>437.75631481964848</v>
       </c>
       <c r="AR28" t="s">
         <v>413</v>
@@ -10901,13 +10901,13 @@
         <v>878</v>
       </c>
       <c r="BB28" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="BC28">
-        <v>0.97481390334887996</v>
+        <v>0.98341789520181955</v>
       </c>
       <c r="BD28">
-        <v>461.74510527053314</v>
+        <v>304.0052546333078</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10972,16 +10972,16 @@
         <v>452</v>
       </c>
       <c r="Y29" t="s">
-        <v>343</v>
+        <v>409</v>
       </c>
       <c r="Z29" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="AA29">
-        <v>0.98981198518654634</v>
+        <v>0.98212250728249206</v>
       </c>
       <c r="AB29">
-        <v>186.78027157998449</v>
+        <v>327.75403315431197</v>
       </c>
       <c r="AD29" t="s">
         <v>413</v>
@@ -11008,16 +11008,16 @@
         <v>639</v>
       </c>
       <c r="AM29" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AN29" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="AO29">
-        <v>0.97612238282801922</v>
+        <v>0.98933138074259364</v>
       </c>
       <c r="AP29">
-        <v>437.75631481964848</v>
+        <v>195.59135305245039</v>
       </c>
       <c r="AR29" t="s">
         <v>413</v>
@@ -11047,13 +11047,13 @@
         <v>879</v>
       </c>
       <c r="BB29" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="BC29">
-        <v>0.98341789520181955</v>
+        <v>0.97048325247055856</v>
       </c>
       <c r="BD29">
-        <v>304.0052546333078</v>
+        <v>541.14037137309333</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11118,16 +11118,16 @@
         <v>454</v>
       </c>
       <c r="Y30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Z30" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="AA30">
-        <v>0.97580984429062223</v>
+        <v>0.99456410459052502</v>
       </c>
       <c r="AB30">
-        <v>443.48618800525958</v>
+        <v>99.658082507040461</v>
       </c>
       <c r="AD30" t="s">
         <v>413</v>
@@ -11154,16 +11154,16 @@
         <v>641</v>
       </c>
       <c r="AM30" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AN30" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="AO30">
-        <v>0.98933138074259364</v>
+        <v>0.98703324072992327</v>
       </c>
       <c r="AP30">
-        <v>195.59135305245039</v>
+        <v>237.72391995140771</v>
       </c>
       <c r="AR30" t="s">
         <v>413</v>
@@ -11193,13 +11193,13 @@
         <v>880</v>
       </c>
       <c r="BB30" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="BC30">
-        <v>0.96827543539739536</v>
+        <v>0.96692898910976954</v>
       </c>
       <c r="BD30">
-        <v>581.61701771441915</v>
+        <v>606.30186632089146</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11264,16 +11264,16 @@
         <v>456</v>
       </c>
       <c r="Y31" t="s">
-        <v>403</v>
+        <v>344</v>
       </c>
       <c r="Z31" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="AA31">
-        <v>0.98738988106093839</v>
+        <v>0.97891429500574301</v>
       </c>
       <c r="AB31">
-        <v>231.18551388279656</v>
+        <v>386.57125822804534</v>
       </c>
       <c r="AD31" t="s">
         <v>413</v>
@@ -11300,16 +11300,16 @@
         <v>643</v>
       </c>
       <c r="AM31" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AN31" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="AO31">
-        <v>0.98703324072992327</v>
+        <v>0.98653333840245183</v>
       </c>
       <c r="AP31">
-        <v>237.72391995140771</v>
+        <v>246.88879595504923</v>
       </c>
       <c r="AR31" t="s">
         <v>413</v>
@@ -11342,10 +11342,10 @@
         <v>581</v>
       </c>
       <c r="BC31">
-        <v>0.96595696185315882</v>
+        <v>0.97481390334887996</v>
       </c>
       <c r="BD31">
-        <v>624.12236602542168</v>
+        <v>461.74510527053314</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11410,16 +11410,16 @@
         <v>458</v>
       </c>
       <c r="Y32" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="Z32" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AA32">
-        <v>0.97723778280633045</v>
+        <v>0.99086247853214549</v>
       </c>
       <c r="AB32">
-        <v>417.30731521727455</v>
+        <v>167.52122691066626</v>
       </c>
       <c r="AD32" t="s">
         <v>413</v>
@@ -11446,16 +11446,16 @@
         <v>645</v>
       </c>
       <c r="AM32" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AN32" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="AO32">
-        <v>0.98653333840245183</v>
+        <v>0.96800325464323944</v>
       </c>
       <c r="AP32">
-        <v>246.88879595504923</v>
+        <v>586.60699820727632</v>
       </c>
       <c r="AR32" t="s">
         <v>413</v>
@@ -11485,13 +11485,13 @@
         <v>882</v>
       </c>
       <c r="BB32" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="BC32">
-        <v>0.96501685329080267</v>
+        <v>0.96884606421228714</v>
       </c>
       <c r="BD32">
-        <v>641.35768966861792</v>
+        <v>571.15548944140187</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11556,16 +11556,16 @@
         <v>460</v>
       </c>
       <c r="Y33" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="Z33" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="AA33">
-        <v>0.99035601519017957</v>
+        <v>0.9839124944774571</v>
       </c>
       <c r="AB33">
-        <v>176.80638818004016</v>
+        <v>294.93760124661941</v>
       </c>
       <c r="AD33" t="s">
         <v>413</v>
@@ -11592,16 +11592,16 @@
         <v>647</v>
       </c>
       <c r="AM33" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AN33" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="AO33">
-        <v>0.96800325464323944</v>
+        <v>0.99009266720704037</v>
       </c>
       <c r="AP33">
-        <v>586.60699820727632</v>
+        <v>181.63443453759336</v>
       </c>
       <c r="AR33" t="s">
         <v>413</v>
@@ -11631,13 +11631,13 @@
         <v>883</v>
       </c>
       <c r="BB33" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="BC33">
-        <v>0.97197172623840289</v>
+        <v>0.97158773589553182</v>
       </c>
       <c r="BD33">
-        <v>513.8516856292805</v>
+        <v>520.89150858191567</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11702,16 +11702,16 @@
         <v>462</v>
       </c>
       <c r="Y34" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="Z34" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="AA34">
-        <v>0.97970789283404214</v>
+        <v>0.97678875799905829</v>
       </c>
       <c r="AB34">
-        <v>372.02196470922701</v>
+        <v>425.5394366839318</v>
       </c>
       <c r="AD34" t="s">
         <v>413</v>
@@ -11738,16 +11738,16 @@
         <v>649</v>
       </c>
       <c r="AM34" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AN34" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AO34">
-        <v>0.98893828971746323</v>
+        <v>0.98371568181207825</v>
       </c>
       <c r="AP34">
-        <v>202.7980218465068</v>
+        <v>298.5458334452332</v>
       </c>
       <c r="AR34" t="s">
         <v>413</v>
@@ -11777,13 +11777,13 @@
         <v>884</v>
       </c>
       <c r="BB34" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="BC34">
-        <v>0.98010852330645815</v>
+        <v>0.96837970323216338</v>
       </c>
       <c r="BD34">
-        <v>364.67707271493384</v>
+        <v>579.70544074367149</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11848,16 +11848,16 @@
         <v>464</v>
       </c>
       <c r="Y35" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="Z35" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AA35">
-        <v>0.98270299973748321</v>
+        <v>0.98055369884714538</v>
       </c>
       <c r="AB35">
-        <v>317.11167147947373</v>
+        <v>356.51552113566873</v>
       </c>
       <c r="AD35" t="s">
         <v>413</v>
@@ -11884,16 +11884,16 @@
         <v>651</v>
       </c>
       <c r="AM35" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AN35" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="AO35">
-        <v>0.98238877493134946</v>
+        <v>0.98435286039872183</v>
       </c>
       <c r="AP35">
-        <v>322.87245959192745</v>
+        <v>286.8642260234331</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11958,16 +11958,16 @@
         <v>466</v>
       </c>
       <c r="Y36" t="s">
-        <v>383</v>
+        <v>338</v>
       </c>
       <c r="Z36" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="AA36">
-        <v>0.97598085885692565</v>
+        <v>0.99284163372730061</v>
       </c>
       <c r="AB36">
-        <v>440.3509209563627</v>
+        <v>131.23671499948927</v>
       </c>
       <c r="AD36" t="s">
         <v>413</v>
@@ -11994,16 +11994,16 @@
         <v>653</v>
       </c>
       <c r="AM36" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AN36" t="s">
         <v>590</v>
       </c>
       <c r="AO36">
-        <v>0.98644744628709446</v>
+        <v>0.97655782887090981</v>
       </c>
       <c r="AP36">
-        <v>248.46348473660174</v>
+        <v>429.77313736665354</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12068,16 +12068,16 @@
         <v>468</v>
       </c>
       <c r="Y37" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z37" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="AA37">
-        <v>0.98338655524515672</v>
+        <v>0.980949293282396</v>
       </c>
       <c r="AB37">
-        <v>304.57982050546099</v>
+        <v>349.26295648940771</v>
       </c>
       <c r="AD37" t="s">
         <v>413</v>
@@ -12104,16 +12104,16 @@
         <v>655</v>
       </c>
       <c r="AM37" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AN37" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AO37">
-        <v>0.98967580974453273</v>
+        <v>0.98879946679477992</v>
       </c>
       <c r="AP37">
-        <v>189.27682135023403</v>
+        <v>205.34310876236799</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12178,16 +12178,16 @@
         <v>470</v>
       </c>
       <c r="Y38" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AA38">
-        <v>0.97813651992719985</v>
+        <v>0.98440429555001041</v>
       </c>
       <c r="AB38">
-        <v>400.83046800133633</v>
+        <v>285.92124824980857</v>
       </c>
       <c r="AD38" t="s">
         <v>413</v>
@@ -12214,16 +12214,16 @@
         <v>657</v>
       </c>
       <c r="AM38" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AN38" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AO38">
-        <v>0.98562083412131529</v>
+        <v>0.98121294780398804</v>
       </c>
       <c r="AP38">
-        <v>263.61804110921923</v>
+        <v>344.42929026021937</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12288,16 +12288,16 @@
         <v>472</v>
       </c>
       <c r="Y39" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z39" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AA39">
-        <v>0.99243389564470808</v>
+        <v>0.97996308088186879</v>
       </c>
       <c r="AB39">
-        <v>138.71191318035258</v>
+        <v>367.343517165739</v>
       </c>
       <c r="AD39" t="s">
         <v>413</v>
@@ -12324,16 +12324,16 @@
         <v>659</v>
       </c>
       <c r="AM39" t="s">
+        <v>768</v>
+      </c>
+      <c r="AN39" t="s">
         <v>769</v>
       </c>
-      <c r="AN39" t="s">
-        <v>593</v>
-      </c>
       <c r="AO39">
-        <v>0.99417752457368125</v>
+        <v>0.97759288697657265</v>
       </c>
       <c r="AP39">
-        <v>106.74538281584397</v>
+        <v>410.79707209616811</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12398,16 +12398,16 @@
         <v>474</v>
       </c>
       <c r="Y40" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="Z40" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AA40">
-        <v>0.98258925616289594</v>
+        <v>0.97636760270586087</v>
       </c>
       <c r="AB40">
-        <v>319.19697034690739</v>
+        <v>433.26061705921813</v>
       </c>
       <c r="AD40" t="s">
         <v>413</v>
@@ -12437,13 +12437,13 @@
         <v>770</v>
       </c>
       <c r="AN40" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="AO40">
-        <v>0.98213512486164511</v>
+        <v>0.97393752600115946</v>
       </c>
       <c r="AP40">
-        <v>327.5227108698395</v>
+        <v>477.81202331207646</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12508,16 +12508,16 @@
         <v>476</v>
       </c>
       <c r="Y41" t="s">
-        <v>401</v>
+        <v>362</v>
       </c>
       <c r="Z41" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="AA41">
-        <v>0.98625535317143753</v>
+        <v>0.97272179131491798</v>
       </c>
       <c r="AB41">
-        <v>251.98519185697839</v>
+        <v>500.10049255983796</v>
       </c>
       <c r="AD41" t="s">
         <v>413</v>
@@ -12547,13 +12547,13 @@
         <v>771</v>
       </c>
       <c r="AN41" t="s">
-        <v>772</v>
+        <v>597</v>
       </c>
       <c r="AO41">
-        <v>0.98305809009413248</v>
+        <v>0.98689046040235784</v>
       </c>
       <c r="AP41">
-        <v>310.60168160757155</v>
+        <v>240.34155929010652</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12618,16 +12618,16 @@
         <v>478</v>
       </c>
       <c r="Y42" t="s">
-        <v>405</v>
+        <v>346</v>
       </c>
       <c r="Z42" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AA42">
-        <v>0.98719346865782154</v>
+        <v>0.98444284858889564</v>
       </c>
       <c r="AB42">
-        <v>234.78640793993935</v>
+        <v>285.21444253691413</v>
       </c>
       <c r="AD42" t="s">
         <v>413</v>
@@ -12654,16 +12654,16 @@
         <v>665</v>
       </c>
       <c r="AM42" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AN42" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AO42">
-        <v>0.99584474408886259</v>
+        <v>0.97821870369907904</v>
       </c>
       <c r="AP42">
-        <v>76.179691704186226</v>
+        <v>399.32376551688469</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12728,16 +12728,16 @@
         <v>480</v>
       </c>
       <c r="Y43" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="Z43" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="AA43">
-        <v>0.97184397355215157</v>
+        <v>0.98269942042940017</v>
       </c>
       <c r="AB43">
-        <v>516.19381821055424</v>
+        <v>317.17729212766454</v>
       </c>
       <c r="AD43" t="s">
         <v>413</v>
@@ -12764,16 +12764,16 @@
         <v>667</v>
       </c>
       <c r="AM43" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AN43" t="s">
         <v>578</v>
       </c>
       <c r="AO43">
-        <v>0.9771067451947747</v>
+        <v>0.98830156477913722</v>
       </c>
       <c r="AP43">
-        <v>419.70967142912968</v>
+        <v>214.47131238248457</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12838,16 +12838,16 @@
         <v>482</v>
       </c>
       <c r="Y44" t="s">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="Z44" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="AA44">
-        <v>0.99382288375189876</v>
+        <v>0.98213943337265219</v>
       </c>
       <c r="AB44">
-        <v>113.24713121519014</v>
+        <v>327.44372150137696</v>
       </c>
       <c r="AD44" t="s">
         <v>413</v>
@@ -12874,16 +12874,16 @@
         <v>669</v>
       </c>
       <c r="AM44" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AN44" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="AO44">
-        <v>0.97431371456908866</v>
+        <v>0.99112984822979389</v>
       </c>
       <c r="AP44">
-        <v>470.91523290004181</v>
+        <v>162.61944912044567</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12948,16 +12948,16 @@
         <v>484</v>
       </c>
       <c r="Y45" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="Z45" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="AA45">
-        <v>0.97000043567738925</v>
+        <v>0.98443531955055918</v>
       </c>
       <c r="AB45">
-        <v>549.99201258119717</v>
+        <v>285.35247490641569</v>
       </c>
       <c r="AD45" t="s">
         <v>413</v>
@@ -12984,16 +12984,16 @@
         <v>671</v>
       </c>
       <c r="AM45" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AN45" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AO45">
-        <v>0.98039873263051136</v>
+        <v>0.98583529483105414</v>
       </c>
       <c r="AP45">
-        <v>359.35656844062476</v>
+        <v>259.6862614306732</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13058,16 +13058,16 @@
         <v>486</v>
       </c>
       <c r="Y46" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="Z46" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AA46">
-        <v>0.98823937652699512</v>
+        <v>0.97398849158227818</v>
       </c>
       <c r="AB46">
-        <v>215.61143033842296</v>
+        <v>476.87765432490079</v>
       </c>
       <c r="AD46" t="s">
         <v>413</v>
@@ -13094,16 +13094,16 @@
         <v>673</v>
       </c>
       <c r="AM46" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AN46" t="s">
         <v>579</v>
       </c>
       <c r="AO46">
-        <v>0.98326547324039271</v>
+        <v>0.97176508181545596</v>
       </c>
       <c r="AP46">
-        <v>306.79965725946761</v>
+        <v>517.64016671664035</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13168,16 +13168,16 @@
         <v>488</v>
       </c>
       <c r="Y47" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="Z47" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AA47">
-        <v>0.97307234437114887</v>
+        <v>0.98814122429339546</v>
       </c>
       <c r="AB47">
-        <v>493.6736865289368</v>
+        <v>217.4108879544159</v>
       </c>
       <c r="AD47" t="s">
         <v>413</v>
@@ -13204,16 +13204,16 @@
         <v>675</v>
       </c>
       <c r="AM47" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="AN47" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="AO47">
-        <v>0.98997462954848647</v>
+        <v>0.99168257517392877</v>
       </c>
       <c r="AP47">
-        <v>183.79845827774895</v>
+        <v>152.48612181130682</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13278,16 +13278,16 @@
         <v>490</v>
       </c>
       <c r="Y48" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="Z48" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="AA48">
-        <v>0.97831141720185744</v>
+        <v>0.97065607524213282</v>
       </c>
       <c r="AB48">
-        <v>397.62401796594617</v>
+        <v>537.97195389423189</v>
       </c>
       <c r="AD48" t="s">
         <v>413</v>
@@ -13314,16 +13314,16 @@
         <v>677</v>
       </c>
       <c r="AM48" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AN48" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="AO48">
-        <v>0.98425147469462704</v>
+        <v>0.97961567568507724</v>
       </c>
       <c r="AP48">
-        <v>288.72296393183791</v>
+        <v>373.71261244025072</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13388,16 +13388,16 @@
         <v>492</v>
       </c>
       <c r="Y49" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="Z49" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="AA49">
-        <v>0.9753018595470957</v>
+        <v>0.97916314637278834</v>
       </c>
       <c r="AB49">
-        <v>452.79924163657859</v>
+        <v>382.00898316554651</v>
       </c>
       <c r="AD49" t="s">
         <v>413</v>
@@ -13424,16 +13424,16 @@
         <v>679</v>
       </c>
       <c r="AM49" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AN49" t="s">
-        <v>595</v>
+        <v>574</v>
       </c>
       <c r="AO49">
-        <v>0.97434541537281683</v>
+        <v>0.97567317785568242</v>
       </c>
       <c r="AP49">
-        <v>470.33405149835795</v>
+        <v>445.99173931248959</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13498,16 +13498,16 @@
         <v>494</v>
       </c>
       <c r="Y50" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="Z50" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="AA50">
-        <v>0.98694170150784422</v>
+        <v>0.99062084979042209</v>
       </c>
       <c r="AB50">
-        <v>239.40213902285669</v>
+        <v>171.95108717559444</v>
       </c>
       <c r="AD50" t="s">
         <v>413</v>
@@ -13534,16 +13534,16 @@
         <v>681</v>
       </c>
       <c r="AM50" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AN50" t="s">
-        <v>782</v>
+        <v>598</v>
       </c>
       <c r="AO50">
-        <v>0.98430775783289481</v>
+        <v>0.99568797339637038</v>
       </c>
       <c r="AP50">
-        <v>287.69110639692803</v>
+        <v>79.053821066542412</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13608,16 +13608,16 @@
         <v>496</v>
       </c>
       <c r="Y51" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="Z51" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="AA51">
-        <v>0.98336988732579877</v>
+        <v>0.98254903847705999</v>
       </c>
       <c r="AB51">
-        <v>304.88539902702166</v>
+        <v>319.93429458723335</v>
       </c>
       <c r="AD51" t="s">
         <v>413</v>
@@ -13644,16 +13644,16 @@
         <v>683</v>
       </c>
       <c r="AM51" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AN51" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AO51">
-        <v>0.97444364094885727</v>
+        <v>0.9918951652662058</v>
       </c>
       <c r="AP51">
-        <v>468.53324927094968</v>
+        <v>148.58863678622743</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13718,16 +13718,16 @@
         <v>498</v>
       </c>
       <c r="Y52" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="Z52" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="AA52">
-        <v>0.97870278293688284</v>
+        <v>0.97646711233585171</v>
       </c>
       <c r="AB52">
-        <v>390.44897949048118</v>
+        <v>431.43627384271826</v>
       </c>
       <c r="AD52" t="s">
         <v>413</v>
@@ -13754,16 +13754,16 @@
         <v>685</v>
       </c>
       <c r="AM52" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AN52" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="AO52">
-        <v>0.98574603285635165</v>
+        <v>0.98531999116946412</v>
       </c>
       <c r="AP52">
-        <v>261.32273096688704</v>
+        <v>269.13349522649082</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13828,16 +13828,16 @@
         <v>500</v>
       </c>
       <c r="Y53" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Z53" t="s">
         <v>596</v>
       </c>
       <c r="AA53">
-        <v>0.98376398069352888</v>
+        <v>0.9863634971037446</v>
       </c>
       <c r="AB53">
-        <v>297.66035395197099</v>
+        <v>250.00255309801472</v>
       </c>
       <c r="AD53" t="s">
         <v>413</v>
@@ -13864,16 +13864,16 @@
         <v>687</v>
       </c>
       <c r="AM53" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="AN53" t="s">
-        <v>786</v>
+        <v>598</v>
       </c>
       <c r="AO53">
-        <v>0.97968688829580564</v>
+        <v>0.99054353037519915</v>
       </c>
       <c r="AP53">
-        <v>372.40704791023012</v>
+        <v>173.36860978801644</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -13938,16 +13938,16 @@
         <v>502</v>
       </c>
       <c r="Y54" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="Z54" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="AA54">
-        <v>0.98456002227805428</v>
+        <v>0.98024768078410096</v>
       </c>
       <c r="AB54">
-        <v>283.06625823567157</v>
+        <v>362.12585229148283</v>
       </c>
       <c r="AD54" t="s">
         <v>413</v>
@@ -13974,16 +13974,16 @@
         <v>689</v>
       </c>
       <c r="AM54" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="AN54" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AO54">
-        <v>0.98420825457429406</v>
+        <v>0.9768934332867476</v>
       </c>
       <c r="AP54">
-        <v>289.51533280460853</v>
+        <v>423.6203897429599</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -14048,16 +14048,16 @@
         <v>504</v>
       </c>
       <c r="Y55" t="s">
-        <v>407</v>
+        <v>355</v>
       </c>
       <c r="Z55" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="AA55">
-        <v>0.98915672308345548</v>
+        <v>0.99243389564470808</v>
       </c>
       <c r="AB55">
-        <v>198.79341013664933</v>
+        <v>138.71191318035258</v>
       </c>
       <c r="AD55" t="s">
         <v>413</v>
@@ -14084,16 +14084,16 @@
         <v>691</v>
       </c>
       <c r="AM55" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="AN55" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AO55">
-        <v>0.98302364254854535</v>
+        <v>0.9802768549486589</v>
       </c>
       <c r="AP55">
-        <v>311.23321994333526</v>
+        <v>361.5909926079201</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14158,16 +14158,16 @@
         <v>506</v>
       </c>
       <c r="Y56" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="Z56" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="AA56">
-        <v>0.98436057808473831</v>
+        <v>0.98258925616289594</v>
       </c>
       <c r="AB56">
-        <v>286.72273511313136</v>
+        <v>319.19697034690739</v>
       </c>
       <c r="AD56" t="s">
         <v>413</v>
@@ -14194,16 +14194,16 @@
         <v>693</v>
       </c>
       <c r="AM56" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="AN56" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="AO56">
-        <v>0.98003745158806088</v>
+        <v>0.97414990055259076</v>
       </c>
       <c r="AP56">
-        <v>365.98005421888422</v>
+        <v>473.91848986916989</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14268,16 +14268,16 @@
         <v>508</v>
       </c>
       <c r="Y57" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="Z57" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="AA57">
-        <v>0.99132783885824616</v>
+        <v>0.98625535317143753</v>
       </c>
       <c r="AB57">
-        <v>158.989620932154</v>
+        <v>251.98519185697839</v>
       </c>
       <c r="AD57" t="s">
         <v>413</v>
@@ -14304,16 +14304,16 @@
         <v>695</v>
       </c>
       <c r="AM57" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="AN57" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="AO57">
-        <v>0.98867603245018398</v>
+        <v>0.98705643087911032</v>
       </c>
       <c r="AP57">
-        <v>207.60607174662678</v>
+        <v>237.29876721631038</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14378,16 +14378,16 @@
         <v>510</v>
       </c>
       <c r="Y58" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="Z58" t="s">
         <v>581</v>
       </c>
       <c r="AA58">
-        <v>0.98031356085023202</v>
+        <v>0.98719346865782154</v>
       </c>
       <c r="AB58">
-        <v>360.91805107908004</v>
+        <v>234.78640793993935</v>
       </c>
       <c r="AD58" t="s">
         <v>413</v>
@@ -14414,16 +14414,16 @@
         <v>697</v>
       </c>
       <c r="AM58" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="AN58" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="AO58">
-        <v>0.98689046040235784</v>
+        <v>0.98989284585574766</v>
       </c>
       <c r="AP58">
-        <v>240.34155929010652</v>
+        <v>185.29782597795898</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14488,16 +14488,16 @@
         <v>512</v>
       </c>
       <c r="Y59" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z59" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AA59">
-        <v>0.97974172455321451</v>
+        <v>0.97184397355215157</v>
       </c>
       <c r="AB59">
-        <v>371.40171652440046</v>
+        <v>516.19381821055424</v>
       </c>
       <c r="AD59" t="s">
         <v>413</v>
@@ -14524,16 +14524,16 @@
         <v>699</v>
       </c>
       <c r="AM59" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="AN59" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="AO59">
-        <v>0.97821870369907904</v>
+        <v>0.98238877493134946</v>
       </c>
       <c r="AP59">
-        <v>399.32376551688469</v>
+        <v>322.87245959192745</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14598,16 +14598,16 @@
         <v>514</v>
       </c>
       <c r="Y60" t="s">
-        <v>375</v>
+        <v>345</v>
       </c>
       <c r="Z60" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="AA60">
-        <v>0.98815787487536866</v>
+        <v>0.97870278293688284</v>
       </c>
       <c r="AB60">
-        <v>217.10562728490754</v>
+        <v>390.44897949048118</v>
       </c>
       <c r="AD60" t="s">
         <v>413</v>
@@ -14634,16 +14634,16 @@
         <v>701</v>
       </c>
       <c r="AM60" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="AN60" t="s">
-        <v>576</v>
+        <v>598</v>
       </c>
       <c r="AO60">
-        <v>0.98830156477913722</v>
+        <v>0.98644744628709446</v>
       </c>
       <c r="AP60">
-        <v>214.47131238248457</v>
+        <v>248.46348473660174</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14708,16 +14708,16 @@
         <v>516</v>
       </c>
       <c r="Y61" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="Z61" t="s">
-        <v>583</v>
+        <v>599</v>
       </c>
       <c r="AA61">
-        <v>0.97272179131491798</v>
+        <v>0.98376398069352888</v>
       </c>
       <c r="AB61">
-        <v>500.10049255983796</v>
+        <v>297.66035395197099</v>
       </c>
       <c r="AD61" t="s">
         <v>413</v>
@@ -14744,16 +14744,16 @@
         <v>703</v>
       </c>
       <c r="AM61" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="AN61" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="AO61">
-        <v>0.99112984822979389</v>
+        <v>0.98967580974453273</v>
       </c>
       <c r="AP61">
-        <v>162.61944912044567</v>
+        <v>189.27682135023403</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14818,16 +14818,16 @@
         <v>518</v>
       </c>
       <c r="Y62" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="Z62" t="s">
         <v>598</v>
       </c>
       <c r="AA62">
-        <v>0.98444284858889564</v>
+        <v>0.98456002227805428</v>
       </c>
       <c r="AB62">
-        <v>285.21444253691413</v>
+        <v>283.06625823567157</v>
       </c>
       <c r="AD62" t="s">
         <v>413</v>
@@ -14854,16 +14854,16 @@
         <v>705</v>
       </c>
       <c r="AM62" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="AN62" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="AO62">
-        <v>0.98879946679477992</v>
+        <v>0.98562083412131529</v>
       </c>
       <c r="AP62">
-        <v>205.34310876236799</v>
+        <v>263.61804110921923</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14928,16 +14928,16 @@
         <v>520</v>
       </c>
       <c r="Y63" t="s">
-        <v>360</v>
+        <v>407</v>
       </c>
       <c r="Z63" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="AA63">
-        <v>0.98269942042940017</v>
+        <v>0.98915672308345548</v>
       </c>
       <c r="AB63">
-        <v>317.17729212766454</v>
+        <v>198.79341013664933</v>
       </c>
       <c r="AD63" t="s">
         <v>413</v>
@@ -14964,16 +14964,16 @@
         <v>707</v>
       </c>
       <c r="AM63" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="AN63" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AO63">
-        <v>0.98121294780398804</v>
+        <v>0.98039873263051136</v>
       </c>
       <c r="AP63">
-        <v>344.42929026021937</v>
+        <v>359.35656844062476</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -15038,16 +15038,16 @@
         <v>522</v>
       </c>
       <c r="Y64" t="s">
-        <v>361</v>
+        <v>408</v>
       </c>
       <c r="Z64" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="AA64">
-        <v>0.98213943337265219</v>
+        <v>0.98436057808473831</v>
       </c>
       <c r="AB64">
-        <v>327.44372150137696</v>
+        <v>286.72273511313136</v>
       </c>
       <c r="AD64" t="s">
         <v>413</v>
@@ -15074,16 +15074,16 @@
         <v>709</v>
       </c>
       <c r="AM64" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="AN64" t="s">
-        <v>798</v>
+        <v>592</v>
       </c>
       <c r="AO64">
-        <v>0.97759288697657265</v>
+        <v>0.98326547324039271</v>
       </c>
       <c r="AP64">
-        <v>410.79707209616811</v>
+        <v>306.79965725946761</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -15148,16 +15148,16 @@
         <v>524</v>
       </c>
       <c r="Y65" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="Z65" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="AA65">
-        <v>0.98055369884714538</v>
+        <v>0.99132783885824616</v>
       </c>
       <c r="AB65">
-        <v>356.51552113566873</v>
+        <v>158.989620932154</v>
       </c>
       <c r="AD65" t="s">
         <v>413</v>
@@ -15184,16 +15184,16 @@
         <v>711</v>
       </c>
       <c r="AM65" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="AN65" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AO65">
-        <v>0.97393752600115946</v>
+        <v>0.98997462954848647</v>
       </c>
       <c r="AP65">
-        <v>477.81202331207646</v>
+        <v>183.79845827774895</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15258,16 +15258,16 @@
         <v>526</v>
       </c>
       <c r="Y66" t="s">
-        <v>338</v>
+        <v>378</v>
       </c>
       <c r="Z66" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="AA66">
-        <v>0.99284163372730061</v>
+        <v>0.98031356085023202</v>
       </c>
       <c r="AB66">
-        <v>131.23671499948927</v>
+        <v>360.91805107908004</v>
       </c>
       <c r="AD66" t="s">
         <v>413</v>
@@ -15294,16 +15294,16 @@
         <v>713</v>
       </c>
       <c r="AM66" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="AN66" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="AO66">
-        <v>0.97567317785568242</v>
+        <v>0.98425147469462704</v>
       </c>
       <c r="AP66">
-        <v>445.99173931248959</v>
+        <v>288.72296393183791</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15368,16 +15368,16 @@
         <v>528</v>
       </c>
       <c r="Y67" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="Z67" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="AA67">
-        <v>0.980949293282396</v>
+        <v>0.97974172455321451</v>
       </c>
       <c r="AB67">
-        <v>349.26295648940771</v>
+        <v>371.40171652440046</v>
       </c>
       <c r="AD67" t="s">
         <v>413</v>
@@ -15404,16 +15404,16 @@
         <v>715</v>
       </c>
       <c r="AM67" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="AN67" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="AO67">
-        <v>0.99568797339637038</v>
+        <v>0.97434541537281683</v>
       </c>
       <c r="AP67">
-        <v>79.053821066542412</v>
+        <v>470.33405149835795</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15478,16 +15478,16 @@
         <v>530</v>
       </c>
       <c r="Y68" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="Z68" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AA68">
-        <v>0.98440429555001041</v>
+        <v>0.98815787487536866</v>
       </c>
       <c r="AB68">
-        <v>285.92124824980857</v>
+        <v>217.10562728490754</v>
       </c>
       <c r="AD68" t="s">
         <v>413</v>
@@ -15514,16 +15514,16 @@
         <v>717</v>
       </c>
       <c r="AM68" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="AN68" t="s">
-        <v>581</v>
+        <v>799</v>
       </c>
       <c r="AO68">
-        <v>0.9918951652662058</v>
+        <v>0.98430775783289481</v>
       </c>
       <c r="AP68">
-        <v>148.58863678622743</v>
+        <v>287.69110639692803</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -15588,16 +15588,16 @@
         <v>532</v>
       </c>
       <c r="Y69" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="Z69" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="AA69">
-        <v>0.97996308088186879</v>
+        <v>0.97878284543380634</v>
       </c>
       <c r="AB69">
-        <v>367.343517165739</v>
+        <v>388.98116704688283</v>
       </c>
       <c r="AD69" t="s">
         <v>413</v>
@@ -15624,16 +15624,16 @@
         <v>719</v>
       </c>
       <c r="AM69" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="AN69" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="AO69">
-        <v>0.98531999116946412</v>
+        <v>0.97444364094885727</v>
       </c>
       <c r="AP69">
-        <v>269.13349522649082</v>
+        <v>468.53324927094968</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -15698,16 +15698,16 @@
         <v>534</v>
       </c>
       <c r="Y70" t="s">
-        <v>386</v>
+        <v>340</v>
       </c>
       <c r="Z70" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="AA70">
-        <v>0.97636760270586087</v>
+        <v>0.9898744603534384</v>
       </c>
       <c r="AB70">
-        <v>433.26061705921813</v>
+        <v>185.63489352029583</v>
       </c>
       <c r="AD70" t="s">
         <v>413</v>
@@ -15734,16 +15734,16 @@
         <v>721</v>
       </c>
       <c r="AM70" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="AN70" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="AO70">
-        <v>0.99009266720704037</v>
+        <v>0.98574603285635165</v>
       </c>
       <c r="AP70">
-        <v>181.63443453759336</v>
+        <v>261.32273096688704</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -15808,16 +15808,16 @@
         <v>536</v>
       </c>
       <c r="Y71" t="s">
-        <v>406</v>
+        <v>336</v>
       </c>
       <c r="Z71" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="AA71">
-        <v>0.99165078812878382</v>
+        <v>0.98205187669897798</v>
       </c>
       <c r="AB71">
-        <v>153.06888430562992</v>
+        <v>329.04892718540373</v>
       </c>
       <c r="AD71" t="s">
         <v>413</v>
@@ -15844,16 +15844,16 @@
         <v>723</v>
       </c>
       <c r="AM71" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="AN71" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="AO71">
-        <v>0.98371568181207825</v>
+        <v>0.98003745158806088</v>
       </c>
       <c r="AP71">
-        <v>298.5458334452332</v>
+        <v>365.98005421888422</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -15918,16 +15918,16 @@
         <v>538</v>
       </c>
       <c r="Y72" t="s">
-        <v>353</v>
+        <v>400</v>
       </c>
       <c r="Z72" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA72">
-        <v>0.97646479583958734</v>
+        <v>0.99142494197358011</v>
       </c>
       <c r="AB72">
-        <v>431.47874294089837</v>
+        <v>157.20939715103142</v>
       </c>
       <c r="AD72" t="s">
         <v>413</v>
@@ -15954,16 +15954,16 @@
         <v>725</v>
       </c>
       <c r="AM72" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="AN72" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="AO72">
-        <v>0.98435286039872183</v>
+        <v>0.98867603245018398</v>
       </c>
       <c r="AP72">
-        <v>286.8642260234331</v>
+        <v>207.60607174662678</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16028,16 +16028,16 @@
         <v>540</v>
       </c>
       <c r="Y73" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="Z73" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="AA73">
-        <v>0.96562135615554268</v>
+        <v>0.9807975141504387</v>
       </c>
       <c r="AB73">
-        <v>630.27513714838358</v>
+        <v>352.04557390862351</v>
       </c>
       <c r="AD73" t="s">
         <v>413</v>
@@ -16064,16 +16064,16 @@
         <v>727</v>
       </c>
       <c r="AM73" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="AN73" t="s">
-        <v>586</v>
+        <v>805</v>
       </c>
       <c r="AO73">
-        <v>0.97655782887090981</v>
+        <v>0.97223070787085453</v>
       </c>
       <c r="AP73">
-        <v>429.77313736665354</v>
+        <v>509.10368903433471</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -16138,16 +16138,16 @@
         <v>542</v>
       </c>
       <c r="Y74" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="Z74" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="AA74">
-        <v>0.98843111817052332</v>
+        <v>0.98596629583708084</v>
       </c>
       <c r="AB74">
-        <v>212.09616687373853</v>
+        <v>257.28457632018387</v>
       </c>
       <c r="AD74" t="s">
         <v>413</v>
@@ -16174,16 +16174,16 @@
         <v>729</v>
       </c>
       <c r="AM74" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="AN74" t="s">
-        <v>593</v>
+        <v>807</v>
       </c>
       <c r="AO74">
-        <v>0.98583529483105414</v>
+        <v>0.99323428174300499</v>
       </c>
       <c r="AP74">
-        <v>259.6862614306732</v>
+        <v>124.03816804490805</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -16248,16 +16248,16 @@
         <v>544</v>
       </c>
       <c r="Y75" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="Z75" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="AA75">
-        <v>0.99409930001823366</v>
+        <v>0.99365868734102913</v>
       </c>
       <c r="AB75">
-        <v>108.17949966571678</v>
+        <v>116.25739874780012</v>
       </c>
       <c r="AD75" t="s">
         <v>413</v>
@@ -16284,16 +16284,16 @@
         <v>731</v>
       </c>
       <c r="AM75" t="s">
+        <v>808</v>
+      </c>
+      <c r="AN75" t="s">
         <v>809</v>
       </c>
-      <c r="AN75" t="s">
-        <v>583</v>
-      </c>
       <c r="AO75">
-        <v>0.97176508181545596</v>
+        <v>0.97340237375196048</v>
       </c>
       <c r="AP75">
-        <v>517.64016671664035</v>
+        <v>487.62314788072359</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -16358,16 +16358,16 @@
         <v>546</v>
       </c>
       <c r="Y76" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="Z76" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="AA76">
-        <v>0.99045315399849054</v>
+        <v>0.98564262027093064</v>
       </c>
       <c r="AB76">
-        <v>175.02551002767362</v>
+        <v>263.21862836627207</v>
       </c>
       <c r="AD76" t="s">
         <v>413</v>
@@ -16397,13 +16397,13 @@
         <v>810</v>
       </c>
       <c r="AN76" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="AO76">
-        <v>0.99168257517392877</v>
+        <v>0.98709698070191276</v>
       </c>
       <c r="AP76">
-        <v>152.48612181130682</v>
+        <v>236.55535379826514</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -16468,16 +16468,16 @@
         <v>548</v>
       </c>
       <c r="Y77" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="Z77" t="s">
         <v>583</v>
       </c>
       <c r="AA77">
-        <v>0.98443531955055918</v>
+        <v>0.99296984942213296</v>
       </c>
       <c r="AB77">
-        <v>285.35247490641569</v>
+        <v>128.88609392756314</v>
       </c>
       <c r="AD77" t="s">
         <v>413</v>
@@ -16507,13 +16507,13 @@
         <v>811</v>
       </c>
       <c r="AN77" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AO77">
-        <v>0.97961567568507724</v>
+        <v>0.97913435966240669</v>
       </c>
       <c r="AP77">
-        <v>373.71261244025072</v>
+        <v>382.53673952254371</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -16578,16 +16578,16 @@
         <v>550</v>
       </c>
       <c r="Y78" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="Z78" t="s">
         <v>600</v>
       </c>
       <c r="AA78">
-        <v>0.97398849158227818</v>
+        <v>0.99409930001823366</v>
       </c>
       <c r="AB78">
-        <v>476.87765432490079</v>
+        <v>108.17949966571678</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -16652,16 +16652,16 @@
         <v>552</v>
       </c>
       <c r="Y79" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z79" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="AA79">
-        <v>0.98814122429339546</v>
+        <v>0.99045315399849054</v>
       </c>
       <c r="AB79">
-        <v>217.4108879544159</v>
+        <v>175.02551002767362</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -16726,16 +16726,16 @@
         <v>554</v>
       </c>
       <c r="Y80" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="Z80" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="AA80">
-        <v>0.97065607524213282</v>
+        <v>0.97970789283404214</v>
       </c>
       <c r="AB80">
-        <v>537.97195389423189</v>
+        <v>372.02196470922701</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -16800,16 +16800,16 @@
         <v>556</v>
       </c>
       <c r="Y81" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="Z81" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="AA81">
-        <v>0.97916314637278834</v>
+        <v>0.98270299973748321</v>
       </c>
       <c r="AB81">
-        <v>382.00898316554651</v>
+        <v>317.11167147947373</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -16874,16 +16874,16 @@
         <v>558</v>
       </c>
       <c r="Y82" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="Z82" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="AA82">
-        <v>0.97545857121381951</v>
+        <v>0.97598085885692565</v>
       </c>
       <c r="AB82">
-        <v>449.92619441330908</v>
+        <v>440.3509209563627</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -16948,16 +16948,16 @@
         <v>560</v>
       </c>
       <c r="Y83" t="s">
-        <v>409</v>
+        <v>364</v>
       </c>
       <c r="Z83" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="AA83">
-        <v>0.98212250728249206</v>
+        <v>0.98042255120792365</v>
       </c>
       <c r="AB83">
-        <v>327.75403315431197</v>
+        <v>358.91989452139876</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -17022,16 +17022,16 @@
         <v>562</v>
       </c>
       <c r="Y84" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="Z84" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="AA84">
-        <v>0.99456410459052502</v>
+        <v>0.98981198518654634</v>
       </c>
       <c r="AB84">
-        <v>99.658082507040461</v>
+        <v>186.78027157998449</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -17096,16 +17096,16 @@
         <v>564</v>
       </c>
       <c r="Y85" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="Z85" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="AA85">
-        <v>0.97891429500574301</v>
+        <v>0.97580984429062223</v>
       </c>
       <c r="AB85">
-        <v>386.57125822804534</v>
+        <v>443.48618800525958</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -17170,16 +17170,16 @@
         <v>566</v>
       </c>
       <c r="Y86" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="Z86" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="AA86">
-        <v>0.99086247853214549</v>
+        <v>0.98738988106093839</v>
       </c>
       <c r="AB86">
-        <v>167.52122691066626</v>
+        <v>231.18551388279656</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -17244,16 +17244,16 @@
         <v>568</v>
       </c>
       <c r="Y87" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="Z87" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="AA87">
-        <v>0.9839124944774571</v>
+        <v>0.97723778280633045</v>
       </c>
       <c r="AB87">
-        <v>294.93760124661941</v>
+        <v>417.30731521727455</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -17318,16 +17318,16 @@
         <v>570</v>
       </c>
       <c r="Y88" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z88" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="AA88">
-        <v>0.97678875799905829</v>
+        <v>0.99035601519017957</v>
       </c>
       <c r="AB88">
-        <v>425.5394366839318</v>
+        <v>176.80638818004016</v>
       </c>
     </row>
   </sheetData>
@@ -17336,7 +17336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43274664-79B4-4115-BA76-BCCD51465C6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D09E94EA-B567-4ECA-9ED1-D01A38CADAC3}">
   <dimension ref="B9:Z77"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17448,7 +17448,7 @@
         <v>885</v>
       </c>
       <c r="K11" t="s">
-        <v>780</v>
+        <v>797</v>
       </c>
       <c r="L11">
         <v>29.7146465744454</v>
@@ -17549,7 +17549,7 @@
         <v>1021</v>
       </c>
       <c r="X12" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="Y12">
         <v>10.88325</v>
@@ -17617,7 +17617,7 @@
         <v>1023</v>
       </c>
       <c r="X13" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
       <c r="Y13">
         <v>26.983499999999999</v>
@@ -17652,7 +17652,7 @@
         <v>891</v>
       </c>
       <c r="K14" t="s">
-        <v>764</v>
+        <v>745</v>
       </c>
       <c r="L14">
         <v>16.006796560234815</v>
@@ -17720,7 +17720,7 @@
         <v>893</v>
       </c>
       <c r="K15" t="s">
-        <v>773</v>
+        <v>750</v>
       </c>
       <c r="L15">
         <v>17.682358378036344</v>
@@ -17753,7 +17753,7 @@
         <v>1027</v>
       </c>
       <c r="X15" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="Y15">
         <v>24.900749999999999</v>
@@ -17788,7 +17788,7 @@
         <v>895</v>
       </c>
       <c r="K16" t="s">
-        <v>789</v>
+        <v>802</v>
       </c>
       <c r="L16">
         <v>29.492382648463739</v>
@@ -17821,7 +17821,7 @@
         <v>1029</v>
       </c>
       <c r="X16" t="s">
-        <v>882</v>
+        <v>864</v>
       </c>
       <c r="Y16">
         <v>18.545249999999999</v>
@@ -17856,7 +17856,7 @@
         <v>897</v>
       </c>
       <c r="K17" t="s">
-        <v>805</v>
+        <v>763</v>
       </c>
       <c r="L17">
         <v>8.6778699255653748</v>
@@ -17889,7 +17889,7 @@
         <v>1031</v>
       </c>
       <c r="X17" t="s">
-        <v>864</v>
+        <v>882</v>
       </c>
       <c r="Y17">
         <v>29.838000000000001</v>
@@ -17924,7 +17924,7 @@
         <v>899</v>
       </c>
       <c r="K18" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="L18">
         <v>12.772248157772113</v>
@@ -17957,7 +17957,7 @@
         <v>1033</v>
       </c>
       <c r="X18" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="Y18">
         <v>58.689</v>
@@ -17992,7 +17992,7 @@
         <v>901</v>
       </c>
       <c r="K19" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="L19">
         <v>11.876635800692616</v>
@@ -18025,7 +18025,7 @@
         <v>1035</v>
       </c>
       <c r="X19" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="Y19">
         <v>48.432000000000002</v>
@@ -18093,7 +18093,7 @@
         <v>1037</v>
       </c>
       <c r="X20" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="Y20">
         <v>47.794499999999999</v>
@@ -18128,7 +18128,7 @@
         <v>905</v>
       </c>
       <c r="K21" t="s">
-        <v>799</v>
+        <v>770</v>
       </c>
       <c r="L21">
         <v>27.043339674957092</v>
@@ -18161,7 +18161,7 @@
         <v>1039</v>
       </c>
       <c r="X21" t="s">
-        <v>874</v>
+        <v>860</v>
       </c>
       <c r="Y21">
         <v>7.1767500000000002</v>
@@ -18196,7 +18196,7 @@
         <v>907</v>
       </c>
       <c r="K22" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L22">
         <v>12.170927347824723</v>
@@ -18229,7 +18229,7 @@
         <v>1041</v>
       </c>
       <c r="X22" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="Y22">
         <v>8.1052499999999998</v>
@@ -18264,7 +18264,7 @@
         <v>909</v>
       </c>
       <c r="K23" t="s">
-        <v>756</v>
+        <v>788</v>
       </c>
       <c r="L23">
         <v>26.999240466622091</v>
@@ -18297,7 +18297,7 @@
         <v>1043</v>
       </c>
       <c r="X23" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="Y23">
         <v>9.3810000000000002</v>
@@ -18332,7 +18332,7 @@
         <v>911</v>
       </c>
       <c r="K24" t="s">
-        <v>802</v>
+        <v>781</v>
       </c>
       <c r="L24">
         <v>23.305350986470582</v>
@@ -18365,7 +18365,7 @@
         <v>1045</v>
       </c>
       <c r="X24" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="Y24">
         <v>11.47575</v>
@@ -18400,7 +18400,7 @@
         <v>913</v>
       </c>
       <c r="K25" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="L25">
         <v>19.293897715957783</v>
@@ -18433,7 +18433,7 @@
         <v>1047</v>
       </c>
       <c r="X25" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="Y25">
         <v>6.1372499999999999</v>
@@ -18468,7 +18468,7 @@
         <v>915</v>
       </c>
       <c r="K26" t="s">
-        <v>811</v>
+        <v>778</v>
       </c>
       <c r="L26">
         <v>15.217638427037592</v>
@@ -18501,7 +18501,7 @@
         <v>1049</v>
       </c>
       <c r="X26" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="Y26">
         <v>14.57325</v>
@@ -18536,7 +18536,7 @@
         <v>917</v>
       </c>
       <c r="K27" t="s">
-        <v>767</v>
+        <v>791</v>
       </c>
       <c r="L27">
         <v>3.1385663053565613</v>
@@ -18569,7 +18569,7 @@
         <v>1051</v>
       </c>
       <c r="X27" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="Y27">
         <v>10.491</v>
@@ -18604,7 +18604,7 @@
         <v>919</v>
       </c>
       <c r="K28" t="s">
-        <v>768</v>
+        <v>792</v>
       </c>
       <c r="L28">
         <v>4.0628682283884237</v>
@@ -18637,7 +18637,7 @@
         <v>1053</v>
       </c>
       <c r="X28" t="s">
-        <v>883</v>
+        <v>865</v>
       </c>
       <c r="Y28">
         <v>17.414249999999999</v>
@@ -18672,7 +18672,7 @@
         <v>921</v>
       </c>
       <c r="K29" t="s">
-        <v>784</v>
+        <v>801</v>
       </c>
       <c r="L29">
         <v>18.31221960055294</v>
@@ -18705,7 +18705,7 @@
         <v>1055</v>
       </c>
       <c r="X29" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="Y29">
         <v>10.968</v>
@@ -18740,7 +18740,7 @@
         <v>923</v>
       </c>
       <c r="K30" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="L30">
         <v>27.91719839668141</v>
@@ -18773,7 +18773,7 @@
         <v>1057</v>
       </c>
       <c r="X30" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="Y30">
         <v>10.79175</v>
@@ -18808,7 +18808,7 @@
         <v>925</v>
       </c>
       <c r="K31" t="s">
-        <v>788</v>
+        <v>756</v>
       </c>
       <c r="L31">
         <v>20.659184774772967</v>
@@ -18841,7 +18841,7 @@
         <v>1059</v>
       </c>
       <c r="X31" t="s">
-        <v>875</v>
+        <v>861</v>
       </c>
       <c r="Y31">
         <v>20.114249999999998</v>
@@ -18876,7 +18876,7 @@
         <v>927</v>
       </c>
       <c r="K32" t="s">
-        <v>793</v>
+        <v>773</v>
       </c>
       <c r="L32">
         <v>1.6724491767694549</v>
@@ -18909,7 +18909,7 @@
         <v>1061</v>
       </c>
       <c r="X32" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="Y32">
         <v>44.373750000000001</v>
@@ -18944,7 +18944,7 @@
         <v>929</v>
       </c>
       <c r="K33" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="L33">
         <v>13.9157416320151</v>
@@ -18977,7 +18977,7 @@
         <v>1063</v>
       </c>
       <c r="X33" t="s">
-        <v>866</v>
+        <v>884</v>
       </c>
       <c r="Y33">
         <v>18.57525</v>
@@ -19012,7 +19012,7 @@
         <v>931</v>
       </c>
       <c r="K34" t="s">
-        <v>790</v>
+        <v>803</v>
       </c>
       <c r="L34">
         <v>19.755004592887676</v>
@@ -19045,7 +19045,7 @@
         <v>1065</v>
       </c>
       <c r="X34" t="s">
-        <v>865</v>
+        <v>883</v>
       </c>
       <c r="Y34">
         <v>18.241499999999998</v>
@@ -19080,7 +19080,7 @@
         <v>933</v>
       </c>
       <c r="K35" t="s">
-        <v>787</v>
+        <v>755</v>
       </c>
       <c r="L35">
         <v>14.794879040591612</v>
@@ -19115,7 +19115,7 @@
         <v>935</v>
       </c>
       <c r="K36" t="s">
-        <v>792</v>
+        <v>772</v>
       </c>
       <c r="L36">
         <v>6.2274748795149915</v>
@@ -19150,7 +19150,7 @@
         <v>937</v>
       </c>
       <c r="K37" t="s">
-        <v>781</v>
+        <v>798</v>
       </c>
       <c r="L37">
         <v>20.047482861417784</v>
@@ -19185,7 +19185,7 @@
         <v>939</v>
       </c>
       <c r="K38" t="s">
-        <v>810</v>
+        <v>777</v>
       </c>
       <c r="L38">
         <v>39.487686646898077</v>
@@ -19290,7 +19290,7 @@
         <v>945</v>
       </c>
       <c r="K41" t="s">
-        <v>771</v>
+        <v>748</v>
       </c>
       <c r="L41">
         <v>48.268110562179842</v>
@@ -19325,7 +19325,7 @@
         <v>947</v>
       </c>
       <c r="K42" t="s">
-        <v>747</v>
+        <v>806</v>
       </c>
       <c r="L42">
         <v>90.630298494129065</v>
@@ -19360,7 +19360,7 @@
         <v>949</v>
       </c>
       <c r="K43" t="s">
-        <v>745</v>
+        <v>804</v>
       </c>
       <c r="L43">
         <v>33.627820830597955</v>
@@ -19395,7 +19395,7 @@
         <v>951</v>
       </c>
       <c r="K44" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="L44">
         <v>30.412670648726838</v>
@@ -19430,7 +19430,7 @@
         <v>953</v>
       </c>
       <c r="K45" t="s">
-        <v>804</v>
+        <v>762</v>
       </c>
       <c r="L45">
         <v>47.878917655816522</v>
@@ -19465,7 +19465,7 @@
         <v>955</v>
       </c>
       <c r="K46" t="s">
-        <v>770</v>
+        <v>747</v>
       </c>
       <c r="L46">
         <v>69.366510391046873</v>
@@ -19500,7 +19500,7 @@
         <v>957</v>
       </c>
       <c r="K47" t="s">
-        <v>807</v>
+        <v>765</v>
       </c>
       <c r="L47">
         <v>19.428837136062757</v>
@@ -19535,7 +19535,7 @@
         <v>959</v>
       </c>
       <c r="K48" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="L48">
         <v>15.054857587707319</v>
@@ -19570,7 +19570,7 @@
         <v>961</v>
       </c>
       <c r="K49" t="s">
-        <v>797</v>
+        <v>768</v>
       </c>
       <c r="L49">
         <v>13.019602602156084</v>
@@ -19605,7 +19605,7 @@
         <v>963</v>
       </c>
       <c r="K50" t="s">
-        <v>752</v>
+        <v>811</v>
       </c>
       <c r="L50">
         <v>25.094411791551167</v>
@@ -19640,7 +19640,7 @@
         <v>965</v>
       </c>
       <c r="K51" t="s">
-        <v>758</v>
+        <v>784</v>
       </c>
       <c r="L51">
         <v>10.512568509966947</v>
@@ -19675,7 +19675,7 @@
         <v>967</v>
       </c>
       <c r="K52" t="s">
-        <v>806</v>
+        <v>764</v>
       </c>
       <c r="L52">
         <v>19.484319735030326</v>
@@ -19710,7 +19710,7 @@
         <v>969</v>
       </c>
       <c r="K53" t="s">
-        <v>783</v>
+        <v>800</v>
       </c>
       <c r="L53">
         <v>10.300130106481824</v>
@@ -19745,7 +19745,7 @@
         <v>971</v>
       </c>
       <c r="K54" t="s">
-        <v>751</v>
+        <v>810</v>
       </c>
       <c r="L54">
         <v>38.113797875314695</v>
@@ -19780,7 +19780,7 @@
         <v>973</v>
       </c>
       <c r="K55" t="s">
-        <v>774</v>
+        <v>751</v>
       </c>
       <c r="L55">
         <v>48.324816212675138</v>
@@ -19815,7 +19815,7 @@
         <v>975</v>
       </c>
       <c r="K56" t="s">
-        <v>753</v>
+        <v>785</v>
       </c>
       <c r="L56">
         <v>69.883597189706848</v>
@@ -19850,7 +19850,7 @@
         <v>977</v>
       </c>
       <c r="K57" t="s">
-        <v>791</v>
+        <v>771</v>
       </c>
       <c r="L57">
         <v>65.706815294563484</v>
@@ -19885,7 +19885,7 @@
         <v>979</v>
       </c>
       <c r="K58" t="s">
-        <v>776</v>
+        <v>793</v>
       </c>
       <c r="L58">
         <v>55.231206871897385</v>
@@ -19920,7 +19920,7 @@
         <v>981</v>
       </c>
       <c r="K59" t="s">
-        <v>777</v>
+        <v>794</v>
       </c>
       <c r="L59">
         <v>19.970554339652629</v>
@@ -19955,7 +19955,7 @@
         <v>983</v>
       </c>
       <c r="K60" t="s">
-        <v>808</v>
+        <v>775</v>
       </c>
       <c r="L60">
         <v>72.559102068013246</v>
@@ -19990,7 +19990,7 @@
         <v>985</v>
       </c>
       <c r="K61" t="s">
-        <v>769</v>
+        <v>746</v>
       </c>
       <c r="L61">
         <v>44.220292794619994</v>
@@ -20025,7 +20025,7 @@
         <v>987</v>
       </c>
       <c r="K62" t="s">
-        <v>796</v>
+        <v>767</v>
       </c>
       <c r="L62">
         <v>39.277945374969107</v>
@@ -20060,7 +20060,7 @@
         <v>989</v>
       </c>
       <c r="K63" t="s">
-        <v>795</v>
+        <v>766</v>
       </c>
       <c r="L63">
         <v>59.341737840109467</v>
@@ -20095,7 +20095,7 @@
         <v>991</v>
       </c>
       <c r="K64" t="s">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="L64">
         <v>29.191927665826828</v>
@@ -20130,7 +20130,7 @@
         <v>993</v>
       </c>
       <c r="K65" t="s">
-        <v>778</v>
+        <v>795</v>
       </c>
       <c r="L65">
         <v>39.617260419426948</v>
@@ -20165,7 +20165,7 @@
         <v>995</v>
       </c>
       <c r="K66" t="s">
-        <v>765</v>
+        <v>789</v>
       </c>
       <c r="L66">
         <v>47.296862636729713</v>
@@ -20235,7 +20235,7 @@
         <v>999</v>
       </c>
       <c r="K68" t="s">
-        <v>785</v>
+        <v>753</v>
       </c>
       <c r="L68">
         <v>15.401477961960474</v>
@@ -20270,7 +20270,7 @@
         <v>1001</v>
       </c>
       <c r="K69" t="s">
-        <v>754</v>
+        <v>786</v>
       </c>
       <c r="L69">
         <v>10.395885695189069</v>
@@ -20305,7 +20305,7 @@
         <v>1003</v>
       </c>
       <c r="K70" t="s">
-        <v>749</v>
+        <v>808</v>
       </c>
       <c r="L70">
         <v>23.89105636564183</v>
@@ -20375,7 +20375,7 @@
         <v>1007</v>
       </c>
       <c r="K72" t="s">
-        <v>766</v>
+        <v>790</v>
       </c>
       <c r="L72">
         <v>6.6550975614073966</v>
@@ -20410,7 +20410,7 @@
         <v>1009</v>
       </c>
       <c r="K73" t="s">
-        <v>757</v>
+        <v>783</v>
       </c>
       <c r="L73">
         <v>13.961943802326671</v>
@@ -20445,7 +20445,7 @@
         <v>1011</v>
       </c>
       <c r="K74" t="s">
-        <v>809</v>
+        <v>776</v>
       </c>
       <c r="L74">
         <v>53.946776653453853</v>
@@ -20480,7 +20480,7 @@
         <v>1013</v>
       </c>
       <c r="K75" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="L75">
         <v>21.246092446368579</v>
@@ -20515,7 +20515,7 @@
         <v>1015</v>
       </c>
       <c r="K76" t="s">
-        <v>779</v>
+        <v>796</v>
       </c>
       <c r="L76">
         <v>19.51059121972445</v>
@@ -20550,7 +20550,7 @@
         <v>1017</v>
       </c>
       <c r="K77" t="s">
-        <v>800</v>
+        <v>779</v>
       </c>
       <c r="L77">
         <v>30.378621105864486</v>
@@ -20565,7 +20565,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E095C656-32EC-483F-A9C0-C875B69C0001}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D2D85A-73CD-43BC-A573-5A8FD031DC9E}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
